--- a/Tu_Vung_On_Tap_JLPT_N2.xlsx
+++ b/Tu_Vung_On_Tap_JLPT_N2.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tu_Vung_On_Tap" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tu_Vung_On_Tap'!$A$1:$F$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tu_Vung_On_Tap'!$A$1:$F$451</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F213"/>
+  <dimension ref="A1:F451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6903,8 +6903,7148 @@
         </is>
       </c>
     </row>
+    <row r="214" ht="24" customHeight="1">
+      <c r="A214" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>済ます</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>すます</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>Hoàn thành, làm xong, kết thúc</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>できるだけ早く仕事を済ます (cố gắng làm xong việc càng sớm càng tốt)</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 219] Đồng nghĩa với 終える.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="24" customHeight="1">
+      <c r="A215" s="8" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="9" t="inlineStr">
+        <is>
+          <t>覚える</t>
+        </is>
+      </c>
+      <c r="C215" s="9" t="inlineStr">
+        <is>
+          <t>おぼえる</t>
+        </is>
+      </c>
+      <c r="D215" s="10" t="inlineStr">
+        <is>
+          <t>Ghi nhớ, học thuộc; cảm thấy</t>
+        </is>
+      </c>
+      <c r="E215" s="10" t="inlineStr">
+        <is>
+          <t>単語を暗記して覚える (học thuộc từ vựng)</t>
+        </is>
+      </c>
+      <c r="F215" s="10" t="inlineStr">
+        <is>
+          <t>Ghi nhớ vào đầu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="24" customHeight="1">
+      <c r="A216" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>終える</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>おえる</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>Kết thúc, hoàn thành việc gì</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>今日の仕事を無事に終える (hoàn thành công việc hôm nay an toàn)</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 219] = 済ます.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="24" customHeight="1">
+      <c r="A217" s="8" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="9" t="inlineStr">
+        <is>
+          <t>始める</t>
+        </is>
+      </c>
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>はじめる</t>
+        </is>
+      </c>
+      <c r="D217" s="10" t="inlineStr">
+        <is>
+          <t>Bắt đầu làm việc gì</t>
+        </is>
+      </c>
+      <c r="E217" s="10" t="inlineStr">
+        <is>
+          <t>新しい趣味を始める (bắt đầu một sở thích mới)</t>
+        </is>
+      </c>
+      <c r="F217" s="10" t="inlineStr">
+        <is>
+          <t>Khởi đầu một hành động.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="24" customHeight="1">
+      <c r="A218" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>教える</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>おしえる</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr">
+        <is>
+          <t>Dạy học, chỉ dẫn, nói cho biết</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>駅への道を教える (chỉ đường ra ga)</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>Cung cấp kiến thức hoặc thông tin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="24" customHeight="1">
+      <c r="A219" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>あいまい</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>あいまい (曖昧)</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>Mơ hồ, mập mờ, không rõ ràng</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>態度があいまいだ (thái độ mập mờ, nước đôi)</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 220] Đồng nghĩa với はっきりしない.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="24" customHeight="1">
+      <c r="A220" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>丁寧</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>ていねい (丁寧)</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>Lịch sự, cẩn thận, chu đáo</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>丁寧な言葉遣い (cách dùng từ lịch sự, nhã nhặn)</t>
+        </is>
+      </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>Thái độ tôn trọng, cẩn thận.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="24" customHeight="1">
+      <c r="A221" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>はっきりしない</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>はっきりしない</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>Không rõ ràng, không dứt khoát</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>態度がはっきりしない (thái độ không dứt khoát, mập mờ)</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 220] = あいまい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="24" customHeight="1">
+      <c r="A222" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>立派</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>りっぱ (立派)</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t>Tuyệt vời, đàng hoàng, vẻ vang</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>立派な業績を残す (để lại thành tích xuất sắc, đáng nể)</t>
+        </is>
+      </c>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>Đáng khâm phục, hoành tráng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="24" customHeight="1">
+      <c r="A223" s="8" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="9" t="inlineStr">
+        <is>
+          <t>情けない</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>なさけない (情けない)</t>
+        </is>
+      </c>
+      <c r="D223" s="10" t="inlineStr">
+        <is>
+          <t>Thảm hại, đáng thương, đáng xấu hổ</t>
+        </is>
+      </c>
+      <c r="E223" s="10" t="inlineStr">
+        <is>
+          <t>こんなミスをするなんて情けない (mắc lỗi ngớ ngẩn thế này thật thảm hại)</t>
+        </is>
+      </c>
+      <c r="F223" s="10" t="inlineStr">
+        <is>
+          <t>Tự trách bản thân hoặc thấy tệ hại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="24" customHeight="1">
+      <c r="A224" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>思いがけない</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>おもいがけない</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>Bất ngờ, ngoài dự tính, không ngờ tới</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>思いがけない出来事 (sự việc bất ngờ xảy đến)</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 221] Đồng nghĩa với 意外な.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="24" customHeight="1">
+      <c r="A225" s="8" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="9" t="inlineStr">
+        <is>
+          <t>面白い</t>
+        </is>
+      </c>
+      <c r="C225" s="9" t="inlineStr">
+        <is>
+          <t>おもしろい</t>
+        </is>
+      </c>
+      <c r="D225" s="10" t="inlineStr">
+        <is>
+          <t>Thú vị, hấp dẫn, hài hước</t>
+        </is>
+      </c>
+      <c r="E225" s="10" t="inlineStr">
+        <is>
+          <t>面白い小説を読む (đọc một cuốn tiểu thuyết hay)</t>
+        </is>
+      </c>
+      <c r="F225" s="10" t="inlineStr">
+        <is>
+          <t>Gây hứng thú, cười vui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="24" customHeight="1">
+      <c r="A226" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>悲しい</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>かなしい</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>Đau buồn, buồn bã</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>悲しい知らせを聞く (nghe tin buồn)</t>
+        </is>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>Tâm trạng đau lòng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="24" customHeight="1">
+      <c r="A227" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>意外な</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>いがいな</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>Bất ngờ, ngoài sức tưởng tượng</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>意外な結果に驚く (ngạc nhiên trước kết quả bất ngờ)</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 221] = 思いがけない.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="24" customHeight="1">
+      <c r="A228" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>不思議な</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>ふしぎな</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>Kỳ lạ, kỳ diệu, bí ẩn</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>不思議な現象が起こる (xảy ra hiện tượng kỳ bí)</t>
+        </is>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>Không thể giải thích bằng lẽ thường.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="24" customHeight="1">
+      <c r="A229" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>みずから</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>みずから (自ら)</t>
+        </is>
+      </c>
+      <c r="D229" s="7" t="inlineStr">
+        <is>
+          <t>Tự mình, đích thân, tự thân</t>
+        </is>
+      </c>
+      <c r="E229" s="7" t="inlineStr">
+        <is>
+          <t>みずから会社を立ち上げる (tự mình đứng ra thành lập công ty)</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 222] Đồng nghĩa với 自分で.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="24" customHeight="1">
+      <c r="A230" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>自分で</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>じぶんで</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>Tự bản thân mình</t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t>自分で決める (tự bản thân quyết định)</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 222] = みずから.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="24" customHeight="1">
+      <c r="A231" s="8" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="9" t="inlineStr">
+        <is>
+          <t>すぐに</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="inlineStr">
+        <is>
+          <t>すぐに</t>
+        </is>
+      </c>
+      <c r="D231" s="10" t="inlineStr">
+        <is>
+          <t>Ngay lập tức, tức thì</t>
+        </is>
+      </c>
+      <c r="E231" s="10" t="inlineStr">
+        <is>
+          <t>すぐに電話する (gọi điện thoại ngay lập tức)</t>
+        </is>
+      </c>
+      <c r="F231" s="10" t="inlineStr">
+        <is>
+          <t>Khoảng thời gian cực ngắn sau đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="24" customHeight="1">
+      <c r="A232" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>仲間と</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>なかまと</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="inlineStr">
+        <is>
+          <t>Cùng với bạn bè bè bạn</t>
+        </is>
+      </c>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t>仲間と協力する (hợp tác cùng bạn bè chiến hữu)</t>
+        </is>
+      </c>
+      <c r="F232" s="4" t="inlineStr">
+        <is>
+          <t>Đi cùng đồng đội.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="24" customHeight="1">
+      <c r="A233" s="8" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="9" t="inlineStr">
+        <is>
+          <t>しばらくして</t>
+        </is>
+      </c>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t>しばらくして</t>
+        </is>
+      </c>
+      <c r="D233" s="10" t="inlineStr">
+        <is>
+          <t>Một lúc sau, một lát sau</t>
+        </is>
+      </c>
+      <c r="E233" s="10" t="inlineStr">
+        <is>
+          <t>しばらくして雨がやんだ (một lát sau trời tạnh mưa)</t>
+        </is>
+      </c>
+      <c r="F233" s="10" t="inlineStr">
+        <is>
+          <t>Trôi qua một đoạn thời gian ngắn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="24" customHeight="1">
+      <c r="A234" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>そろう</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>そろう (揃う)</t>
+        </is>
+      </c>
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>Tập hợp đầy đủ, tề tựu đông đủ</t>
+        </is>
+      </c>
+      <c r="E234" s="7" t="inlineStr">
+        <is>
+          <t>全員がそろう (mọi người đã tập hợp đầy đủ)</t>
+        </is>
+      </c>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 223] Đồng nghĩa với 集まる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="24" customHeight="1">
+      <c r="A235" s="5" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>集まる</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>あつまる</t>
+        </is>
+      </c>
+      <c r="D235" s="7" t="inlineStr">
+        <is>
+          <t>Tập trung lại, tụ họp</t>
+        </is>
+      </c>
+      <c r="E235" s="7" t="inlineStr">
+        <is>
+          <t>広場に人が集まる (mọi người tụ tập ở quảng trường)</t>
+        </is>
+      </c>
+      <c r="F235" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 223] = そろう.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="24" customHeight="1">
+      <c r="A236" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>訪ねる</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>たずねる</t>
+        </is>
+      </c>
+      <c r="D236" s="4" t="inlineStr">
+        <is>
+          <t>Đến thăm, ghé chơi</t>
+        </is>
+      </c>
+      <c r="E236" s="4" t="inlineStr">
+        <is>
+          <t>恩師の家を訪ねる (đến thăm nhà thầy giáo cũ)</t>
+        </is>
+      </c>
+      <c r="F236" s="4" t="inlineStr">
+        <is>
+          <t>Ghé thăm ai đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="24" customHeight="1">
+      <c r="A237" s="8" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="9" t="inlineStr">
+        <is>
+          <t>出発する</t>
+        </is>
+      </c>
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>しゅっぱつする</t>
+        </is>
+      </c>
+      <c r="D237" s="10" t="inlineStr">
+        <is>
+          <t>Xuất phát, khởi hành</t>
+        </is>
+      </c>
+      <c r="E237" s="10" t="inlineStr">
+        <is>
+          <t>定刻に出発する (khởi hành đúng giờ)</t>
+        </is>
+      </c>
+      <c r="F237" s="10" t="inlineStr">
+        <is>
+          <t>Bắt đầu chuyến đi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="24" customHeight="1">
+      <c r="A238" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>案内する</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>あんないする</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, dẫn đường</t>
+        </is>
+      </c>
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>市内を案内する (dẫn đường hướng dẫn tham quan nội thành)</t>
+        </is>
+      </c>
+      <c r="F238" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ dẫn đường đi lối lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="24" customHeight="1">
+      <c r="A239" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t>およそ</t>
+        </is>
+      </c>
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>およそ</t>
+        </is>
+      </c>
+      <c r="D239" s="7" t="inlineStr">
+        <is>
+          <t>Khoảng chừng, xấp xỉ (= 約)</t>
+        </is>
+      </c>
+      <c r="E239" s="7" t="inlineStr">
+        <is>
+          <t>荷物の重さはおよそ5キロ (khối lượng hành lý khoảng chừng 5kg)</t>
+        </is>
+      </c>
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 224] Đồng nghĩa với だいたい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="24" customHeight="1">
+      <c r="A240" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>全部で</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>ぜんぶで</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>Tổng cộng tất cả</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>全部でいくらですか (tất cả hết bao nhiêu tiền)</t>
+        </is>
+      </c>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>Toàn bộ số lượng tính gộp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="24" customHeight="1">
+      <c r="A241" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="9" t="inlineStr">
+        <is>
+          <t>ぴったり</t>
+        </is>
+      </c>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>ぴったり</t>
+        </is>
+      </c>
+      <c r="D241" s="10" t="inlineStr">
+        <is>
+          <t>Vừa khít, chuẩn xác không thừa thiếu</t>
+        </is>
+      </c>
+      <c r="E241" s="10" t="inlineStr">
+        <is>
+          <t>時間がぴったりだ (giờ giấc chuẩn xác từng phút)</t>
+        </is>
+      </c>
+      <c r="F241" s="10" t="inlineStr">
+        <is>
+          <t>Không xê xích chút nào.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="24" customHeight="1">
+      <c r="A242" s="5" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t>だいたい</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>だいたい</t>
+        </is>
+      </c>
+      <c r="D242" s="7" t="inlineStr">
+        <is>
+          <t>Đại khái, khoảng chừng, hầu như</t>
+        </is>
+      </c>
+      <c r="E242" s="7" t="inlineStr">
+        <is>
+          <t>だいたい理解した (đại khái đã hiểu gần hết)</t>
+        </is>
+      </c>
+      <c r="F242" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 224] = およそ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="24" customHeight="1">
+      <c r="A243" s="8" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="9" t="inlineStr">
+        <is>
+          <t>それぞれ</t>
+        </is>
+      </c>
+      <c r="C243" s="9" t="inlineStr">
+        <is>
+          <t>それぞれ</t>
+        </is>
+      </c>
+      <c r="D243" s="10" t="inlineStr">
+        <is>
+          <t>Từng người, mỗi cái một vẻ</t>
+        </is>
+      </c>
+      <c r="E243" s="10" t="inlineStr">
+        <is>
+          <t>それぞれ意見を言う (mỗi người đưa ra ý kiến riêng)</t>
+        </is>
+      </c>
+      <c r="F243" s="10" t="inlineStr">
+        <is>
+          <t>Chỉ từng cá thể riêng rẽ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="24" customHeight="1">
+      <c r="A244" s="5" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
+        <is>
+          <t>プラン</t>
+        </is>
+      </c>
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>プラン</t>
+        </is>
+      </c>
+      <c r="D244" s="7" t="inlineStr">
+        <is>
+          <t>Kế hoạch, bản dự thảo (plan)</t>
+        </is>
+      </c>
+      <c r="E244" s="7" t="inlineStr">
+        <is>
+          <t>具体的なプランを教えてほしい (hãy nói cho tôi kế hoạch cụ thể)</t>
+        </is>
+      </c>
+      <c r="F244" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 225] Đồng nghĩa với 計画.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="24" customHeight="1">
+      <c r="A245" s="8" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="9" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="C245" s="9" t="inlineStr">
+        <is>
+          <t>りゆう</t>
+        </is>
+      </c>
+      <c r="D245" s="10" t="inlineStr">
+        <is>
+          <t>Lý do, nguyên cớ</t>
+        </is>
+      </c>
+      <c r="E245" s="10" t="inlineStr">
+        <is>
+          <t>遅刻した理由を説明する (giải thích lý do đi muộn)</t>
+        </is>
+      </c>
+      <c r="F245" s="10" t="inlineStr">
+        <is>
+          <t>Nguyên nhân sự việc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="24" customHeight="1">
+      <c r="A246" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>情報</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>じょうほう</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>Thông tin, dữ liệu</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>最新の情報を集める (thu thập thông tin mới nhất)</t>
+        </is>
+      </c>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>Tin tức dữ liệu trong đời sống/máy móc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="24" customHeight="1">
+      <c r="A247" s="8" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="9" t="inlineStr">
+        <is>
+          <t>特徴</t>
+        </is>
+      </c>
+      <c r="C247" s="9" t="inlineStr">
+        <is>
+          <t>とくちょう</t>
+        </is>
+      </c>
+      <c r="D247" s="10" t="inlineStr">
+        <is>
+          <t>Đặc trưng, điểm nổi bật</t>
+        </is>
+      </c>
+      <c r="E247" s="10" t="inlineStr">
+        <is>
+          <t>商品の特徴をアピールする (quảng bá đặc trưng sản phẩm)</t>
+        </is>
+      </c>
+      <c r="F247" s="10" t="inlineStr">
+        <is>
+          <t>Nét riêng biệt của sự vật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="24" customHeight="1">
+      <c r="A248" s="5" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="6" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>けいかく</t>
+        </is>
+      </c>
+      <c r="D248" s="7" t="inlineStr">
+        <is>
+          <t>Kế hoạch, dự định</t>
+        </is>
+      </c>
+      <c r="E248" s="7" t="inlineStr">
+        <is>
+          <t>将来の計画を立てる (lên kế hoạch cho tương lai)</t>
+        </is>
+      </c>
+      <c r="F248" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 225] = プラン.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="24" customHeight="1">
+      <c r="A249" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="6" t="inlineStr">
+        <is>
+          <t>依然として</t>
+        </is>
+      </c>
+      <c r="C249" s="6" t="inlineStr">
+        <is>
+          <t>いぜんとして</t>
+        </is>
+      </c>
+      <c r="D249" s="7" t="inlineStr">
+        <is>
+          <t>Vẫn như trước, vẫn y nguyên</t>
+        </is>
+      </c>
+      <c r="E249" s="7" t="inlineStr">
+        <is>
+          <t>経済状況は依然として厳しい (tình hình kinh tế vẫn gay gắt như cũ)</t>
+        </is>
+      </c>
+      <c r="F249" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 226] Đồng nghĩa với 相変わらず.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="24" customHeight="1">
+      <c r="A250" s="5" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="6" t="inlineStr">
+        <is>
+          <t>相変わらず</t>
+        </is>
+      </c>
+      <c r="C250" s="6" t="inlineStr">
+        <is>
+          <t>あいかわらず</t>
+        </is>
+      </c>
+      <c r="D250" s="7" t="inlineStr">
+        <is>
+          <t>Vẫn như cũ, như mọi khi</t>
+        </is>
+      </c>
+      <c r="E250" s="7" t="inlineStr">
+        <is>
+          <t>相変わらず元気そうだ (trông anh vẫn khỏe khoắn như mọi khi)</t>
+        </is>
+      </c>
+      <c r="F250" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 226] = 依然として.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="24" customHeight="1">
+      <c r="A251" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="9" t="inlineStr">
+        <is>
+          <t>思ったとおり</t>
+        </is>
+      </c>
+      <c r="C251" s="9" t="inlineStr">
+        <is>
+          <t>おもったとおり</t>
+        </is>
+      </c>
+      <c r="D251" s="10" t="inlineStr">
+        <is>
+          <t>Đúng như đã nghĩ</t>
+        </is>
+      </c>
+      <c r="E251" s="10" t="inlineStr">
+        <is>
+          <t>思ったとおりの結果になった (kết quả diễn ra đúng như dự đoán)</t>
+        </is>
+      </c>
+      <c r="F251" s="10" t="inlineStr">
+        <is>
+          <t>Khớp với suy nghĩ ban đầu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="24" customHeight="1">
+      <c r="A252" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>実際には</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>じっさいには</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="inlineStr">
+        <is>
+          <t>Trên thực tế</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="inlineStr">
+        <is>
+          <t>実際にはそう簡単ではない (trên thực tế không hề đơn giản vậy)</t>
+        </is>
+      </c>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>Đối chiếu với thực tế ngoài đời.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="24" customHeight="1">
+      <c r="A253" s="8" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="9" t="inlineStr">
+        <is>
+          <t>これまでより</t>
+        </is>
+      </c>
+      <c r="C253" s="9" t="inlineStr">
+        <is>
+          <t>これまでより</t>
+        </is>
+      </c>
+      <c r="D253" s="10" t="inlineStr">
+        <is>
+          <t>Hơn so với trước đây</t>
+        </is>
+      </c>
+      <c r="E253" s="10" t="inlineStr">
+        <is>
+          <t>これまでより努力が必要だ (cần nỗ lực hơn trước đây nhiều)</t>
+        </is>
+      </c>
+      <c r="F253" s="10" t="inlineStr">
+        <is>
+          <t>So sánh với thời gian trong quá khứ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="24" customHeight="1">
+      <c r="A254" s="5" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="6" t="inlineStr">
+        <is>
+          <t>必死</t>
+        </is>
+      </c>
+      <c r="C254" s="6" t="inlineStr">
+        <is>
+          <t>ひっし</t>
+        </is>
+      </c>
+      <c r="D254" s="7" t="inlineStr">
+        <is>
+          <t>Dốc hết sức, liều mạng, hết mình</t>
+        </is>
+      </c>
+      <c r="E254" s="7" t="inlineStr">
+        <is>
+          <t>あのときは本当に必死だった (khi ấy tôi đã thực sự dốc hết toàn lực)</t>
+        </is>
+      </c>
+      <c r="F254" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 227] Đồng nghĩa với 一生懸命.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="24" customHeight="1">
+      <c r="A255" s="8" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="9" t="inlineStr">
+        <is>
+          <t>危ない</t>
+        </is>
+      </c>
+      <c r="C255" s="9" t="inlineStr">
+        <is>
+          <t>あぶない</t>
+        </is>
+      </c>
+      <c r="D255" s="10" t="inlineStr">
+        <is>
+          <t>Nguy hiểm</t>
+        </is>
+      </c>
+      <c r="E255" s="10" t="inlineStr">
+        <is>
+          <t>危ないから近寄るな (nguy hiểm đừng lại gần)</t>
+        </is>
+      </c>
+      <c r="F255" s="10" t="inlineStr">
+        <is>
+          <t>Mối đe dọa an toàn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="24" customHeight="1">
+      <c r="A256" s="5" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="6" t="inlineStr">
+        <is>
+          <t>一生懸命</t>
+        </is>
+      </c>
+      <c r="C256" s="6" t="inlineStr">
+        <is>
+          <t>いっしょうけんめい</t>
+        </is>
+      </c>
+      <c r="D256" s="7" t="inlineStr">
+        <is>
+          <t>Hết sức mình, miệt mài dốc lòng</t>
+        </is>
+      </c>
+      <c r="E256" s="7" t="inlineStr">
+        <is>
+          <t>一生懸命勉強する (dốc sức miệt mài học tập)</t>
+        </is>
+      </c>
+      <c r="F256" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 227] = 必死.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="24" customHeight="1">
+      <c r="A257" s="8" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="9" t="inlineStr">
+        <is>
+          <t>緊張した</t>
+        </is>
+      </c>
+      <c r="C257" s="9" t="inlineStr">
+        <is>
+          <t>きんちょうした</t>
+        </is>
+      </c>
+      <c r="D257" s="10" t="inlineStr">
+        <is>
+          <t>Căng thẳng, hồi hộp</t>
+        </is>
+      </c>
+      <c r="E257" s="10" t="inlineStr">
+        <is>
+          <t>面接でとても緊張した (vô cùng căng thẳng trong buổi phỏng vấn)</t>
+        </is>
+      </c>
+      <c r="F257" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái tâm lý tim đập chân run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="24" customHeight="1">
+      <c r="A258" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>恐ろしかった</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>おそろしかった</t>
+        </is>
+      </c>
+      <c r="D258" s="4" t="inlineStr">
+        <is>
+          <t>Kinh khủng, đáng sợ khiếp đảm</t>
+        </is>
+      </c>
+      <c r="E258" s="4" t="inlineStr">
+        <is>
+          <t>恐ろしい夢を見て起きた (tỉnh dậy sau cơn ác mộng kinh hoàng)</t>
+        </is>
+      </c>
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>Gây sợ hãi cực độ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="24" customHeight="1">
+      <c r="A259" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="6" t="inlineStr">
+        <is>
+          <t>ふもと</t>
+        </is>
+      </c>
+      <c r="C259" s="6" t="inlineStr">
+        <is>
+          <t>ふもと (麓)</t>
+        </is>
+      </c>
+      <c r="D259" s="7" t="inlineStr">
+        <is>
+          <t>Chân núi, vùng chân đồi</t>
+        </is>
+      </c>
+      <c r="E259" s="7" t="inlineStr">
+        <is>
+          <t>山のふもとにきれいな湖がある (ở chân núi có một hồ nước tuyệt đẹp)</t>
+        </is>
+      </c>
+      <c r="F259" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 228] Đồng nghĩa với 山の下のほう.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="24" customHeight="1">
+      <c r="A260" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>山の向こう</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>やまのむこう</t>
+        </is>
+      </c>
+      <c r="D260" s="4" t="inlineStr">
+        <is>
+          <t>Phía bên kia ngọn núi</t>
+        </is>
+      </c>
+      <c r="E260" s="4" t="inlineStr">
+        <is>
+          <t>山の向こうに海が見える (bên kia núi nhìn thấy biển)</t>
+        </is>
+      </c>
+      <c r="F260" s="4" t="inlineStr">
+        <is>
+          <t>Vị trí khuất sau dãy núi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="24" customHeight="1">
+      <c r="A261" s="8" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="9" t="inlineStr">
+        <is>
+          <t>山の上のほう</t>
+        </is>
+      </c>
+      <c r="C261" s="9" t="inlineStr">
+        <is>
+          <t>やまのうえのほう</t>
+        </is>
+      </c>
+      <c r="D261" s="10" t="inlineStr">
+        <is>
+          <t>Phía trên đỉnh núi, phía cao</t>
+        </is>
+      </c>
+      <c r="E261" s="10" t="inlineStr">
+        <is>
+          <t>山の上のほうは雪が積もっている (phía trên núi tuyết đóng dày)</t>
+        </is>
+      </c>
+      <c r="F261" s="10" t="inlineStr">
+        <is>
+          <t>Khu vực đỉnh núi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="24" customHeight="1">
+      <c r="A262" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>山の中間あたり</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>やまのちゅうかんあたり</t>
+        </is>
+      </c>
+      <c r="D262" s="4" t="inlineStr">
+        <is>
+          <t>Khu vực lưng chừng núi</t>
+        </is>
+      </c>
+      <c r="E262" s="4" t="inlineStr">
+        <is>
+          <t>山の中間あたりで休憩する (nghỉ chân ở lưng chừng núi)</t>
+        </is>
+      </c>
+      <c r="F262" s="4" t="inlineStr">
+        <is>
+          <t>Lưng chừng núi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="24" customHeight="1">
+      <c r="A263" s="5" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
+        <is>
+          <t>山の下のほう</t>
+        </is>
+      </c>
+      <c r="C263" s="6" t="inlineStr">
+        <is>
+          <t>やまのしたのほう</t>
+        </is>
+      </c>
+      <c r="D263" s="7" t="inlineStr">
+        <is>
+          <t>Phía chân núi, vùng dưới thấp</t>
+        </is>
+      </c>
+      <c r="E263" s="7" t="inlineStr">
+        <is>
+          <t>山の下のほうに村がある (phía dưới chân núi có ngôi làng)</t>
+        </is>
+      </c>
+      <c r="F263" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 228] = ふもと.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="24" customHeight="1">
+      <c r="A264" s="5" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="6" t="inlineStr">
+        <is>
+          <t>そろえる</t>
+        </is>
+      </c>
+      <c r="C264" s="6" t="inlineStr">
+        <is>
+          <t>そろえる (揃える)</t>
+        </is>
+      </c>
+      <c r="D264" s="7" t="inlineStr">
+        <is>
+          <t>Làm cho đồng đều, đồng nhất</t>
+        </is>
+      </c>
+      <c r="E264" s="7" t="inlineStr">
+        <is>
+          <t>文字のサイズをそろえてください (xin hãy chỉnh cỡ chữ cho đồng nhất)</t>
+        </is>
+      </c>
+      <c r="F264" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 229] Đồng nghĩa với 同じにする.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="24" customHeight="1">
+      <c r="A265" s="8" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
+        <is>
+          <t>大きくして</t>
+        </is>
+      </c>
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>おおきくして</t>
+        </is>
+      </c>
+      <c r="D265" s="10" t="inlineStr">
+        <is>
+          <t>Làm cho to lớn ra</t>
+        </is>
+      </c>
+      <c r="E265" s="10" t="inlineStr">
+        <is>
+          <t>写真を大きくして印刷する (phóng to ảnh rồi in)</t>
+        </is>
+      </c>
+      <c r="F265" s="10" t="inlineStr">
+        <is>
+          <t>Tăng kích thước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="24" customHeight="1">
+      <c r="A266" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
+        <is>
+          <t>同じにして</t>
+        </is>
+      </c>
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>おなじにして</t>
+        </is>
+      </c>
+      <c r="D266" s="7" t="inlineStr">
+        <is>
+          <t>Làm cho giống nhau, đồng nhất kích cỡ</t>
+        </is>
+      </c>
+      <c r="E266" s="7" t="inlineStr">
+        <is>
+          <t>サイズを同じにして並べる (chỉnh kích cỡ bằng nhau rồi xếp ngay ngắn)</t>
+        </is>
+      </c>
+      <c r="F266" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 229] = そろえる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="24" customHeight="1">
+      <c r="A267" s="8" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="9" t="inlineStr">
+        <is>
+          <t>調べて</t>
+        </is>
+      </c>
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>しらべて</t>
+        </is>
+      </c>
+      <c r="D267" s="10" t="inlineStr">
+        <is>
+          <t>Tra cứu, tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E267" s="10" t="inlineStr">
+        <is>
+          <t>辞書で意味を調べてみる (tra từ điển xem ý nghĩa)</t>
+        </is>
+      </c>
+      <c r="F267" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra thông tin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="24" customHeight="1">
+      <c r="A268" s="5" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
+        <is>
+          <t>買い占める</t>
+        </is>
+      </c>
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>かいしめる</t>
+        </is>
+      </c>
+      <c r="D268" s="7" t="inlineStr">
+        <is>
+          <t>Mua vét sạch, mua gom toàn bộ</t>
+        </is>
+      </c>
+      <c r="E268" s="7" t="inlineStr">
+        <is>
+          <t>空いた土地を買いしめた (mua gom sạch toàn bộ khu đất trống)</t>
+        </is>
+      </c>
+      <c r="F268" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 230] Đồng nghĩa với 全部買った.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="24" customHeight="1">
+      <c r="A269" s="8" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="9" t="inlineStr">
+        <is>
+          <t>無理に買った</t>
+        </is>
+      </c>
+      <c r="C269" s="9" t="inlineStr">
+        <is>
+          <t>むりにかった</t>
+        </is>
+      </c>
+      <c r="D269" s="10" t="inlineStr">
+        <is>
+          <t>Mua gượng ép, cố quá sức mua</t>
+        </is>
+      </c>
+      <c r="E269" s="10" t="inlineStr">
+        <is>
+          <t>予算オーバーだが無理に買った (quá ngân sách nhưng vẫn cố bấm bụng mua)</t>
+        </is>
+      </c>
+      <c r="F269" s="10" t="inlineStr">
+        <is>
+          <t>Mua quá khả năng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="24" customHeight="1">
+      <c r="A270" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
+        <is>
+          <t>全部買った</t>
+        </is>
+      </c>
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>ぜんぶかった</t>
+        </is>
+      </c>
+      <c r="D270" s="7" t="inlineStr">
+        <is>
+          <t>Mua toàn bộ, mua hết sạch</t>
+        </is>
+      </c>
+      <c r="E270" s="7" t="inlineStr">
+        <is>
+          <t>店頭の商品を全部買った (mua sạch sành sanh hàng trên kệ)</t>
+        </is>
+      </c>
+      <c r="F270" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 230] = 買い占める.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="24" customHeight="1">
+      <c r="A271" s="8" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="9" t="inlineStr">
+        <is>
+          <t>安く買った</t>
+        </is>
+      </c>
+      <c r="C271" s="9" t="inlineStr">
+        <is>
+          <t>やすくかった</t>
+        </is>
+      </c>
+      <c r="D271" s="10" t="inlineStr">
+        <is>
+          <t>Mua với giá rẻ</t>
+        </is>
+      </c>
+      <c r="E271" s="10" t="inlineStr">
+        <is>
+          <t>セールで安く買った (mua được giá rẻ trong đợt giảm giá)</t>
+        </is>
+      </c>
+      <c r="F271" s="10" t="inlineStr">
+        <is>
+          <t>Mua được hời.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="24" customHeight="1">
+      <c r="A272" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>さっそく買った</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>さっそくかった</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="inlineStr">
+        <is>
+          <t>Mua ngay lập tức không chần chừ</t>
+        </is>
+      </c>
+      <c r="E272" s="4" t="inlineStr">
+        <is>
+          <t>発売日にさっそく買った (vừa mở bán là mua liền tay)</t>
+        </is>
+      </c>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>Làm ngay lập tức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="24" customHeight="1">
+      <c r="A273" s="5" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t>間際</t>
+        </is>
+      </c>
+      <c r="C273" s="6" t="inlineStr">
+        <is>
+          <t>まぎわ</t>
+        </is>
+      </c>
+      <c r="D273" s="7" t="inlineStr">
+        <is>
+          <t>Ngay trước khi, sát nút (= 直前)</t>
+        </is>
+      </c>
+      <c r="E273" s="7" t="inlineStr">
+        <is>
+          <t>出発間際に電話がかかってきた (ngay trước khi xuất phát thì điện thoại reo)</t>
+        </is>
+      </c>
+      <c r="F273" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 231] Đồng nghĩa với 直前.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="24" customHeight="1">
+      <c r="A274" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="6" t="inlineStr">
+        <is>
+          <t>直前</t>
+        </is>
+      </c>
+      <c r="C274" s="6" t="inlineStr">
+        <is>
+          <t>ちょくぜん</t>
+        </is>
+      </c>
+      <c r="D274" s="7" t="inlineStr">
+        <is>
+          <t>Ngay trước thời điểm</t>
+        </is>
+      </c>
+      <c r="E274" s="7" t="inlineStr">
+        <is>
+          <t>テストの直前に復習する (ôn bài ngay sát giờ thi)</t>
+        </is>
+      </c>
+      <c r="F274" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 231] = 間際.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="24" customHeight="1">
+      <c r="A275" s="8" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="9" t="inlineStr">
+        <is>
+          <t>直後</t>
+        </is>
+      </c>
+      <c r="C275" s="9" t="inlineStr">
+        <is>
+          <t>ちょくご</t>
+        </is>
+      </c>
+      <c r="D275" s="10" t="inlineStr">
+        <is>
+          <t>Ngay sau thời điểm</t>
+        </is>
+      </c>
+      <c r="E275" s="10" t="inlineStr">
+        <is>
+          <t>卒業の直後に就職した (vừa tốt nghiệp xong là đi làm ngay)</t>
+        </is>
+      </c>
+      <c r="F275" s="10" t="inlineStr">
+        <is>
+          <t>Ngay sau khi kết thúc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="24" customHeight="1">
+      <c r="A276" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>当日</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>とうじつ</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện, chính ngày hôm đó</t>
+        </is>
+      </c>
+      <c r="E276" s="4" t="inlineStr">
+        <is>
+          <t>試験の当日に遅刻する (đến muộn vào đúng ngày thi)</t>
+        </is>
+      </c>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>Ngày ấn định sự kiện.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="24" customHeight="1">
+      <c r="A277" s="8" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="9" t="inlineStr">
+        <is>
+          <t>前日</t>
+        </is>
+      </c>
+      <c r="C277" s="9" t="inlineStr">
+        <is>
+          <t>ぜんじつ</t>
+        </is>
+      </c>
+      <c r="D277" s="10" t="inlineStr">
+        <is>
+          <t>Ngày hôm trước</t>
+        </is>
+      </c>
+      <c r="E277" s="10" t="inlineStr">
+        <is>
+          <t>結婚式の前日に準備を終える (hoàn tất chuẩn bị vào ngày hôm trước đám cưới)</t>
+        </is>
+      </c>
+      <c r="F277" s="10" t="inlineStr">
+        <is>
+          <t>Ngày liền kề trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="24" customHeight="1">
+      <c r="A278" s="5" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="6" t="inlineStr">
+        <is>
+          <t>たちまち</t>
+        </is>
+      </c>
+      <c r="C278" s="6" t="inlineStr">
+        <is>
+          <t>たちまち</t>
+        </is>
+      </c>
+      <c r="D278" s="7" t="inlineStr">
+        <is>
+          <t>Ngay lập tức, tức thì trong chớp mắt</t>
+        </is>
+      </c>
+      <c r="E278" s="7" t="inlineStr">
+        <is>
+          <t>薬を飲んだらたちまち治まった (uống thuốc xong là cơn đau dịu ngay lập tức)</t>
+        </is>
+      </c>
+      <c r="F278" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 232] Đồng nghĩa với すぐに.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="24" customHeight="1">
+      <c r="A279" s="8" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="9" t="inlineStr">
+        <is>
+          <t>すっかり</t>
+        </is>
+      </c>
+      <c r="C279" s="9" t="inlineStr">
+        <is>
+          <t>すっかり</t>
+        </is>
+      </c>
+      <c r="D279" s="10" t="inlineStr">
+        <is>
+          <t>Hoàn toàn, sạch trơn</t>
+        </is>
+      </c>
+      <c r="E279" s="10" t="inlineStr">
+        <is>
+          <t>すっかり忘れていた (quên bẵng đi hoàn toàn)</t>
+        </is>
+      </c>
+      <c r="F279" s="10" t="inlineStr">
+        <is>
+          <t>Hết sạch không còn vết tích.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="24" customHeight="1">
+      <c r="A280" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>やっと</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>やっと</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="inlineStr">
+        <is>
+          <t>Cuối cùng thì (sau nhiều gian nan)</t>
+        </is>
+      </c>
+      <c r="E280" s="4" t="inlineStr">
+        <is>
+          <t>やっと宿題が終わった (cuối cùng cũng làm xong bài tập)</t>
+        </is>
+      </c>
+      <c r="F280" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả sau một thời gian dài nỗ lực.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="24" customHeight="1">
+      <c r="A281" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="6" t="inlineStr">
+        <is>
+          <t>すぐに</t>
+        </is>
+      </c>
+      <c r="C281" s="6" t="inlineStr">
+        <is>
+          <t>すぐに</t>
+        </is>
+      </c>
+      <c r="D281" s="7" t="inlineStr">
+        <is>
+          <t>Ngay lập tức</t>
+        </is>
+      </c>
+      <c r="E281" s="7" t="inlineStr">
+        <is>
+          <t>すぐに医者を呼んでください (hãy gọi bác sĩ tới ngay lập tức)</t>
+        </is>
+      </c>
+      <c r="F281" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 232] = たちまち.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="24" customHeight="1">
+      <c r="A282" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>確かに</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>たしかに</t>
+        </is>
+      </c>
+      <c r="D282" s="4" t="inlineStr">
+        <is>
+          <t>Chắc chắn, quả thật đúng như vậy</t>
+        </is>
+      </c>
+      <c r="E282" s="4" t="inlineStr">
+        <is>
+          <t>確かに彼の言うとおりだ (quả thật đúng như lời anh ấy nói)</t>
+        </is>
+      </c>
+      <c r="F282" s="4" t="inlineStr">
+        <is>
+          <t>Xác nhận sự thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="24" customHeight="1">
+      <c r="A283" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="6" t="inlineStr">
+        <is>
+          <t>お勘定</t>
+        </is>
+      </c>
+      <c r="C283" s="6" t="inlineStr">
+        <is>
+          <t>おかんじょう</t>
+        </is>
+      </c>
+      <c r="D283" s="7" t="inlineStr">
+        <is>
+          <t>Thanh toán hóa đơn tiền bạc</t>
+        </is>
+      </c>
+      <c r="E283" s="7" t="inlineStr">
+        <is>
+          <t>もうお勘定は済ませました (tôi đã thanh toán tiền xong rồi)</t>
+        </is>
+      </c>
+      <c r="F283" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 233] Đồng nghĩa với お金を払う.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="24" customHeight="1">
+      <c r="A284" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>注文する</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>ちゅうもんする</t>
+        </is>
+      </c>
+      <c r="D284" s="4" t="inlineStr">
+        <is>
+          <t>Gọi món, đặt hàng</t>
+        </is>
+      </c>
+      <c r="E284" s="4" t="inlineStr">
+        <is>
+          <t>レストランで料理を注文する (gọi món ăn ở nhà hàng)</t>
+        </is>
+      </c>
+      <c r="F284" s="4" t="inlineStr">
+        <is>
+          <t>Yêu cầu món hoặc đặt hàng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="24" customHeight="1">
+      <c r="A285" s="8" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="9" t="inlineStr">
+        <is>
+          <t>予約する</t>
+        </is>
+      </c>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>よやくする</t>
+        </is>
+      </c>
+      <c r="D285" s="10" t="inlineStr">
+        <is>
+          <t>Đặt chỗ trước, đặt bàn trước</t>
+        </is>
+      </c>
+      <c r="E285" s="10" t="inlineStr">
+        <is>
+          <t>ホテルの部屋を予約する (đặt phòng khách sạn trước)</t>
+        </is>
+      </c>
+      <c r="F285" s="10" t="inlineStr">
+        <is>
+          <t>Giữ chỗ trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="24" customHeight="1">
+      <c r="A286" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>呼ぶ</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>よぶ</t>
+        </is>
+      </c>
+      <c r="D286" s="4" t="inlineStr">
+        <is>
+          <t>Gọi ai đó lại</t>
+        </is>
+      </c>
+      <c r="E286" s="4" t="inlineStr">
+        <is>
+          <t>店員を大きな声で呼ぶ (gọi nhân viên bằng giọng to)</t>
+        </is>
+      </c>
+      <c r="F286" s="4" t="inlineStr">
+        <is>
+          <t>Cất tiếng gọi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="24" customHeight="1">
+      <c r="A287" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="6" t="inlineStr">
+        <is>
+          <t>お金を払う</t>
+        </is>
+      </c>
+      <c r="C287" s="6" t="inlineStr">
+        <is>
+          <t>おかねをはらう</t>
+        </is>
+      </c>
+      <c r="D287" s="7" t="inlineStr">
+        <is>
+          <t>Thanh toán tiền, trả tiền</t>
+        </is>
+      </c>
+      <c r="E287" s="7" t="inlineStr">
+        <is>
+          <t>レジでお金を払う (trả tiền ở quầy thu ngân)</t>
+        </is>
+      </c>
+      <c r="F287" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 233] = お勘定をする.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="24" customHeight="1">
+      <c r="A288" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
+        <is>
+          <t>異なる</t>
+        </is>
+      </c>
+      <c r="C288" s="6" t="inlineStr">
+        <is>
+          <t>ことなる</t>
+        </is>
+      </c>
+      <c r="D288" s="7" t="inlineStr">
+        <is>
+          <t>Khác nhau, sai khác</t>
+        </is>
+      </c>
+      <c r="E288" s="7" t="inlineStr">
+        <is>
+          <t>テーマが異なる (chủ đề bài báo cáo khác nhau)</t>
+        </is>
+      </c>
+      <c r="F288" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 234] Đồng nghĩa với 違う.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="24" customHeight="1">
+      <c r="A289" s="8" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="9" t="inlineStr">
+        <is>
+          <t>単純</t>
+        </is>
+      </c>
+      <c r="C289" s="9" t="inlineStr">
+        <is>
+          <t>たんじゅん</t>
+        </is>
+      </c>
+      <c r="D289" s="10" t="inlineStr">
+        <is>
+          <t>Đơn giản, đơn thuần</t>
+        </is>
+      </c>
+      <c r="E289" s="10" t="inlineStr">
+        <is>
+          <t>単純なミス (sai sót đơn giản, ngớ ngẩn)</t>
+        </is>
+      </c>
+      <c r="F289" s="10" t="inlineStr">
+        <is>
+          <t>Không phức tạp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="24" customHeight="1">
+      <c r="A290" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>似ている</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>にている</t>
+        </is>
+      </c>
+      <c r="D290" s="4" t="inlineStr">
+        <is>
+          <t>Tương tự, giống nhau</t>
+        </is>
+      </c>
+      <c r="E290" s="4" t="inlineStr">
+        <is>
+          <t>親によく似ている (rất giống bố mẹ)</t>
+        </is>
+      </c>
+      <c r="F290" s="4" t="inlineStr">
+        <is>
+          <t>Có nhiều nét tương đồng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="24" customHeight="1">
+      <c r="A291" s="8" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="9" t="inlineStr">
+        <is>
+          <t>複雑</t>
+        </is>
+      </c>
+      <c r="C291" s="9" t="inlineStr">
+        <is>
+          <t>ふくざつ</t>
+        </is>
+      </c>
+      <c r="D291" s="10" t="inlineStr">
+        <is>
+          <t>Phức tạp, rắc rối</t>
+        </is>
+      </c>
+      <c r="E291" s="10" t="inlineStr">
+        <is>
+          <t>複雑な人間関係 (mối quan hệ con người phức tạp)</t>
+        </is>
+      </c>
+      <c r="F291" s="10" t="inlineStr">
+        <is>
+          <t>Nhiều yếu tố rườm rà.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="24" customHeight="1">
+      <c r="A292" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="6" t="inlineStr">
+        <is>
+          <t>違う</t>
+        </is>
+      </c>
+      <c r="C292" s="6" t="inlineStr">
+        <is>
+          <t>ちがう</t>
+        </is>
+      </c>
+      <c r="D292" s="7" t="inlineStr">
+        <is>
+          <t>Khác biệt, không giống</t>
+        </is>
+      </c>
+      <c r="E292" s="7" t="inlineStr">
+        <is>
+          <t>意見が違う (quan điểm khác nhau)</t>
+        </is>
+      </c>
+      <c r="F292" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 234] = 異なる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="24" customHeight="1">
+      <c r="A293" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
+        <is>
+          <t>たまたま</t>
+        </is>
+      </c>
+      <c r="C293" s="6" t="inlineStr">
+        <is>
+          <t>たまたま</t>
+        </is>
+      </c>
+      <c r="D293" s="7" t="inlineStr">
+        <is>
+          <t>Tình cờ, ngẫu nhiên gặp</t>
+        </is>
+      </c>
+      <c r="E293" s="7" t="inlineStr">
+        <is>
+          <t>街でたまたま会った (tình cờ gặp nhau trên phố)</t>
+        </is>
+      </c>
+      <c r="F293" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 235] Đồng nghĩa với 偶然.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="24" customHeight="1">
+      <c r="A294" s="5" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
+        <is>
+          <t>偶然</t>
+        </is>
+      </c>
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>ぐうぜん</t>
+        </is>
+      </c>
+      <c r="D294" s="7" t="inlineStr">
+        <is>
+          <t>Ngẫu nhiên, tình cờ bất ngờ</t>
+        </is>
+      </c>
+      <c r="E294" s="7" t="inlineStr">
+        <is>
+          <t>偶然の出会い (cuộc gặp gỡ định mệnh tình cờ)</t>
+        </is>
+      </c>
+      <c r="F294" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 235] = たまたま.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="24" customHeight="1">
+      <c r="A295" s="8" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="9" t="inlineStr">
+        <is>
+          <t>何度も</t>
+        </is>
+      </c>
+      <c r="C295" s="9" t="inlineStr">
+        <is>
+          <t>なんども</t>
+        </is>
+      </c>
+      <c r="D295" s="10" t="inlineStr">
+        <is>
+          <t>Nhiều lần, lặp đi lặp lại</t>
+        </is>
+      </c>
+      <c r="E295" s="10" t="inlineStr">
+        <is>
+          <t>何度も同じ過ちを繰り返す (lặp lại cùng một sai lầm nhiều lần)</t>
+        </is>
+      </c>
+      <c r="F295" s="10" t="inlineStr">
+        <is>
+          <t>Số lần diễn ra nhiều.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="24" customHeight="1">
+      <c r="A296" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="inlineStr">
+        <is>
+          <t>Vừa nãy, lúc nãy</t>
+        </is>
+      </c>
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>さっき届いた手紙 (bức thư vừa mới tới lúc nãy)</t>
+        </is>
+      </c>
+      <c r="F296" s="4" t="inlineStr">
+        <is>
+          <t>Thời điểm rất gần trong quá khứ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="24" customHeight="1">
+      <c r="A297" s="5" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
+        <is>
+          <t>明らかな</t>
+        </is>
+      </c>
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>あきらかな</t>
+        </is>
+      </c>
+      <c r="D297" s="7" t="inlineStr">
+        <is>
+          <t>Rõ ràng, minh bạch, rành rành</t>
+        </is>
+      </c>
+      <c r="E297" s="7" t="inlineStr">
+        <is>
+          <t>明らかな証拠がある (có bằng chứng rành rành rõ ràng)</t>
+        </is>
+      </c>
+      <c r="F297" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 236] Đồng nghĩa với はっきりした.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="24" customHeight="1">
+      <c r="A298" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>様々な</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>さまざまな</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
+        <is>
+          <t>Đa dạng, muôn màu muôn vẻ</t>
+        </is>
+      </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>様々な意見がある (có nhiều luồng ý kiến đa dạng)</t>
+        </is>
+      </c>
+      <c r="F298" s="4" t="inlineStr">
+        <is>
+          <t>Phong phú về chủng loại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="24" customHeight="1">
+      <c r="A299" s="8" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="9" t="inlineStr">
+        <is>
+          <t>別の</t>
+        </is>
+      </c>
+      <c r="C299" s="9" t="inlineStr">
+        <is>
+          <t>べつの</t>
+        </is>
+      </c>
+      <c r="D299" s="10" t="inlineStr">
+        <is>
+          <t>Khác, biệt lập</t>
+        </is>
+      </c>
+      <c r="E299" s="10" t="inlineStr">
+        <is>
+          <t>別の方法を試す (thử một phương pháp khác)</t>
+        </is>
+      </c>
+      <c r="F299" s="10" t="inlineStr">
+        <is>
+          <t>Không phải cái này mà là cái khác.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="24" customHeight="1">
+      <c r="A300" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>新しい</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>あたらしい</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>Mới mẻ</t>
+        </is>
+      </c>
+      <c r="E300" s="4" t="inlineStr">
+        <is>
+          <t>新しい靴を買う (mua một đôi giày mới)</t>
+        </is>
+      </c>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>Mới tinh, chưa cũ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="24" customHeight="1">
+      <c r="A301" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t>はっきりした</t>
+        </is>
+      </c>
+      <c r="C301" s="6" t="inlineStr">
+        <is>
+          <t>はっきりした</t>
+        </is>
+      </c>
+      <c r="D301" s="7" t="inlineStr">
+        <is>
+          <t>Rõ ràng, không mập mờ</t>
+        </is>
+      </c>
+      <c r="E301" s="7" t="inlineStr">
+        <is>
+          <t>はっきりした証拠 (chứng cứ rành rành rõ ràng)</t>
+        </is>
+      </c>
+      <c r="F301" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 236] = 明らかな.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="24" customHeight="1">
+      <c r="A302" s="5" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="6" t="inlineStr">
+        <is>
+          <t>用心</t>
+        </is>
+      </c>
+      <c r="C302" s="6" t="inlineStr">
+        <is>
+          <t>ようじん</t>
+        </is>
+      </c>
+      <c r="D302" s="7" t="inlineStr">
+        <is>
+          <t>Cẩn trọng, đề phòng, chú ý cẩn thận</t>
+        </is>
+      </c>
+      <c r="E302" s="7" t="inlineStr">
+        <is>
+          <t>できるだけ用心したほうがいい (nên cẩn trọng đề phòng hết mức có thể)</t>
+        </is>
+      </c>
+      <c r="F302" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 237] Đồng nghĩa với 注意.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="24" customHeight="1">
+      <c r="A303" s="5" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="6" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="C303" s="6" t="inlineStr">
+        <is>
+          <t>ちゅうい</t>
+        </is>
+      </c>
+      <c r="D303" s="7" t="inlineStr">
+        <is>
+          <t>Chú ý, cẩn thận, cảnh giác</t>
+        </is>
+      </c>
+      <c r="E303" s="7" t="inlineStr">
+        <is>
+          <t>足元に注意する (chú ý cẩn thận dưới chân)</t>
+        </is>
+      </c>
+      <c r="F303" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 237] = 用心.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="24" customHeight="1">
+      <c r="A304" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>努力</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>どりょく</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="inlineStr">
+        <is>
+          <t>Nỗ lực, cố gắng hết mình</t>
+        </is>
+      </c>
+      <c r="E304" s="4" t="inlineStr">
+        <is>
+          <t>目標に向かって努力する (nỗ lực hướng tới mục tiêu)</t>
+        </is>
+      </c>
+      <c r="F304" s="4" t="inlineStr">
+        <is>
+          <t>Cố gắng chăm chỉ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="24" customHeight="1">
+      <c r="A305" s="8" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="9" t="inlineStr">
+        <is>
+          <t>我慢</t>
+        </is>
+      </c>
+      <c r="C305" s="9" t="inlineStr">
+        <is>
+          <t>がまん</t>
+        </is>
+      </c>
+      <c r="D305" s="10" t="inlineStr">
+        <is>
+          <t>Chịu đựng, nhẫn nhịn</t>
+        </is>
+      </c>
+      <c r="E305" s="10" t="inlineStr">
+        <is>
+          <t>痛みを我慢する (cắn răng chịu đựng cơn đau)</t>
+        </is>
+      </c>
+      <c r="F305" s="10" t="inlineStr">
+        <is>
+          <t>Kìm nén cảm xúc/đau đớn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="24" customHeight="1">
+      <c r="A306" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>遠慮</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>えんりょ</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr">
+        <is>
+          <t>Khách khí, ngần ngại, kiêng dè</t>
+        </is>
+      </c>
+      <c r="E306" s="4" t="inlineStr">
+        <is>
+          <t>遠慮なく召し上がってください (xin đừng ngần ngại, hãy ăn tự nhiên)</t>
+        </is>
+      </c>
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>Khách sáo e dè.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="24" customHeight="1">
+      <c r="A307" s="5" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="6" t="inlineStr">
+        <is>
+          <t>騒々しい</t>
+        </is>
+      </c>
+      <c r="C307" s="6" t="inlineStr">
+        <is>
+          <t>そうぞうしい</t>
+        </is>
+      </c>
+      <c r="D307" s="7" t="inlineStr">
+        <is>
+          <t>Ồn ào, náo loạn, om sòm</t>
+        </is>
+      </c>
+      <c r="E307" s="7" t="inlineStr">
+        <is>
+          <t>会場が急にそうぞうしくなった (hội trường bỗng nhiên ồn ào náo loạn hẳn lên)</t>
+        </is>
+      </c>
+      <c r="F307" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 238] Đồng nghĩa với うるさい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="24" customHeight="1">
+      <c r="A308" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>暗い</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>くらい</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr">
+        <is>
+          <t>Tối tăm, u ám</t>
+        </is>
+      </c>
+      <c r="E308" s="4" t="inlineStr">
+        <is>
+          <t>部屋が暗い (căn phòng tối om)</t>
+        </is>
+      </c>
+      <c r="F308" s="4" t="inlineStr">
+        <is>
+          <t>Thiếu ánh sáng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="24" customHeight="1">
+      <c r="A309" s="8" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="9" t="inlineStr">
+        <is>
+          <t>静か</t>
+        </is>
+      </c>
+      <c r="C309" s="9" t="inlineStr">
+        <is>
+          <t>しずか</t>
+        </is>
+      </c>
+      <c r="D309" s="10" t="inlineStr">
+        <is>
+          <t>Yên tĩnh, thanh tịnh</t>
+        </is>
+      </c>
+      <c r="E309" s="10" t="inlineStr">
+        <is>
+          <t>静かな夜 (đêm thanh vắng)</t>
+        </is>
+      </c>
+      <c r="F309" s="10" t="inlineStr">
+        <is>
+          <t>Không có tiếng ồn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="24" customHeight="1">
+      <c r="A310" s="5" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="6" t="inlineStr">
+        <is>
+          <t>うるさい</t>
+        </is>
+      </c>
+      <c r="C310" s="6" t="inlineStr">
+        <is>
+          <t>うるさい</t>
+        </is>
+      </c>
+      <c r="D310" s="7" t="inlineStr">
+        <is>
+          <t>Ồn ào, làm phiền chói tai</t>
+        </is>
+      </c>
+      <c r="E310" s="7" t="inlineStr">
+        <is>
+          <t>工事の音がうるさい (tiếng công trường ồn ào inh ỏi)</t>
+        </is>
+      </c>
+      <c r="F310" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 238] = そうぞうしい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="24" customHeight="1">
+      <c r="A311" s="8" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="9" t="inlineStr">
+        <is>
+          <t>寒い</t>
+        </is>
+      </c>
+      <c r="C311" s="9" t="inlineStr">
+        <is>
+          <t>さむい</t>
+        </is>
+      </c>
+      <c r="D311" s="10" t="inlineStr">
+        <is>
+          <t>Lạnh lẽo (thời tiết)</t>
+        </is>
+      </c>
+      <c r="E311" s="10" t="inlineStr">
+        <is>
+          <t>外はとても寒い (bên ngoài trời rất lạnh)</t>
+        </is>
+      </c>
+      <c r="F311" s="10" t="inlineStr">
+        <is>
+          <t>Nhiệt độ không khí thấp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="24" customHeight="1">
+      <c r="A312" s="5" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="6" t="inlineStr">
+        <is>
+          <t>所有している</t>
+        </is>
+      </c>
+      <c r="C312" s="6" t="inlineStr">
+        <is>
+          <t>しょゆうしている</t>
+        </is>
+      </c>
+      <c r="D312" s="7" t="inlineStr">
+        <is>
+          <t>Sở hữu, có trong tay (tài sản)</t>
+        </is>
+      </c>
+      <c r="E312" s="7" t="inlineStr">
+        <is>
+          <t>店を所有している (nắm quyền sở hữu cửa tiệm)</t>
+        </is>
+      </c>
+      <c r="F312" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 239] Đồng nghĩa với 持っている.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="24" customHeight="1">
+      <c r="A313" s="8" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="9" t="inlineStr">
+        <is>
+          <t>探す</t>
+        </is>
+      </c>
+      <c r="C313" s="9" t="inlineStr">
+        <is>
+          <t>さがす</t>
+        </is>
+      </c>
+      <c r="D313" s="10" t="inlineStr">
+        <is>
+          <t>Tìm kiếm đồ vật/con người</t>
+        </is>
+      </c>
+      <c r="E313" s="10" t="inlineStr">
+        <is>
+          <t>鍵を探す (tìm chìa khóa)</t>
+        </is>
+      </c>
+      <c r="F313" s="10" t="inlineStr">
+        <is>
+          <t>Đi tìm vật bị mất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="24" customHeight="1">
+      <c r="A314" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>借りる</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>かりる</t>
+        </is>
+      </c>
+      <c r="D314" s="4" t="inlineStr">
+        <is>
+          <t>Vay mượn, thuê nhà</t>
+        </is>
+      </c>
+      <c r="E314" s="4" t="inlineStr">
+        <is>
+          <t>本を借りる (mượn sách)</t>
+        </is>
+      </c>
+      <c r="F314" s="4" t="inlineStr">
+        <is>
+          <t>Nhận dùng tạm rồi trả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="24" customHeight="1">
+      <c r="A315" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="6" t="inlineStr">
+        <is>
+          <t>持っている</t>
+        </is>
+      </c>
+      <c r="C315" s="6" t="inlineStr">
+        <is>
+          <t>もっている</t>
+        </is>
+      </c>
+      <c r="D315" s="7" t="inlineStr">
+        <is>
+          <t>Nắm giữ, sở hữu trong tay</t>
+        </is>
+      </c>
+      <c r="E315" s="7" t="inlineStr">
+        <is>
+          <t>自分の店を持っている (có quán của riêng mình)</t>
+        </is>
+      </c>
+      <c r="F315" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 239] = 所有している.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="24" customHeight="1">
+      <c r="A316" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>建てる</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>たてる</t>
+        </is>
+      </c>
+      <c r="D316" s="4" t="inlineStr">
+        <is>
+          <t>Xây dựng công trình</t>
+        </is>
+      </c>
+      <c r="E316" s="4" t="inlineStr">
+        <is>
+          <t>家を建てる (xây nhà)</t>
+        </is>
+      </c>
+      <c r="F316" s="4" t="inlineStr">
+        <is>
+          <t>Dựng lên nhà cửa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="24" customHeight="1">
+      <c r="A317" s="5" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="6" t="inlineStr">
+        <is>
+          <t>おそらく</t>
+        </is>
+      </c>
+      <c r="C317" s="6" t="inlineStr">
+        <is>
+          <t>おそらく</t>
+        </is>
+      </c>
+      <c r="D317" s="7" t="inlineStr">
+        <is>
+          <t>Có lẽ, chắc là (phỏng đoán có căn cứ)</t>
+        </is>
+      </c>
+      <c r="E317" s="7" t="inlineStr">
+        <is>
+          <t>おそらく来ないと思う (có lẽ anh ấy sẽ không đến đâu)</t>
+        </is>
+      </c>
+      <c r="F317" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 240] Đồng nghĩa với たぶん.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="24" customHeight="1">
+      <c r="A318" s="5" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" s="6" t="inlineStr">
+        <is>
+          <t>たぶん</t>
+        </is>
+      </c>
+      <c r="C318" s="6" t="inlineStr">
+        <is>
+          <t>たぶん</t>
+        </is>
+      </c>
+      <c r="D318" s="7" t="inlineStr">
+        <is>
+          <t>Có lẽ, có thể</t>
+        </is>
+      </c>
+      <c r="E318" s="7" t="inlineStr">
+        <is>
+          <t>たぶん雨が降るだろう (có lẽ trời sẽ mưa)</t>
+        </is>
+      </c>
+      <c r="F318" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 240] = おそらく.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="24" customHeight="1">
+      <c r="A319" s="8" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" s="9" t="inlineStr">
+        <is>
+          <t>当然</t>
+        </is>
+      </c>
+      <c r="C319" s="9" t="inlineStr">
+        <is>
+          <t>とうぜん</t>
+        </is>
+      </c>
+      <c r="D319" s="10" t="inlineStr">
+        <is>
+          <t>Đương nhiên, dĩ nhiên</t>
+        </is>
+      </c>
+      <c r="E319" s="10" t="inlineStr">
+        <is>
+          <t>合格して当然だ (đỗ là chuyện đương nhiên)</t>
+        </is>
+      </c>
+      <c r="F319" s="10" t="inlineStr">
+        <is>
+          <t>Hiển nhiên phải thế.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="24" customHeight="1">
+      <c r="A320" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>やはり</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>やはり</t>
+        </is>
+      </c>
+      <c r="D320" s="4" t="inlineStr">
+        <is>
+          <t>Quả nhiên đúng như dự đoán</t>
+        </is>
+      </c>
+      <c r="E320" s="4" t="inlineStr">
+        <is>
+          <t>やはり彼が勝った (quả nhiên anh ấy đã thắng)</t>
+        </is>
+      </c>
+      <c r="F320" s="4" t="inlineStr">
+        <is>
+          <t>Đúng như linh tính/dự liệu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="24" customHeight="1">
+      <c r="A321" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" s="9" t="inlineStr">
+        <is>
+          <t>絶対</t>
+        </is>
+      </c>
+      <c r="C321" s="9" t="inlineStr">
+        <is>
+          <t>ぜったい</t>
+        </is>
+      </c>
+      <c r="D321" s="10" t="inlineStr">
+        <is>
+          <t>Tuyệt đối, nhất định 100%</t>
+        </is>
+      </c>
+      <c r="E321" s="10" t="inlineStr">
+        <is>
+          <t>絶対に諦めない (tuyệt đối không bỏ cuộc)</t>
+        </is>
+      </c>
+      <c r="F321" s="10" t="inlineStr">
+        <is>
+          <t>Khẳng định chắc chắn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="24" customHeight="1">
+      <c r="A322" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
+        <is>
+          <t>収納する</t>
+        </is>
+      </c>
+      <c r="C322" s="6" t="inlineStr">
+        <is>
+          <t>しゅうのうする</t>
+        </is>
+      </c>
+      <c r="D322" s="7" t="inlineStr">
+        <is>
+          <t>Cất gọn, xếp gọn vào ngăn nắp</t>
+        </is>
+      </c>
+      <c r="E322" s="7" t="inlineStr">
+        <is>
+          <t>収納していない物がたくさんある (còn nhiều đồ đạc chưa được cất gọn ghẽ)</t>
+        </is>
+      </c>
+      <c r="F322" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 241] Đồng nghĩa với しまう.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="24" customHeight="1">
+      <c r="A323" s="8" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" s="9" t="inlineStr">
+        <is>
+          <t>集める</t>
+        </is>
+      </c>
+      <c r="C323" s="9" t="inlineStr">
+        <is>
+          <t>あつめる</t>
+        </is>
+      </c>
+      <c r="D323" s="10" t="inlineStr">
+        <is>
+          <t>Gom lại, thu thập</t>
+        </is>
+      </c>
+      <c r="E323" s="10" t="inlineStr">
+        <is>
+          <t>切手を集める (sưu tầm tem)</t>
+        </is>
+      </c>
+      <c r="F323" s="10" t="inlineStr">
+        <is>
+          <t>Gom nhiều thứ về một chỗ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="24" customHeight="1">
+      <c r="A324" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>預ける</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>あずける</t>
+        </is>
+      </c>
+      <c r="D324" s="4" t="inlineStr">
+        <is>
+          <t>Gửi đồ, giao phó tiền/con trẻ</t>
+        </is>
+      </c>
+      <c r="E324" s="4" t="inlineStr">
+        <is>
+          <t>荷物をロッカーに預ける (gửi hành lý vào tủ khóa)</t>
+        </is>
+      </c>
+      <c r="F324" s="4" t="inlineStr">
+        <is>
+          <t>Nhờ người khác trông nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="24" customHeight="1">
+      <c r="A325" s="8" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" s="9" t="inlineStr">
+        <is>
+          <t>返す</t>
+        </is>
+      </c>
+      <c r="C325" s="9" t="inlineStr">
+        <is>
+          <t>かえす</t>
+        </is>
+      </c>
+      <c r="D325" s="10" t="inlineStr">
+        <is>
+          <t>Trả lại đồ vật</t>
+        </is>
+      </c>
+      <c r="E325" s="10" t="inlineStr">
+        <is>
+          <t>借りた本を返す (trả lại cuốn sách đã mượn)</t>
+        </is>
+      </c>
+      <c r="F325" s="10" t="inlineStr">
+        <is>
+          <t>Đem hoàn trả chủ cũ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="24" customHeight="1">
+      <c r="A326" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" s="6" t="inlineStr">
+        <is>
+          <t>しまう</t>
+        </is>
+      </c>
+      <c r="C326" s="6" t="inlineStr">
+        <is>
+          <t>しまう</t>
+        </is>
+      </c>
+      <c r="D326" s="7" t="inlineStr">
+        <is>
+          <t>Cất vào trong tủ/hộp ngăn nắp</t>
+        </is>
+      </c>
+      <c r="E326" s="7" t="inlineStr">
+        <is>
+          <t>服をクローゼットにしまう (cất quần áo gọn gàng vào tủ)</t>
+        </is>
+      </c>
+      <c r="F326" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 241] = 収納する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="24" customHeight="1">
+      <c r="A327" s="5" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" s="6" t="inlineStr">
+        <is>
+          <t>小柄</t>
+        </is>
+      </c>
+      <c r="C327" s="6" t="inlineStr">
+        <is>
+          <t>こがら</t>
+        </is>
+      </c>
+      <c r="D327" s="7" t="inlineStr">
+        <is>
+          <t>Vóc dáng nhỏ nhắn, người bé</t>
+        </is>
+      </c>
+      <c r="E327" s="7" t="inlineStr">
+        <is>
+          <t>母に似て小柄だ (dáng người nhỏ nhắn giống mẹ)</t>
+        </is>
+      </c>
+      <c r="F327" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 242] Đồng nghĩa với 体が小さい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="24" customHeight="1">
+      <c r="A328" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>声が小さい</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>こえがちいさい</t>
+        </is>
+      </c>
+      <c r="D328" s="4" t="inlineStr">
+        <is>
+          <t>Giọng nói nhỏ nhẹ</t>
+        </is>
+      </c>
+      <c r="E328" s="4" t="inlineStr">
+        <is>
+          <t>声が小さくて聞こえない (giọng lí nhí không nghe thấy gì)</t>
+        </is>
+      </c>
+      <c r="F328" s="4" t="inlineStr">
+        <is>
+          <t>Âm lượng bé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="24" customHeight="1">
+      <c r="A329" s="8" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="9" t="inlineStr">
+        <is>
+          <t>力が弱い</t>
+        </is>
+      </c>
+      <c r="C329" s="9" t="inlineStr">
+        <is>
+          <t>ちからがよわい</t>
+        </is>
+      </c>
+      <c r="D329" s="10" t="inlineStr">
+        <is>
+          <t>Sức lực yếu ớt</t>
+        </is>
+      </c>
+      <c r="E329" s="10" t="inlineStr">
+        <is>
+          <t>腕の力が弱い (lực cánh tay yếu)</t>
+        </is>
+      </c>
+      <c r="F329" s="10" t="inlineStr">
+        <is>
+          <t>Không có cơ bắp/thể lực.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="24" customHeight="1">
+      <c r="A330" s="5" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t>体が小さい</t>
+        </is>
+      </c>
+      <c r="C330" s="6" t="inlineStr">
+        <is>
+          <t>からだがちいさい</t>
+        </is>
+      </c>
+      <c r="D330" s="7" t="inlineStr">
+        <is>
+          <t>Thân hình nhỏ nhắn</t>
+        </is>
+      </c>
+      <c r="E330" s="7" t="inlineStr">
+        <is>
+          <t>体が小さくてすばしっこい (người nhỏ nhắn mà thoăn thoắt)</t>
+        </is>
+      </c>
+      <c r="F330" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 242] = 小柄.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="24" customHeight="1">
+      <c r="A331" s="8" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" s="9" t="inlineStr">
+        <is>
+          <t>心が弱い</t>
+        </is>
+      </c>
+      <c r="C331" s="9" t="inlineStr">
+        <is>
+          <t>こころがよわい</t>
+        </is>
+      </c>
+      <c r="D331" s="10" t="inlineStr">
+        <is>
+          <t>Tâm hồn mềm yếu, dễ nản lòng</t>
+        </is>
+      </c>
+      <c r="E331" s="10" t="inlineStr">
+        <is>
+          <t>心が弱くてくじけやすい (tâm lý yếu dễ nản chí)</t>
+        </is>
+      </c>
+      <c r="F331" s="10" t="inlineStr">
+        <is>
+          <t>Dễ bị tổn thương.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="24" customHeight="1">
+      <c r="A332" s="5" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" s="6" t="inlineStr">
+        <is>
+          <t>無口</t>
+        </is>
+      </c>
+      <c r="C332" s="6" t="inlineStr">
+        <is>
+          <t>むくち</t>
+        </is>
+      </c>
+      <c r="D332" s="7" t="inlineStr">
+        <is>
+          <t>Kiệm lời, ít nói, trầm ngâm</t>
+        </is>
+      </c>
+      <c r="E332" s="7" t="inlineStr">
+        <is>
+          <t>鈴木さんは無口な性格だ (anh Suzuki là người trầm tính ít nói)</t>
+        </is>
+      </c>
+      <c r="F332" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 243] Đồng nghĩa với あまり話さない.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="24" customHeight="1">
+      <c r="A333" s="8" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" s="9" t="inlineStr">
+        <is>
+          <t>あまり笑わない</t>
+        </is>
+      </c>
+      <c r="C333" s="9" t="inlineStr">
+        <is>
+          <t>あまりわらわない</t>
+        </is>
+      </c>
+      <c r="D333" s="10" t="inlineStr">
+        <is>
+          <t>Ít khi cười đùa</t>
+        </is>
+      </c>
+      <c r="E333" s="10" t="inlineStr">
+        <is>
+          <t>彼は真面目で滅多に笑わない (anh ấy nghiêm túc hiếm khi cười)</t>
+        </is>
+      </c>
+      <c r="F333" s="10" t="inlineStr">
+        <is>
+          <t>Khuôn mặt lạnh lùng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="24" customHeight="1">
+      <c r="A334" s="5" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" s="6" t="inlineStr">
+        <is>
+          <t>あまり話さない</t>
+        </is>
+      </c>
+      <c r="C334" s="6" t="inlineStr">
+        <is>
+          <t>あまりはなさない</t>
+        </is>
+      </c>
+      <c r="D334" s="7" t="inlineStr">
+        <is>
+          <t>Ít trò chuyện, không hay nói</t>
+        </is>
+      </c>
+      <c r="E334" s="7" t="inlineStr">
+        <is>
+          <t>普段はあまり話さない (bình thường rất ít khi nói chuyện)</t>
+        </is>
+      </c>
+      <c r="F334" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 243] = 無口.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="24" customHeight="1">
+      <c r="A335" s="8" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" s="9" t="inlineStr">
+        <is>
+          <t>あまり思わない</t>
+        </is>
+      </c>
+      <c r="C335" s="9" t="inlineStr">
+        <is>
+          <t>あまりおもわない</t>
+        </is>
+      </c>
+      <c r="D335" s="10" t="inlineStr">
+        <is>
+          <t>Không nghĩ ngợi nhiều</t>
+        </is>
+      </c>
+      <c r="E335" s="10" t="inlineStr">
+        <is>
+          <t>そうはあまり思わない (tôi không nghĩ như thế cho lắm)</t>
+        </is>
+      </c>
+      <c r="F335" s="10" t="inlineStr">
+        <is>
+          <t>Không có quan điểm mạnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="24" customHeight="1">
+      <c r="A336" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>あまり食べない</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>あまりたべない</t>
+        </is>
+      </c>
+      <c r="D336" s="4" t="inlineStr">
+        <is>
+          <t>Ăn ít, kén ăn</t>
+        </is>
+      </c>
+      <c r="E336" s="4" t="inlineStr">
+        <is>
+          <t>小食であまり食べない (ăn như mèo ngửi, ăn rất ít)</t>
+        </is>
+      </c>
+      <c r="F336" s="4" t="inlineStr">
+        <is>
+          <t>Lượng thức ăn nạp vào ít.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="24" customHeight="1">
+      <c r="A337" s="5" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" s="6" t="inlineStr">
+        <is>
+          <t>やや</t>
+        </is>
+      </c>
+      <c r="C337" s="6" t="inlineStr">
+        <is>
+          <t>やや</t>
+        </is>
+      </c>
+      <c r="D337" s="7" t="inlineStr">
+        <is>
+          <t>Một chút, hơi hơi, đôi chút</t>
+        </is>
+      </c>
+      <c r="E337" s="7" t="inlineStr">
+        <is>
+          <t>今日よりやや涼しくなる (trời sẽ se lạnh hơn một chút so với hôm nay)</t>
+        </is>
+      </c>
+      <c r="F337" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 244] Đồng nghĩa với 少し.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="24" customHeight="1">
+      <c r="A338" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>もっと</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>もっと</t>
+        </is>
+      </c>
+      <c r="D338" s="4" t="inlineStr">
+        <is>
+          <t>Hơn nữa, nhiều hơn nữa</t>
+        </is>
+      </c>
+      <c r="E338" s="4" t="inlineStr">
+        <is>
+          <t>もっと勉強しなさい (hãy học chăm hơn nữa)</t>
+        </is>
+      </c>
+      <c r="F338" s="4" t="inlineStr">
+        <is>
+          <t>Mức độ tăng thêm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="24" customHeight="1">
+      <c r="A339" s="5" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" s="6" t="inlineStr">
+        <is>
+          <t>少し</t>
+        </is>
+      </c>
+      <c r="C339" s="6" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="D339" s="7" t="inlineStr">
+        <is>
+          <t>Một chút, một ít</t>
+        </is>
+      </c>
+      <c r="E339" s="7" t="inlineStr">
+        <is>
+          <t>少し休もう (nghỉ ngơi một chút nào)</t>
+        </is>
+      </c>
+      <c r="F339" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 244] = やや.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="24" customHeight="1">
+      <c r="A340" s="5" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" s="6" t="inlineStr">
+        <is>
+          <t>テンポ</t>
+        </is>
+      </c>
+      <c r="C340" s="6" t="inlineStr">
+        <is>
+          <t>テンポ</t>
+        </is>
+      </c>
+      <c r="D340" s="7" t="inlineStr">
+        <is>
+          <t>Tốc độ, nhịp độ bài hát/công việc</t>
+        </is>
+      </c>
+      <c r="E340" s="7" t="inlineStr">
+        <is>
+          <t>テンポの速い曲 (bài hát có tiết tấu nhanh)</t>
+        </is>
+      </c>
+      <c r="F340" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 245] Đồng nghĩa với 速さ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="24" customHeight="1">
+      <c r="A341" s="5" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" s="6" t="inlineStr">
+        <is>
+          <t>速さ</t>
+        </is>
+      </c>
+      <c r="C341" s="6" t="inlineStr">
+        <is>
+          <t>はやさ</t>
+        </is>
+      </c>
+      <c r="D341" s="7" t="inlineStr">
+        <is>
+          <t>Tốc độ, độ nhanh</t>
+        </is>
+      </c>
+      <c r="E341" s="7" t="inlineStr">
+        <is>
+          <t>走る速さを競う (thi thố tốc độ chạy)</t>
+        </is>
+      </c>
+      <c r="F341" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 245] = テンポ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="24" customHeight="1">
+      <c r="A342" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>長さ</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="inlineStr">
+        <is>
+          <t>ながさ</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="inlineStr">
+        <is>
+          <t>Độ dài kích thước/thời gian</t>
+        </is>
+      </c>
+      <c r="E342" s="4" t="inlineStr">
+        <is>
+          <t>スカートの長さを調節する (chỉnh độ dài chiếc váy)</t>
+        </is>
+      </c>
+      <c r="F342" s="4" t="inlineStr">
+        <is>
+          <t>Chiều dài centimet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="24" customHeight="1">
+      <c r="A343" s="8" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" s="9" t="inlineStr">
+        <is>
+          <t>高さ</t>
+        </is>
+      </c>
+      <c r="C343" s="9" t="inlineStr">
+        <is>
+          <t>たかさ</t>
+        </is>
+      </c>
+      <c r="D343" s="10" t="inlineStr">
+        <is>
+          <t>Chiều cao, độ cao</t>
+        </is>
+      </c>
+      <c r="E343" s="10" t="inlineStr">
+        <is>
+          <t>山の高さを測る (đo độ cao của ngọn núi)</t>
+        </is>
+      </c>
+      <c r="F343" s="10" t="inlineStr">
+        <is>
+          <t>Khoảng cách thẳng đứng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="24" customHeight="1">
+      <c r="A344" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>明るさ</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="inlineStr">
+        <is>
+          <t>あかるさ</t>
+        </is>
+      </c>
+      <c r="D344" s="4" t="inlineStr">
+        <is>
+          <t>Độ sáng sủa; tính vui vẻ</t>
+        </is>
+      </c>
+      <c r="E344" s="4" t="inlineStr">
+        <is>
+          <t>部屋の明るさを調節する (chỉnh độ sáng căn phòng)</t>
+        </is>
+      </c>
+      <c r="F344" s="4" t="inlineStr">
+        <is>
+          <t>Ánh sáng hoặc tính cách rạng rỡ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="24" customHeight="1">
+      <c r="A345" s="5" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" s="6" t="inlineStr">
+        <is>
+          <t>妙な</t>
+        </is>
+      </c>
+      <c r="C345" s="6" t="inlineStr">
+        <is>
+          <t>みょうな</t>
+        </is>
+      </c>
+      <c r="D345" s="7" t="inlineStr">
+        <is>
+          <t>Kỳ lạ, kỳ quặc, khác thường</t>
+        </is>
+      </c>
+      <c r="E345" s="7" t="inlineStr">
+        <is>
+          <t>妙な噂を耳にする (nghe thấy tin đồn kỳ lạ quái gở)</t>
+        </is>
+      </c>
+      <c r="F345" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 246] Đồng nghĩa với 変な.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="24" customHeight="1">
+      <c r="A346" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>うれしい</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>うれしい</t>
+        </is>
+      </c>
+      <c r="D346" s="4" t="inlineStr">
+        <is>
+          <t>Vui mừng, sung sướng</t>
+        </is>
+      </c>
+      <c r="E346" s="4" t="inlineStr">
+        <is>
+          <t>合格できて本当にうれしい (được đỗ thấy thật sung sướng)</t>
+        </is>
+      </c>
+      <c r="F346" s="4" t="inlineStr">
+        <is>
+          <t>Cảm xúc hân hoan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="24" customHeight="1">
+      <c r="A347" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" s="6" t="inlineStr">
+        <is>
+          <t>変な</t>
+        </is>
+      </c>
+      <c r="C347" s="6" t="inlineStr">
+        <is>
+          <t>へんな</t>
+        </is>
+      </c>
+      <c r="D347" s="7" t="inlineStr">
+        <is>
+          <t>Kỳ lạ, quái dị, bất thường</t>
+        </is>
+      </c>
+      <c r="E347" s="7" t="inlineStr">
+        <is>
+          <t>変な音が聞こえる (nghe thấy âm thanh quái lạ)</t>
+        </is>
+      </c>
+      <c r="F347" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 246] = 妙な.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="24" customHeight="1">
+      <c r="A348" s="2" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>嫌な</t>
+        </is>
+      </c>
+      <c r="C348" s="3" t="inlineStr">
+        <is>
+          <t>いやな</t>
+        </is>
+      </c>
+      <c r="D348" s="4" t="inlineStr">
+        <is>
+          <t>Khó chịu, ghét bỏ</t>
+        </is>
+      </c>
+      <c r="E348" s="4" t="inlineStr">
+        <is>
+          <t>嫌な予感がする (có dự cảm chẳng lành)</t>
+        </is>
+      </c>
+      <c r="F348" s="4" t="inlineStr">
+        <is>
+          <t>Cảm giác không thích thú.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="24" customHeight="1">
+      <c r="A349" s="5" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" s="6" t="inlineStr">
+        <is>
+          <t>ささやく</t>
+        </is>
+      </c>
+      <c r="C349" s="6" t="inlineStr">
+        <is>
+          <t>ささやく</t>
+        </is>
+      </c>
+      <c r="D349" s="7" t="inlineStr">
+        <is>
+          <t>Thì thầm, nói nhỏ nhẹ bên tai</t>
+        </is>
+      </c>
+      <c r="E349" s="7" t="inlineStr">
+        <is>
+          <t>耳元で愛をささやく (thì thầm lời yêu bên vành tai)</t>
+        </is>
+      </c>
+      <c r="F349" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 247] Đồng nghĩa với 小声で話す.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="24" customHeight="1">
+      <c r="A350" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>急いで</t>
+        </is>
+      </c>
+      <c r="C350" s="3" t="inlineStr">
+        <is>
+          <t>いそいで</t>
+        </is>
+      </c>
+      <c r="D350" s="4" t="inlineStr">
+        <is>
+          <t>Vội vã, gấp gáp</t>
+        </is>
+      </c>
+      <c r="E350" s="4" t="inlineStr">
+        <is>
+          <t>急いで家を出る (vội vàng rời khỏi nhà)</t>
+        </is>
+      </c>
+      <c r="F350" s="4" t="inlineStr">
+        <is>
+          <t>Hành động nhanh chóng do gấp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="24" customHeight="1">
+      <c r="A351" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" s="9" t="inlineStr">
+        <is>
+          <t>ゆっくり</t>
+        </is>
+      </c>
+      <c r="C351" s="9" t="inlineStr">
+        <is>
+          <t>ゆっくり</t>
+        </is>
+      </c>
+      <c r="D351" s="10" t="inlineStr">
+        <is>
+          <t>Chậm rãi, từ tốn</t>
+        </is>
+      </c>
+      <c r="E351" s="10" t="inlineStr">
+        <is>
+          <t>ゆっくり話してください (xin hãy nói chậm rãi)</t>
+        </is>
+      </c>
+      <c r="F351" s="10" t="inlineStr">
+        <is>
+          <t>Tốc độ thong dong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="24" customHeight="1">
+      <c r="A352" s="2" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>大声で</t>
+        </is>
+      </c>
+      <c r="C352" s="3" t="inlineStr">
+        <is>
+          <t>おおごえで</t>
+        </is>
+      </c>
+      <c r="D352" s="4" t="inlineStr">
+        <is>
+          <t>Bằng giọng lớn, hét to</t>
+        </is>
+      </c>
+      <c r="E352" s="4" t="inlineStr">
+        <is>
+          <t>大声で助けを呼ぶ (hét lớn kêu cứu)</t>
+        </is>
+      </c>
+      <c r="F352" s="4" t="inlineStr">
+        <is>
+          <t>Âm lượng cực lớn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="24" customHeight="1">
+      <c r="A353" s="5" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" s="6" t="inlineStr">
+        <is>
+          <t>小声で</t>
+        </is>
+      </c>
+      <c r="C353" s="6" t="inlineStr">
+        <is>
+          <t>こごえで</t>
+        </is>
+      </c>
+      <c r="D353" s="7" t="inlineStr">
+        <is>
+          <t>Bằng giọng nhỏ, thì thào</t>
+        </is>
+      </c>
+      <c r="E353" s="7" t="inlineStr">
+        <is>
+          <t>小声で相談する (bàn bạc thì thào với nhau)</t>
+        </is>
+      </c>
+      <c r="F353" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 247] = ささやく.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="24" customHeight="1">
+      <c r="A354" s="5" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" s="6" t="inlineStr">
+        <is>
+          <t>かつて</t>
+        </is>
+      </c>
+      <c r="C354" s="6" t="inlineStr">
+        <is>
+          <t>かつて</t>
+        </is>
+      </c>
+      <c r="D354" s="7" t="inlineStr">
+        <is>
+          <t>Trước đây, xưa kia, từng có một thời</t>
+        </is>
+      </c>
+      <c r="E354" s="7" t="inlineStr">
+        <is>
+          <t>かつてフランスに住んでいた (ngày trước tôi từng sống ở Pháp)</t>
+        </is>
+      </c>
+      <c r="F354" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 248] Đồng nghĩa với 以前.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="24" customHeight="1">
+      <c r="A355" s="8" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" s="9" t="inlineStr">
+        <is>
+          <t>確か</t>
+        </is>
+      </c>
+      <c r="C355" s="9" t="inlineStr">
+        <is>
+          <t>たしか</t>
+        </is>
+      </c>
+      <c r="D355" s="10" t="inlineStr">
+        <is>
+          <t>Chắc chắn, chính xác</t>
+        </is>
+      </c>
+      <c r="E355" s="10" t="inlineStr">
+        <is>
+          <t>確か昨日のことだ (chắc chắn là chuyện ngày hôm qua)</t>
+        </is>
+      </c>
+      <c r="F355" s="10" t="inlineStr">
+        <is>
+          <t>Nhớ mang máng nhưng khá chắc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="24" customHeight="1">
+      <c r="A356" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>主に</t>
+        </is>
+      </c>
+      <c r="C356" s="3" t="inlineStr">
+        <is>
+          <t>おもに</t>
+        </is>
+      </c>
+      <c r="D356" s="4" t="inlineStr">
+        <is>
+          <t>Chủ yếu, phần lớn</t>
+        </is>
+      </c>
+      <c r="E356" s="4" t="inlineStr">
+        <is>
+          <t>主にお米を主食としている (chủ yếu lấy gạo làm thức ăn chính)</t>
+        </is>
+      </c>
+      <c r="F356" s="4" t="inlineStr">
+        <is>
+          <t>Bộ phận nòng cốt chiếm đa số.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="24" customHeight="1">
+      <c r="A357" s="5" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" s="6" t="inlineStr">
+        <is>
+          <t>以前</t>
+        </is>
+      </c>
+      <c r="C357" s="6" t="inlineStr">
+        <is>
+          <t>いぜん</t>
+        </is>
+      </c>
+      <c r="D357" s="7" t="inlineStr">
+        <is>
+          <t>Trước đây, ngày trước</t>
+        </is>
+      </c>
+      <c r="E357" s="7" t="inlineStr">
+        <is>
+          <t>以前お会いしたことがあります (ngày trước tôi đã từng có dịp gặp bác)</t>
+        </is>
+      </c>
+      <c r="F357" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 248] = かつて.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="24" customHeight="1">
+      <c r="A358" s="2" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>しばらく</t>
+        </is>
+      </c>
+      <c r="C358" s="3" t="inlineStr">
+        <is>
+          <t>しばらく</t>
+        </is>
+      </c>
+      <c r="D358" s="4" t="inlineStr">
+        <is>
+          <t>Một thời gian, một lúc</t>
+        </is>
+      </c>
+      <c r="E358" s="4" t="inlineStr">
+        <is>
+          <t>しばらくお待ちください (xin vui lòng đợi trong giây lát)</t>
+        </is>
+      </c>
+      <c r="F358" s="4" t="inlineStr">
+        <is>
+          <t>Khoảng thời gian ngắn/dài tùy ngữ cảnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="24" customHeight="1">
+      <c r="A359" s="5" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" s="6" t="inlineStr">
+        <is>
+          <t>たびたび</t>
+        </is>
+      </c>
+      <c r="C359" s="6" t="inlineStr">
+        <is>
+          <t>たびたび</t>
+        </is>
+      </c>
+      <c r="D359" s="7" t="inlineStr">
+        <is>
+          <t>Thường xuyên, lặp đi lặp lại nhiều lần</t>
+        </is>
+      </c>
+      <c r="E359" s="7" t="inlineStr">
+        <is>
+          <t>たびたび注意される (thường xuyên bị nhắc nhở nhiều lần)</t>
+        </is>
+      </c>
+      <c r="F359" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 249] Đồng nghĩa với 何度も.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="24" customHeight="1">
+      <c r="A360" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>必ず</t>
+        </is>
+      </c>
+      <c r="C360" s="3" t="inlineStr">
+        <is>
+          <t>かならず</t>
+        </is>
+      </c>
+      <c r="D360" s="4" t="inlineStr">
+        <is>
+          <t>Nhất định, chắc chắn phải làm</t>
+        </is>
+      </c>
+      <c r="E360" s="4" t="inlineStr">
+        <is>
+          <t>必ず約束を守る (nhất định giữ đúng lời hứa)</t>
+        </is>
+      </c>
+      <c r="F360" s="4" t="inlineStr">
+        <is>
+          <t>Khẳng định tuyệt đối 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="24" customHeight="1">
+      <c r="A361" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" s="9" t="inlineStr">
+        <is>
+          <t>ようやく</t>
+        </is>
+      </c>
+      <c r="C361" s="9" t="inlineStr">
+        <is>
+          <t>ようやく</t>
+        </is>
+      </c>
+      <c r="D361" s="10" t="inlineStr">
+        <is>
+          <t>Cuối cùng thì cũng (sau nhiều trắc trở)</t>
+        </is>
+      </c>
+      <c r="E361" s="10" t="inlineStr">
+        <is>
+          <t>ようやく夢が叶った (cuối cùng ước mơ cũng thành hiện thực)</t>
+        </is>
+      </c>
+      <c r="F361" s="10" t="inlineStr">
+        <is>
+          <t>Sau một quá trình gian nan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="24" customHeight="1">
+      <c r="A362" s="5" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" s="6" t="inlineStr">
+        <is>
+          <t>何度も</t>
+        </is>
+      </c>
+      <c r="C362" s="6" t="inlineStr">
+        <is>
+          <t>なんども</t>
+        </is>
+      </c>
+      <c r="D362" s="7" t="inlineStr">
+        <is>
+          <t>Nhiều lần</t>
+        </is>
+      </c>
+      <c r="E362" s="7" t="inlineStr">
+        <is>
+          <t>何度も復習する (ôn tập đi ôn tập lại nhiều lần)</t>
+        </is>
+      </c>
+      <c r="F362" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 249] = たびたび.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="24" customHeight="1">
+      <c r="A363" s="5" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" s="6" t="inlineStr">
+        <is>
+          <t>注目した</t>
+        </is>
+      </c>
+      <c r="C363" s="6" t="inlineStr">
+        <is>
+          <t>ちゅうもくした</t>
+        </is>
+      </c>
+      <c r="D363" s="7" t="inlineStr">
+        <is>
+          <t>Chú mục, hướng sự chú ý quan tâm vào</t>
+        </is>
+      </c>
+      <c r="E363" s="7" t="inlineStr">
+        <is>
+          <t>発言に皆が注目した (mọi người đều đổ dồn sự chú ý vào lời phát biểu)</t>
+        </is>
+      </c>
+      <c r="F363" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 250] Đồng nghĩa với 関心を持った.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="24" customHeight="1">
+      <c r="A364" s="5" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" s="6" t="inlineStr">
+        <is>
+          <t>関心を持った</t>
+        </is>
+      </c>
+      <c r="C364" s="6" t="inlineStr">
+        <is>
+          <t>かんしんをもった</t>
+        </is>
+      </c>
+      <c r="D364" s="7" t="inlineStr">
+        <is>
+          <t>Có sự quan tâm, để ý đến</t>
+        </is>
+      </c>
+      <c r="E364" s="7" t="inlineStr">
+        <is>
+          <t>環境問題に関心を持つ (quan tâm tới các vấn đề môi trường)</t>
+        </is>
+      </c>
+      <c r="F364" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 250] = 注目する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="24" customHeight="1">
+      <c r="A365" s="8" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" s="9" t="inlineStr">
+        <is>
+          <t>疑問を持った</t>
+        </is>
+      </c>
+      <c r="C365" s="9" t="inlineStr">
+        <is>
+          <t>ぎもんをもった</t>
+        </is>
+      </c>
+      <c r="D365" s="10" t="inlineStr">
+        <is>
+          <t>Nảy sinh mối nghi hoặc, thắc mắc</t>
+        </is>
+      </c>
+      <c r="E365" s="10" t="inlineStr">
+        <is>
+          <t>彼の行動に疑問を持つ (nảy sinh nghi ngờ đối với hành động của anh ấy)</t>
+        </is>
+      </c>
+      <c r="F365" s="10" t="inlineStr">
+        <is>
+          <t>Có câu hỏi chất vấn trong lòng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="24" customHeight="1">
+      <c r="A366" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>感動した</t>
+        </is>
+      </c>
+      <c r="C366" s="3" t="inlineStr">
+        <is>
+          <t>かんどうした</t>
+        </is>
+      </c>
+      <c r="D366" s="4" t="inlineStr">
+        <is>
+          <t>Xúc động, rung động tâm can</t>
+        </is>
+      </c>
+      <c r="E366" s="4" t="inlineStr">
+        <is>
+          <t>素晴らしい映画に深く感動した (vô cùng xúc động trước bộ phim hay)</t>
+        </is>
+      </c>
+      <c r="F366" s="4" t="inlineStr">
+        <is>
+          <t>Rung động cảm xúc mãnh liệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="24" customHeight="1">
+      <c r="A367" s="8" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" s="9" t="inlineStr">
+        <is>
+          <t>驚いた</t>
+        </is>
+      </c>
+      <c r="C367" s="9" t="inlineStr">
+        <is>
+          <t>おどろいた</t>
+        </is>
+      </c>
+      <c r="D367" s="10" t="inlineStr">
+        <is>
+          <t>Kinh ngạc, giật mình ngạc nhiên</t>
+        </is>
+      </c>
+      <c r="E367" s="10" t="inlineStr">
+        <is>
+          <t>突然の知らせに大変驚いた (vô cùng kinh ngạc trước tin báo đột ngột)</t>
+        </is>
+      </c>
+      <c r="F367" s="10" t="inlineStr">
+        <is>
+          <t>Bị bất ngờ ngoài dự liệu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="24" customHeight="1">
+      <c r="A368" s="5" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" s="6" t="inlineStr">
+        <is>
+          <t>じかに</t>
+        </is>
+      </c>
+      <c r="C368" s="6" t="inlineStr">
+        <is>
+          <t>じかに (直に)</t>
+        </is>
+      </c>
+      <c r="D368" s="7" t="inlineStr">
+        <is>
+          <t>Trực tiếp mặt đối mặt, không qua trung gian</t>
+        </is>
+      </c>
+      <c r="E368" s="7" t="inlineStr">
+        <is>
+          <t>本人にじかに伝える (truyền đạt trực tiếp tới tận tay người đó)</t>
+        </is>
+      </c>
+      <c r="F368" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 251] Đồng nghĩa với 直接.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="24" customHeight="1">
+      <c r="A369" s="5" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" s="6" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="C369" s="6" t="inlineStr">
+        <is>
+          <t>ちょくせつ</t>
+        </is>
+      </c>
+      <c r="D369" s="7" t="inlineStr">
+        <is>
+          <t>Trực tiếp</t>
+        </is>
+      </c>
+      <c r="E369" s="7" t="inlineStr">
+        <is>
+          <t>直接会って話す (gặp gỡ trực tiếp để nói chuyện)</t>
+        </is>
+      </c>
+      <c r="F369" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 251] = じかに.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="24" customHeight="1">
+      <c r="A370" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t>あとで</t>
+        </is>
+      </c>
+      <c r="C370" s="3" t="inlineStr">
+        <is>
+          <t>あとで</t>
+        </is>
+      </c>
+      <c r="D370" s="4" t="inlineStr">
+        <is>
+          <t>Lát sau, để sau</t>
+        </is>
+      </c>
+      <c r="E370" s="4" t="inlineStr">
+        <is>
+          <t>あとで連絡します (tôi sẽ liên lạc lại sau nhé)</t>
+        </is>
+      </c>
+      <c r="F370" s="4" t="inlineStr">
+        <is>
+          <t>Thời điểm lùi lại phía sau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="24" customHeight="1">
+      <c r="A371" s="8" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" s="9" t="inlineStr">
+        <is>
+          <t>すべて</t>
+        </is>
+      </c>
+      <c r="C371" s="9" t="inlineStr">
+        <is>
+          <t>すべて</t>
+        </is>
+      </c>
+      <c r="D371" s="10" t="inlineStr">
+        <is>
+          <t>Tất cả toàn bộ mọi thứ</t>
+        </is>
+      </c>
+      <c r="E371" s="10" t="inlineStr">
+        <is>
+          <t>すべて順調に進んでいる (mọi thứ đều đang tiến triển suôn sẻ)</t>
+        </is>
+      </c>
+      <c r="F371" s="10" t="inlineStr">
+        <is>
+          <t>Không chừa cái gì.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="24" customHeight="1">
+      <c r="A372" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>確実に</t>
+        </is>
+      </c>
+      <c r="C372" s="3" t="inlineStr">
+        <is>
+          <t>かくじつに</t>
+        </is>
+      </c>
+      <c r="D372" s="4" t="inlineStr">
+        <is>
+          <t>Một cách chắc chắn, không sai lệch</t>
+        </is>
+      </c>
+      <c r="E372" s="4" t="inlineStr">
+        <is>
+          <t>確実に成功させる (chắc chắn sẽ làm cho thành công)</t>
+        </is>
+      </c>
+      <c r="F372" s="4" t="inlineStr">
+        <is>
+          <t>Độ tin cậy 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="24" customHeight="1">
+      <c r="A373" s="5" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" s="6" t="inlineStr">
+        <is>
+          <t>衝突する</t>
+        </is>
+      </c>
+      <c r="C373" s="6" t="inlineStr">
+        <is>
+          <t>しょうとつする</t>
+        </is>
+      </c>
+      <c r="D373" s="7" t="inlineStr">
+        <is>
+          <t>Đâm vào nhau, va chạm tông nhau</t>
+        </is>
+      </c>
+      <c r="E373" s="7" t="inlineStr">
+        <is>
+          <t>車と衝突するところだった (suýt chút nữa là đâm va chạm với ô tô)</t>
+        </is>
+      </c>
+      <c r="F373" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 252] Đồng nghĩa với ぶつかる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="24" customHeight="1">
+      <c r="A374" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>倒れる</t>
+        </is>
+      </c>
+      <c r="C374" s="3" t="inlineStr">
+        <is>
+          <t>たおれる</t>
+        </is>
+      </c>
+      <c r="D374" s="4" t="inlineStr">
+        <is>
+          <t>Ngã lăn ra, đổ sập</t>
+        </is>
+      </c>
+      <c r="E374" s="4" t="inlineStr">
+        <is>
+          <t>強風で木が倒れた (gió lớn làm cây đổ rạp)</t>
+        </is>
+      </c>
+      <c r="F374" s="4" t="inlineStr">
+        <is>
+          <t>Rơi ngã từ vị trí đứng thẳng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="24" customHeight="1">
+      <c r="A375" s="8" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" s="9" t="inlineStr">
+        <is>
+          <t>壊れる</t>
+        </is>
+      </c>
+      <c r="C375" s="9" t="inlineStr">
+        <is>
+          <t>こわれる</t>
+        </is>
+      </c>
+      <c r="D375" s="10" t="inlineStr">
+        <is>
+          <t>Bị hỏng hóc, đổ vỡ</t>
+        </is>
+      </c>
+      <c r="E375" s="10" t="inlineStr">
+        <is>
+          <t>機械が壊れて動かない (máy móc hỏng không chạy được)</t>
+        </is>
+      </c>
+      <c r="F375" s="10" t="inlineStr">
+        <is>
+          <t>Mất đi chức năng sử dụng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="24" customHeight="1">
+      <c r="A376" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" s="6" t="inlineStr">
+        <is>
+          <t>ぶつかる</t>
+        </is>
+      </c>
+      <c r="C376" s="6" t="inlineStr">
+        <is>
+          <t>ぶつかる</t>
+        </is>
+      </c>
+      <c r="D376" s="7" t="inlineStr">
+        <is>
+          <t>Đâm vào, va chạm phải</t>
+        </is>
+      </c>
+      <c r="E376" s="7" t="inlineStr">
+        <is>
+          <t>電柱にぶつかる (tông va phải cột điện)</t>
+        </is>
+      </c>
+      <c r="F376" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 252] = 衝突する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="24" customHeight="1">
+      <c r="A377" s="8" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" s="9" t="inlineStr">
+        <is>
+          <t>破れる</t>
+        </is>
+      </c>
+      <c r="C377" s="9" t="inlineStr">
+        <is>
+          <t>やぶれる</t>
+        </is>
+      </c>
+      <c r="D377" s="10" t="inlineStr">
+        <is>
+          <t>Bị rách (giấy, áo quần)</t>
+        </is>
+      </c>
+      <c r="E377" s="10" t="inlineStr">
+        <is>
+          <t>紙がビリッと破れた (tờ giấy bị rách toạc)</t>
+        </is>
+      </c>
+      <c r="F377" s="10" t="inlineStr">
+        <is>
+          <t>Rách nát vật lý.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="24" customHeight="1">
+      <c r="A378" s="5" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" s="6" t="inlineStr">
+        <is>
+          <t>ひきょうな</t>
+        </is>
+      </c>
+      <c r="C378" s="6" t="inlineStr">
+        <is>
+          <t>ひきょうな (卑怯な)</t>
+        </is>
+      </c>
+      <c r="D378" s="7" t="inlineStr">
+        <is>
+          <t>Hèn hạ, chơi bẩn, gian lận</t>
+        </is>
+      </c>
+      <c r="E378" s="7" t="inlineStr">
+        <is>
+          <t>ひきょうなやり方は許せない (không thể tha thứ cho cách làm hèn hạ bẩn thỉu)</t>
+        </is>
+      </c>
+      <c r="F378" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 253] Đồng nghĩa với ずるい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="24" customHeight="1">
+      <c r="A379" s="5" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" s="6" t="inlineStr">
+        <is>
+          <t>ずるい</t>
+        </is>
+      </c>
+      <c r="C379" s="6" t="inlineStr">
+        <is>
+          <t>ずるい</t>
+        </is>
+      </c>
+      <c r="D379" s="7" t="inlineStr">
+        <is>
+          <t>Gian xảo, ranh mãnh, chơi xấu</t>
+        </is>
+      </c>
+      <c r="E379" s="7" t="inlineStr">
+        <is>
+          <t>ずるい手を使って勝つ (dùng thủ đoạn gian lận để thắng)</t>
+        </is>
+      </c>
+      <c r="F379" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 253] = ひきょうな.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="24" customHeight="1">
+      <c r="A380" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>厳しい</t>
+        </is>
+      </c>
+      <c r="C380" s="3" t="inlineStr">
+        <is>
+          <t>きびしい</t>
+        </is>
+      </c>
+      <c r="D380" s="4" t="inlineStr">
+        <is>
+          <t>Nghiêm khắc, khắc nghiệt</t>
+        </is>
+      </c>
+      <c r="E380" s="4" t="inlineStr">
+        <is>
+          <t>厳しい指導を受ける (nhận sự chỉ bảo nghiêm khắc)</t>
+        </is>
+      </c>
+      <c r="F380" s="4" t="inlineStr">
+        <is>
+          <t>Nghiêm túc không khoan nhượng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="24" customHeight="1">
+      <c r="A381" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" s="9" t="inlineStr">
+        <is>
+          <t>しつこい</t>
+        </is>
+      </c>
+      <c r="C381" s="9" t="inlineStr">
+        <is>
+          <t>しつこい</t>
+        </is>
+      </c>
+      <c r="D381" s="10" t="inlineStr">
+        <is>
+          <t>Dai dẳng, lằng nhằng phát ngấy</t>
+        </is>
+      </c>
+      <c r="E381" s="10" t="inlineStr">
+        <is>
+          <t>しつこく勧誘する (chèo kéo dai như đỉa)</t>
+        </is>
+      </c>
+      <c r="F381" s="10" t="inlineStr">
+        <is>
+          <t>Lặp lại dai dẳng gây khó chịu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="24" customHeight="1">
+      <c r="A382" s="5" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" s="6" t="inlineStr">
+        <is>
+          <t>愉快な</t>
+        </is>
+      </c>
+      <c r="C382" s="6" t="inlineStr">
+        <is>
+          <t>ゆかいな</t>
+        </is>
+      </c>
+      <c r="D382" s="7" t="inlineStr">
+        <is>
+          <t>Hài hước, vui tính, mang lại tiếng cười</t>
+        </is>
+      </c>
+      <c r="E382" s="7" t="inlineStr">
+        <is>
+          <t>愉快な仲間たち (những người bạn vui nhộn, tếu táo)</t>
+        </is>
+      </c>
+      <c r="F382" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 254] Đồng nghĩa với 面白い.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="24" customHeight="1">
+      <c r="A383" s="8" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" s="9" t="inlineStr">
+        <is>
+          <t>おしゃれな</t>
+        </is>
+      </c>
+      <c r="C383" s="9" t="inlineStr">
+        <is>
+          <t>おしゃれな</t>
+        </is>
+      </c>
+      <c r="D383" s="10" t="inlineStr">
+        <is>
+          <t>Sành điệu, thời thượng phong cách</t>
+        </is>
+      </c>
+      <c r="E383" s="10" t="inlineStr">
+        <is>
+          <t>おしゃれなカフェでお茶する (uống trà ở quán cà phê sành điệu)</t>
+        </is>
+      </c>
+      <c r="F383" s="10" t="inlineStr">
+        <is>
+          <t>Gu ăn mặc/bày trí đẹp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="24" customHeight="1">
+      <c r="A384" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>親切な</t>
+        </is>
+      </c>
+      <c r="C384" s="3" t="inlineStr">
+        <is>
+          <t>しんせつな</t>
+        </is>
+      </c>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>Tốt bụng, ân cần nhiệt tình</t>
+        </is>
+      </c>
+      <c r="E384" s="4" t="inlineStr">
+        <is>
+          <t>親切な店員さん (nhân viên bán hàng tốt bụng niềm nở)</t>
+        </is>
+      </c>
+      <c r="F384" s="4" t="inlineStr">
+        <is>
+          <t>Nhiệt tình giúp đỡ người khác.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="24" customHeight="1">
+      <c r="A385" s="8" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" s="9" t="inlineStr">
+        <is>
+          <t>かわいい</t>
+        </is>
+      </c>
+      <c r="C385" s="9" t="inlineStr">
+        <is>
+          <t>かわいい</t>
+        </is>
+      </c>
+      <c r="D385" s="10" t="inlineStr">
+        <is>
+          <t>Đáng yêu, xinh xắn dễ thương</t>
+        </is>
+      </c>
+      <c r="E385" s="10" t="inlineStr">
+        <is>
+          <t>かわいい子犬 (chú cún con đáng yêu)</t>
+        </is>
+      </c>
+      <c r="F385" s="10" t="inlineStr">
+        <is>
+          <t>Ngoại hình nhỏ nhắn dễ mến.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="24" customHeight="1">
+      <c r="A386" s="5" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" s="6" t="inlineStr">
+        <is>
+          <t>やむをえない</t>
+        </is>
+      </c>
+      <c r="C386" s="6" t="inlineStr">
+        <is>
+          <t>やむをえない</t>
+        </is>
+      </c>
+      <c r="D386" s="7" t="inlineStr">
+        <is>
+          <t>Bất đắc dĩ, không còn cách nào khác</t>
+        </is>
+      </c>
+      <c r="E386" s="7" t="inlineStr">
+        <is>
+          <t>やむをえない事情で欠席する (nghỉ học vì lý do bất khả kháng)</t>
+        </is>
+      </c>
+      <c r="F386" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 255] Đồng nghĩa với しかたがない.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="24" customHeight="1">
+      <c r="A387" s="8" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" s="9" t="inlineStr">
+        <is>
+          <t>もったいない</t>
+        </is>
+      </c>
+      <c r="C387" s="9" t="inlineStr">
+        <is>
+          <t>もったいない</t>
+        </is>
+      </c>
+      <c r="D387" s="10" t="inlineStr">
+        <is>
+          <t>Lãng phí, tiếc của</t>
+        </is>
+      </c>
+      <c r="E387" s="10" t="inlineStr">
+        <is>
+          <t>食べ物を残すのはもったいない (bỏ thừa đồ ăn thật là lãng phí)</t>
+        </is>
+      </c>
+      <c r="F387" s="10" t="inlineStr">
+        <is>
+          <t>Tiếc rẻ của cải/tài năng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="24" customHeight="1">
+      <c r="A388" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>つまらない</t>
+        </is>
+      </c>
+      <c r="C388" s="3" t="inlineStr">
+        <is>
+          <t>つまらない</t>
+        </is>
+      </c>
+      <c r="D388" s="4" t="inlineStr">
+        <is>
+          <t>Nhàm chán, vô vị</t>
+        </is>
+      </c>
+      <c r="E388" s="4" t="inlineStr">
+        <is>
+          <t>つまらない冗談 (trò đùa vô duyên, nhạt nhẽo)</t>
+        </is>
+      </c>
+      <c r="F388" s="4" t="inlineStr">
+        <is>
+          <t>Không có gì thu hút.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="24" customHeight="1">
+      <c r="A389" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" s="6" t="inlineStr">
+        <is>
+          <t>しかたがない</t>
+        </is>
+      </c>
+      <c r="C389" s="6" t="inlineStr">
+        <is>
+          <t>しかたがない</t>
+        </is>
+      </c>
+      <c r="D389" s="7" t="inlineStr">
+        <is>
+          <t>Đành chịu, không còn cách nào khác</t>
+        </is>
+      </c>
+      <c r="E389" s="7" t="inlineStr">
+        <is>
+          <t>雨だから中止もしかたがない (trời mưa đành chịu hủy thôi)</t>
+        </is>
+      </c>
+      <c r="F389" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 255] = やむをえない.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="24" customHeight="1">
+      <c r="A390" s="5" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" s="6" t="inlineStr">
+        <is>
+          <t>息抜きした</t>
+        </is>
+      </c>
+      <c r="C390" s="6" t="inlineStr">
+        <is>
+          <t>いきぬきした</t>
+        </is>
+      </c>
+      <c r="D390" s="7" t="inlineStr">
+        <is>
+          <t>Nghỉ xả hơi, nghỉ giải lao</t>
+        </is>
+      </c>
+      <c r="E390" s="7" t="inlineStr">
+        <is>
+          <t>少し息抜きしたほうがいい (nên nghỉ ngơi xả hơi một chút đi)</t>
+        </is>
+      </c>
+      <c r="F390" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 256] Đồng nghĩa với 休んだ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="24" customHeight="1">
+      <c r="A391" s="8" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" s="9" t="inlineStr">
+        <is>
+          <t>待った</t>
+        </is>
+      </c>
+      <c r="C391" s="9" t="inlineStr">
+        <is>
+          <t>まった</t>
+        </is>
+      </c>
+      <c r="D391" s="10" t="inlineStr">
+        <is>
+          <t>Chờ đợi ai đó</t>
+        </is>
+      </c>
+      <c r="E391" s="10" t="inlineStr">
+        <is>
+          <t>駅で友達を待った (chờ bạn ở nhà ga)</t>
+        </is>
+      </c>
+      <c r="F391" s="10" t="inlineStr">
+        <is>
+          <t>Ngóng đợi thời gian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="24" customHeight="1">
+      <c r="A392" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>急いだ</t>
+        </is>
+      </c>
+      <c r="C392" s="3" t="inlineStr">
+        <is>
+          <t>いそいだ</t>
+        </is>
+      </c>
+      <c r="D392" s="4" t="inlineStr">
+        <is>
+          <t>Vội vã, gấp rút</t>
+        </is>
+      </c>
+      <c r="E392" s="4" t="inlineStr">
+        <is>
+          <t>走って急いだ (chạy vội vã)</t>
+        </is>
+      </c>
+      <c r="F392" s="4" t="inlineStr">
+        <is>
+          <t>Tăng tốc vì sợ muộn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="24" customHeight="1">
+      <c r="A393" s="5" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" s="6" t="inlineStr">
+        <is>
+          <t>休んだ</t>
+        </is>
+      </c>
+      <c r="C393" s="6" t="inlineStr">
+        <is>
+          <t>やすんだ</t>
+        </is>
+      </c>
+      <c r="D393" s="7" t="inlineStr">
+        <is>
+          <t>Nghỉ ngơi, tĩnh dưỡng</t>
+        </is>
+      </c>
+      <c r="E393" s="7" t="inlineStr">
+        <is>
+          <t>仕事を休んで旅行に行く (nghỉ làm đi du lịch)</t>
+        </is>
+      </c>
+      <c r="F393" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 256] = 息抜きする.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="24" customHeight="1">
+      <c r="A394" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t>働いた</t>
+        </is>
+      </c>
+      <c r="C394" s="3" t="inlineStr">
+        <is>
+          <t>はたらいた</t>
+        </is>
+      </c>
+      <c r="D394" s="4" t="inlineStr">
+        <is>
+          <t>Lao động, làm việc</t>
+        </is>
+      </c>
+      <c r="E394" s="4" t="inlineStr">
+        <is>
+          <t>一日中真面目に働いた (làm việc chăm chỉ suốt cả ngày)</t>
+        </is>
+      </c>
+      <c r="F394" s="4" t="inlineStr">
+        <is>
+          <t>Làm công việc kiếm sống.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="24" customHeight="1">
+      <c r="A395" s="5" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" s="6" t="inlineStr">
+        <is>
+          <t>ついている</t>
+        </is>
+      </c>
+      <c r="C395" s="6" t="inlineStr">
+        <is>
+          <t>ついている</t>
+        </is>
+      </c>
+      <c r="D395" s="7" t="inlineStr">
+        <is>
+          <t>May mắn, đỏ vận, gặp thời</t>
+        </is>
+      </c>
+      <c r="E395" s="7" t="inlineStr">
+        <is>
+          <t>今日はとてもついていた (hôm nay tôi gặp may mắn cực kỳ)</t>
+        </is>
+      </c>
+      <c r="F395" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 257] Đồng nghĩa với 運がよかった.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="24" customHeight="1">
+      <c r="A396" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>気分が悪かった</t>
+        </is>
+      </c>
+      <c r="C396" s="3" t="inlineStr">
+        <is>
+          <t>きぶんがわるかった</t>
+        </is>
+      </c>
+      <c r="D396" s="4" t="inlineStr">
+        <is>
+          <t>Tâm trạng tệ; khó ở trong người</t>
+        </is>
+      </c>
+      <c r="E396" s="4" t="inlineStr">
+        <is>
+          <t>体調を崩して気分が悪かった (người ớn lạnh khó ở trong người)</t>
+        </is>
+      </c>
+      <c r="F396" s="4" t="inlineStr">
+        <is>
+          <t>Khó chịu cơ thể hoặc bực bội.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="24" customHeight="1">
+      <c r="A397" s="8" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" s="9" t="inlineStr">
+        <is>
+          <t>運が悪かった</t>
+        </is>
+      </c>
+      <c r="C397" s="9" t="inlineStr">
+        <is>
+          <t>うんがわるかった</t>
+        </is>
+      </c>
+      <c r="D397" s="10" t="inlineStr">
+        <is>
+          <t>Xui xẻo, đen đủi, không may</t>
+        </is>
+      </c>
+      <c r="E397" s="10" t="inlineStr">
+        <is>
+          <t>くじが外れて運が悪かった (bốc trượt vé số xui ghê)</t>
+        </is>
+      </c>
+      <c r="F397" s="10" t="inlineStr">
+        <is>
+          <t>Trái nghĩa với ついている.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="24" customHeight="1">
+      <c r="A398" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>気分がよかった</t>
+        </is>
+      </c>
+      <c r="C398" s="3" t="inlineStr">
+        <is>
+          <t>きぶんがよかった</t>
+        </is>
+      </c>
+      <c r="D398" s="4" t="inlineStr">
+        <is>
+          <t>Tâm trạng phấn chấn sảng khoái</t>
+        </is>
+      </c>
+      <c r="E398" s="4" t="inlineStr">
+        <is>
+          <t>天気が晴れて気分がよかった (trời nắng ráo tâm trạng rất tốt)</t>
+        </is>
+      </c>
+      <c r="F398" s="4" t="inlineStr">
+        <is>
+          <t>Cảm giác khoan khoái tâm hồn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="24" customHeight="1">
+      <c r="A399" s="5" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" s="6" t="inlineStr">
+        <is>
+          <t>運がよかった</t>
+        </is>
+      </c>
+      <c r="C399" s="6" t="inlineStr">
+        <is>
+          <t>うんがよかった</t>
+        </is>
+      </c>
+      <c r="D399" s="7" t="inlineStr">
+        <is>
+          <t>Vận đỏ, may mắn</t>
+        </is>
+      </c>
+      <c r="E399" s="7" t="inlineStr">
+        <is>
+          <t>雨に降られず運がよかった (không bị dính mưa may mắn thật)</t>
+        </is>
+      </c>
+      <c r="F399" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 257] = ついている.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="24" customHeight="1">
+      <c r="A400" s="5" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" s="6" t="inlineStr">
+        <is>
+          <t>つねに</t>
+        </is>
+      </c>
+      <c r="C400" s="6" t="inlineStr">
+        <is>
+          <t>つねに (常に)</t>
+        </is>
+      </c>
+      <c r="D400" s="7" t="inlineStr">
+        <is>
+          <t>Luôn luôn, lúc nào cũng</t>
+        </is>
+      </c>
+      <c r="E400" s="7" t="inlineStr">
+        <is>
+          <t>つねに言葉遣いに気をつける (luôn luôn để ý cẩn trọng lời ăn tiếng nói)</t>
+        </is>
+      </c>
+      <c r="F400" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 258] Đồng nghĩa với いつも.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="24" customHeight="1">
+      <c r="A401" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" s="6" t="inlineStr">
+        <is>
+          <t>いつも</t>
+        </is>
+      </c>
+      <c r="C401" s="6" t="inlineStr">
+        <is>
+          <t>いつも</t>
+        </is>
+      </c>
+      <c r="D401" s="7" t="inlineStr">
+        <is>
+          <t>Lúc nào cũng, mọi khi</t>
+        </is>
+      </c>
+      <c r="E401" s="7" t="inlineStr">
+        <is>
+          <t>いつも笑顔を絶やさない (lúc nào cũng giữ nụ cười rạng rỡ)</t>
+        </is>
+      </c>
+      <c r="F401" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 258] = つねに.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="24" customHeight="1">
+      <c r="A402" s="2" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>特に</t>
+        </is>
+      </c>
+      <c r="C402" s="3" t="inlineStr">
+        <is>
+          <t>とくに</t>
+        </is>
+      </c>
+      <c r="D402" s="4" t="inlineStr">
+        <is>
+          <t>Đặc biệt là</t>
+        </is>
+      </c>
+      <c r="E402" s="4" t="inlineStr">
+        <is>
+          <t>特に問題はない (đặc biệt không có vấn đề gì lớn)</t>
+        </is>
+      </c>
+      <c r="F402" s="4" t="inlineStr">
+        <is>
+          <t>Nhấn mạnh trường hợp cụ thể.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="24" customHeight="1">
+      <c r="A403" s="8" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" s="9" t="inlineStr">
+        <is>
+          <t>できるだけ</t>
+        </is>
+      </c>
+      <c r="C403" s="9" t="inlineStr">
+        <is>
+          <t>できるだけ</t>
+        </is>
+      </c>
+      <c r="D403" s="10" t="inlineStr">
+        <is>
+          <t>Cố gắng hết sức trong khả năng</t>
+        </is>
+      </c>
+      <c r="E403" s="10" t="inlineStr">
+        <is>
+          <t>できるだけ早く返事する (trả lời sớm nhất trong khả năng có thể)</t>
+        </is>
+      </c>
+      <c r="F403" s="10" t="inlineStr">
+        <is>
+          <t>Tùy theo năng lực tối đa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="24" customHeight="1">
+      <c r="A404" s="5" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" s="6" t="inlineStr">
+        <is>
+          <t>当てる</t>
+        </is>
+      </c>
+      <c r="C404" s="6" t="inlineStr">
+        <is>
+          <t>あてる</t>
+        </is>
+      </c>
+      <c r="D404" s="7" t="inlineStr">
+        <is>
+          <t>Ném trúng, va vào, làm chạm vào</t>
+        </is>
+      </c>
+      <c r="E404" s="7" t="inlineStr">
+        <is>
+          <t>車にボールを当ててしかられた (ném bóng trúng vào xe ô tô nên bị mắng)</t>
+        </is>
+      </c>
+      <c r="F404" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 259] Đồng nghĩa với ぶつける.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="24" customHeight="1">
+      <c r="A405" s="5" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" s="6" t="inlineStr">
+        <is>
+          <t>ぶつける</t>
+        </is>
+      </c>
+      <c r="C405" s="6" t="inlineStr">
+        <is>
+          <t>ぶつける</t>
+        </is>
+      </c>
+      <c r="D405" s="7" t="inlineStr">
+        <is>
+          <t>Tông vào, va chạm vào</t>
+        </is>
+      </c>
+      <c r="E405" s="7" t="inlineStr">
+        <is>
+          <t>壁に頭をぶつける (va đầu vào tường)</t>
+        </is>
+      </c>
+      <c r="F405" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 259] = 当てる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="24" customHeight="1">
+      <c r="A406" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>隠す</t>
+        </is>
+      </c>
+      <c r="C406" s="3" t="inlineStr">
+        <is>
+          <t>かくす</t>
+        </is>
+      </c>
+      <c r="D406" s="4" t="inlineStr">
+        <is>
+          <t>Che giấu, giấu đi</t>
+        </is>
+      </c>
+      <c r="E406" s="4" t="inlineStr">
+        <is>
+          <t>宝物を土の中に隠す (giấu kho báu vào trong lòng đất)</t>
+        </is>
+      </c>
+      <c r="F406" s="4" t="inlineStr">
+        <is>
+          <t>Che đậy không cho thấy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="24" customHeight="1">
+      <c r="A407" s="8" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" s="9" t="inlineStr">
+        <is>
+          <t>落とす</t>
+        </is>
+      </c>
+      <c r="C407" s="9" t="inlineStr">
+        <is>
+          <t>おとす</t>
+        </is>
+      </c>
+      <c r="D407" s="10" t="inlineStr">
+        <is>
+          <t>Làm rơi, đánh rơi</t>
+        </is>
+      </c>
+      <c r="E407" s="10" t="inlineStr">
+        <is>
+          <t>財布を道に落とす (đánh rơi ví ra đường)</t>
+        </is>
+      </c>
+      <c r="F407" s="10" t="inlineStr">
+        <is>
+          <t>Làm đồ vật rơi xuống đất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="24" customHeight="1">
+      <c r="A408" s="2" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>詰める</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="inlineStr">
+        <is>
+          <t>つめる</t>
+        </is>
+      </c>
+      <c r="D408" s="4" t="inlineStr">
+        <is>
+          <t>Nhồi nhét, đóng gói chặt</t>
+        </is>
+      </c>
+      <c r="E408" s="4" t="inlineStr">
+        <is>
+          <t>箱に荷物を詰める (nhét đồ vào hộp carton)</t>
+        </is>
+      </c>
+      <c r="F408" s="4" t="inlineStr">
+        <is>
+          <t>Đưa vào trong vật chứa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="24" customHeight="1">
+      <c r="A409" s="5" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" s="6" t="inlineStr">
+        <is>
+          <t>あわれな</t>
+        </is>
+      </c>
+      <c r="C409" s="6" t="inlineStr">
+        <is>
+          <t>あわれな (哀れな)</t>
+        </is>
+      </c>
+      <c r="D409" s="7" t="inlineStr">
+        <is>
+          <t>Đáng thương, bi đát, tội nghiệp</t>
+        </is>
+      </c>
+      <c r="E409" s="7" t="inlineStr">
+        <is>
+          <t>あわれな人生を送る (trải qua cuộc đời bi đát đầy đáng thương)</t>
+        </is>
+      </c>
+      <c r="F409" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 260] Đồng nghĩa với かわいそうな.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="24" customHeight="1">
+      <c r="A410" s="2" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>退屈な</t>
+        </is>
+      </c>
+      <c r="C410" s="3" t="inlineStr">
+        <is>
+          <t>たいくつな</t>
+        </is>
+      </c>
+      <c r="D410" s="4" t="inlineStr">
+        <is>
+          <t>Buồn tẻ, chán ngắt không có gì làm</t>
+        </is>
+      </c>
+      <c r="E410" s="4" t="inlineStr">
+        <is>
+          <t>退屈な講義で居眠りする (ngủ gật vì bài giảng tẻ nhạt chán ngắt)</t>
+        </is>
+      </c>
+      <c r="F410" s="4" t="inlineStr">
+        <is>
+          <t>Thiếu kích thích hứng thú.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="24" customHeight="1">
+      <c r="A411" s="8" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" s="9" t="inlineStr">
+        <is>
+          <t>おかしな</t>
+        </is>
+      </c>
+      <c r="C411" s="9" t="inlineStr">
+        <is>
+          <t>おかしな</t>
+        </is>
+      </c>
+      <c r="D411" s="10" t="inlineStr">
+        <is>
+          <t>Nực cười, kỳ quặc lạ lùng</t>
+        </is>
+      </c>
+      <c r="E411" s="10" t="inlineStr">
+        <is>
+          <t>おかしな格好をしている (mặc bộ trang phục buồn cười kỳ quặc)</t>
+        </is>
+      </c>
+      <c r="F411" s="10" t="inlineStr">
+        <is>
+          <t>Gây cười hoặc bất thường.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="24" customHeight="1">
+      <c r="A412" s="5" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" s="6" t="inlineStr">
+        <is>
+          <t>かわいそうな</t>
+        </is>
+      </c>
+      <c r="C412" s="6" t="inlineStr">
+        <is>
+          <t>かわいそうな</t>
+        </is>
+      </c>
+      <c r="D412" s="7" t="inlineStr">
+        <is>
+          <t>Đáng thương, tội nghiệp</t>
+        </is>
+      </c>
+      <c r="E412" s="7" t="inlineStr">
+        <is>
+          <t>捨てられた子猫がかわいそうだ (chú mèo con bị bỏ rơi trông tội nghiệp quá)</t>
+        </is>
+      </c>
+      <c r="F412" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 260] = あわれな.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="24" customHeight="1">
+      <c r="A413" s="8" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" s="9" t="inlineStr">
+        <is>
+          <t>不安な</t>
+        </is>
+      </c>
+      <c r="C413" s="9" t="inlineStr">
+        <is>
+          <t>ふあんな</t>
+        </is>
+      </c>
+      <c r="D413" s="10" t="inlineStr">
+        <is>
+          <t>Bất an, lo âu thấp thỏm</t>
+        </is>
+      </c>
+      <c r="E413" s="10" t="inlineStr">
+        <is>
+          <t>将来に不安を抱く (thấp thỏm âu lo cho tương lai)</t>
+        </is>
+      </c>
+      <c r="F413" s="10" t="inlineStr">
+        <is>
+          <t>Cảm giác không an lòng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="24" customHeight="1">
+      <c r="A414" s="5" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" s="6" t="inlineStr">
+        <is>
+          <t>当分</t>
+        </is>
+      </c>
+      <c r="C414" s="6" t="inlineStr">
+        <is>
+          <t>とうぶん</t>
+        </is>
+      </c>
+      <c r="D414" s="7" t="inlineStr">
+        <is>
+          <t>Hiện tại và sắp tới, tạm thời một thời gian</t>
+        </is>
+      </c>
+      <c r="E414" s="7" t="inlineStr">
+        <is>
+          <t>当分は使わない予定です (tạm thời trong thời gian tới chưa có ý định dùng)</t>
+        </is>
+      </c>
+      <c r="F414" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 261] Đồng nghĩa với しばらく.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="24" customHeight="1">
+      <c r="A415" s="8" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" s="9" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="C415" s="9" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="D415" s="10" t="inlineStr">
+        <is>
+          <t>Từ nay về sau, sắp sửa</t>
+        </is>
+      </c>
+      <c r="E415" s="10" t="inlineStr">
+        <is>
+          <t>これから会議が始まる (từ giờ cuộc họp sẽ bắt đầu)</t>
+        </is>
+      </c>
+      <c r="F415" s="10" t="inlineStr">
+        <is>
+          <t>Tính từ mốc hiện tại trở đi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="24" customHeight="1">
+      <c r="A416" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C416" s="3" t="inlineStr">
+        <is>
+          <t>ぜんぶ</t>
+        </is>
+      </c>
+      <c r="D416" s="4" t="inlineStr">
+        <is>
+          <t>Toàn bộ, tất cả</t>
+        </is>
+      </c>
+      <c r="E416" s="4" t="inlineStr">
+        <is>
+          <t>全部片付けた (dọn dẹp sạch sẽ toàn bộ)</t>
+        </is>
+      </c>
+      <c r="F416" s="4" t="inlineStr">
+        <is>
+          <t>Tất cả mọi thứ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="24" customHeight="1">
+      <c r="A417" s="8" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" s="9" t="inlineStr">
+        <is>
+          <t>今回</t>
+        </is>
+      </c>
+      <c r="C417" s="9" t="inlineStr">
+        <is>
+          <t>こんかい</t>
+        </is>
+      </c>
+      <c r="D417" s="10" t="inlineStr">
+        <is>
+          <t>Lần này</t>
+        </is>
+      </c>
+      <c r="E417" s="10" t="inlineStr">
+        <is>
+          <t>今回のテストは難しかった (bài thi lần này khó quá)</t>
+        </is>
+      </c>
+      <c r="F417" s="10" t="inlineStr">
+        <is>
+          <t>Lượt hiện tại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="24" customHeight="1">
+      <c r="A418" s="5" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" s="6" t="inlineStr">
+        <is>
+          <t>しばらく</t>
+        </is>
+      </c>
+      <c r="C418" s="6" t="inlineStr">
+        <is>
+          <t>しばらく</t>
+        </is>
+      </c>
+      <c r="D418" s="7" t="inlineStr">
+        <is>
+          <t>Một thời gian, tạm thời</t>
+        </is>
+      </c>
+      <c r="E418" s="7" t="inlineStr">
+        <is>
+          <t>しばらく休養を取る (tạm thời nghỉ dưỡng một thời gian)</t>
+        </is>
+      </c>
+      <c r="F418" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 261] = 当分.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="24" customHeight="1">
+      <c r="A419" s="5" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" s="6" t="inlineStr">
+        <is>
+          <t>一転した</t>
+        </is>
+      </c>
+      <c r="C419" s="6" t="inlineStr">
+        <is>
+          <t>いってんした</t>
+        </is>
+      </c>
+      <c r="D419" s="7" t="inlineStr">
+        <is>
+          <t>Xoay chuyển 180 độ, thay đổi hoàn toàn</t>
+        </is>
+      </c>
+      <c r="E419" s="7" t="inlineStr">
+        <is>
+          <t>留学の話が一転した (chuyện du học bỗng chốc đảo ngược thay đổi hoàn toàn)</t>
+        </is>
+      </c>
+      <c r="F419" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 262] Đồng nghĩa với すっかり変わった.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="24" customHeight="1">
+      <c r="A420" s="2" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t>急に止まった</t>
+        </is>
+      </c>
+      <c r="C420" s="3" t="inlineStr">
+        <is>
+          <t>きゅうにとまった</t>
+        </is>
+      </c>
+      <c r="D420" s="4" t="inlineStr">
+        <is>
+          <t>Đột ngột khựng lại, dừng gấp</t>
+        </is>
+      </c>
+      <c r="E420" s="4" t="inlineStr">
+        <is>
+          <t>車が急に止まった (xe ô tô thắng gấp dừng lại đột ngột)</t>
+        </is>
+      </c>
+      <c r="F420" s="4" t="inlineStr">
+        <is>
+          <t>Dừng lại bất thình lình.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="24" customHeight="1">
+      <c r="A421" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" s="6" t="inlineStr">
+        <is>
+          <t>すっかり変わった</t>
+        </is>
+      </c>
+      <c r="C421" s="6" t="inlineStr">
+        <is>
+          <t>すっかりかわった</t>
+        </is>
+      </c>
+      <c r="D421" s="7" t="inlineStr">
+        <is>
+          <t>Thay đổi hoàn toàn không còn như trước</t>
+        </is>
+      </c>
+      <c r="E421" s="7" t="inlineStr">
+        <is>
+          <t>街の様子がすっかり変わった (diện mạo con phố đã thay đổi hoàn toàn)</t>
+        </is>
+      </c>
+      <c r="F421" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 262] = 一転する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="24" customHeight="1">
+      <c r="A422" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
+          <t>少し進んだ</t>
+        </is>
+      </c>
+      <c r="C422" s="3" t="inlineStr">
+        <is>
+          <t>すこしすすんだ</t>
+        </is>
+      </c>
+      <c r="D422" s="4" t="inlineStr">
+        <is>
+          <t>Tiến triển thêm một chút</t>
+        </is>
+      </c>
+      <c r="E422" s="4" t="inlineStr">
+        <is>
+          <t>工事が少し進んだ (công trình đã tiến thêm được một ít)</t>
+        </is>
+      </c>
+      <c r="F422" s="4" t="inlineStr">
+        <is>
+          <t>Tăng thêm chút tiến độ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="24" customHeight="1">
+      <c r="A423" s="8" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" s="9" t="inlineStr">
+        <is>
+          <t>とうとう許された</t>
+        </is>
+      </c>
+      <c r="C423" s="9" t="inlineStr">
+        <is>
+          <t>とうとうゆるされた</t>
+        </is>
+      </c>
+      <c r="D423" s="10" t="inlineStr">
+        <is>
+          <t>Cuối cùng đã được thứ lỗi/cho phép</t>
+        </is>
+      </c>
+      <c r="E423" s="10" t="inlineStr">
+        <is>
+          <t>父にとうとう許された (cuối cùng đã được bố đồng ý cho phép)</t>
+        </is>
+      </c>
+      <c r="F423" s="10" t="inlineStr">
+        <is>
+          <t>Nhận được sự ưng thuận sau cùng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="24" customHeight="1">
+      <c r="A424" s="5" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" s="6" t="inlineStr">
+        <is>
+          <t>じたばたする</t>
+        </is>
+      </c>
+      <c r="C424" s="6" t="inlineStr">
+        <is>
+          <t>じたばたする</t>
+        </is>
+      </c>
+      <c r="D424" s="7" t="inlineStr">
+        <is>
+          <t>Cuống cuồng, hoảng loạn, giãy giụa vô ích</t>
+        </is>
+      </c>
+      <c r="E424" s="7" t="inlineStr">
+        <is>
+          <t>前日になってじたばたしても仕方がない (đến sát ngày thi mới cuống cuồng lên thì cũng chẳng ích gì)</t>
+        </is>
+      </c>
+      <c r="F424" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 263] Đồng nghĩa với 慌てる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="24" customHeight="1">
+      <c r="A425" s="5" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" s="6" t="inlineStr">
+        <is>
+          <t>慌てる</t>
+        </is>
+      </c>
+      <c r="C425" s="6" t="inlineStr">
+        <is>
+          <t>あわてる</t>
+        </is>
+      </c>
+      <c r="D425" s="7" t="inlineStr">
+        <is>
+          <t>Luống cuống, hoảng loạn mất bình tĩnh</t>
+        </is>
+      </c>
+      <c r="E425" s="7" t="inlineStr">
+        <is>
+          <t>地震が起きても慌てないで (dù động đất cũng đừng hoảng loạn)</t>
+        </is>
+      </c>
+      <c r="F425" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 263] = じたばたする.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="24" customHeight="1">
+      <c r="A426" s="2" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>心配する</t>
+        </is>
+      </c>
+      <c r="C426" s="3" t="inlineStr">
+        <is>
+          <t>しんぱいする</t>
+        </is>
+      </c>
+      <c r="D426" s="4" t="inlineStr">
+        <is>
+          <t>Lo lắng về điều gì</t>
+        </is>
+      </c>
+      <c r="E426" s="4" t="inlineStr">
+        <is>
+          <t>親を心配させるな (đừng làm cho cha mẹ phải lo lắng)</t>
+        </is>
+      </c>
+      <c r="F426" s="4" t="inlineStr">
+        <is>
+          <t>Lo âu trong lòng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="24" customHeight="1">
+      <c r="A427" s="8" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" s="9" t="inlineStr">
+        <is>
+          <t>緊張する</t>
+        </is>
+      </c>
+      <c r="C427" s="9" t="inlineStr">
+        <is>
+          <t>きんちょうする</t>
+        </is>
+      </c>
+      <c r="D427" s="10" t="inlineStr">
+        <is>
+          <t>Căng thẳng hồi hộp</t>
+        </is>
+      </c>
+      <c r="E427" s="10" t="inlineStr">
+        <is>
+          <t>本番で緊張する (hồi hộp căng thẳng trong buổi thi chính thức)</t>
+        </is>
+      </c>
+      <c r="F427" s="10" t="inlineStr">
+        <is>
+          <t>Căng thẳng tinh thần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="24" customHeight="1">
+      <c r="A428" s="2" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" s="3" t="inlineStr">
+        <is>
+          <t>悩む</t>
+        </is>
+      </c>
+      <c r="C428" s="3" t="inlineStr">
+        <is>
+          <t>なやむ</t>
+        </is>
+      </c>
+      <c r="D428" s="4" t="inlineStr">
+        <is>
+          <t>Trăn trở, đau đầu suy nghĩ</t>
+        </is>
+      </c>
+      <c r="E428" s="4" t="inlineStr">
+        <is>
+          <t>進路について深く悩む (trăn trở sâu sắc về con đường tương lai)</t>
+        </is>
+      </c>
+      <c r="F428" s="4" t="inlineStr">
+        <is>
+          <t>Suy tư bế tắc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="24" customHeight="1">
+      <c r="A429" s="5" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" s="6" t="inlineStr">
+        <is>
+          <t>テクニック</t>
+        </is>
+      </c>
+      <c r="C429" s="6" t="inlineStr">
+        <is>
+          <t>テクニック</t>
+        </is>
+      </c>
+      <c r="D429" s="7" t="inlineStr">
+        <is>
+          <t>Kỹ thuật, kỹ năng điêu luyện (technique)</t>
+        </is>
+      </c>
+      <c r="E429" s="7" t="inlineStr">
+        <is>
+          <t>特別なテクニックが必要だ (cần có kỹ thuật kỹ năng đặc biệt)</t>
+        </is>
+      </c>
+      <c r="F429" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 264] Đồng nghĩa với 技術.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="24" customHeight="1">
+      <c r="A430" s="5" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" s="6" t="inlineStr">
+        <is>
+          <t>技術</t>
+        </is>
+      </c>
+      <c r="C430" s="6" t="inlineStr">
+        <is>
+          <t>ぎじゅつ</t>
+        </is>
+      </c>
+      <c r="D430" s="7" t="inlineStr">
+        <is>
+          <t>Kỹ thuật, tay nghề, kỹ xảo</t>
+        </is>
+      </c>
+      <c r="E430" s="7" t="inlineStr">
+        <is>
+          <t>高い技術を身につける (nắm vững tay nghề kỹ thuật cao)</t>
+        </is>
+      </c>
+      <c r="F430" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 264] = テクニック.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="24" customHeight="1">
+      <c r="A431" s="8" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" s="9" t="inlineStr">
+        <is>
+          <t>知識</t>
+        </is>
+      </c>
+      <c r="C431" s="9" t="inlineStr">
+        <is>
+          <t>ちしき</t>
+        </is>
+      </c>
+      <c r="D431" s="10" t="inlineStr">
+        <is>
+          <t>Tri thức, kiến thức lý thuyết</t>
+        </is>
+      </c>
+      <c r="E431" s="10" t="inlineStr">
+        <is>
+          <t>幅広い知識を持つ (sở hữu vốn kiến thức sâu rộng)</t>
+        </is>
+      </c>
+      <c r="F431" s="10" t="inlineStr">
+        <is>
+          <t>Hiểu biết học thuật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="24" customHeight="1">
+      <c r="A432" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>工夫</t>
+        </is>
+      </c>
+      <c r="C432" s="3" t="inlineStr">
+        <is>
+          <t>くふう</t>
+        </is>
+      </c>
+      <c r="D432" s="4" t="inlineStr">
+        <is>
+          <t>Sáng tạo, bỏ công tìm tòi giải pháp</t>
+        </is>
+      </c>
+      <c r="E432" s="4" t="inlineStr">
+        <is>
+          <t>いろいろと工夫を凝らす (dày công tìm tòi sáng tạo phương thức mới)</t>
+        </is>
+      </c>
+      <c r="F432" s="4" t="inlineStr">
+        <is>
+          <t>Nghĩ cách cải tiến.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="24" customHeight="1">
+      <c r="A433" s="8" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" s="9" t="inlineStr">
+        <is>
+          <t>訓練</t>
+        </is>
+      </c>
+      <c r="C433" s="9" t="inlineStr">
+        <is>
+          <t>くんれん</t>
+        </is>
+      </c>
+      <c r="D433" s="10" t="inlineStr">
+        <is>
+          <t>Huấn luyện, thao dượt rèn luyện</t>
+        </is>
+      </c>
+      <c r="E433" s="10" t="inlineStr">
+        <is>
+          <t>厳しい訓練に耐える (chịu đựng quá trình huấn luyện gian khổ)</t>
+        </is>
+      </c>
+      <c r="F433" s="10" t="inlineStr">
+        <is>
+          <t>Luyện tập bài bản theo kỷ luật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="24" customHeight="1">
+      <c r="A434" s="5" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" s="6" t="inlineStr">
+        <is>
+          <t>うつむく</t>
+        </is>
+      </c>
+      <c r="C434" s="6" t="inlineStr">
+        <is>
+          <t>うつむく (俯く)</t>
+        </is>
+      </c>
+      <c r="D434" s="7" t="inlineStr">
+        <is>
+          <t>Cúi gằm mặt xuống đất, cúi đầu</t>
+        </is>
+      </c>
+      <c r="E434" s="7" t="inlineStr">
+        <is>
+          <t>黙ってうつむいていた (im lặng cúi gằm mặt nhìn xuống đất)</t>
+        </is>
+      </c>
+      <c r="F434" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 265] Đồng nghĩa với 下を向く.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="24" customHeight="1">
+      <c r="A435" s="8" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" s="9" t="inlineStr">
+        <is>
+          <t>遠くを見る</t>
+        </is>
+      </c>
+      <c r="C435" s="9" t="inlineStr">
+        <is>
+          <t>とおくをみる</t>
+        </is>
+      </c>
+      <c r="D435" s="10" t="inlineStr">
+        <is>
+          <t>Nhìn ra nơi xa xôi</t>
+        </is>
+      </c>
+      <c r="E435" s="10" t="inlineStr">
+        <is>
+          <t>窓から遠くの山を見る (nhìn ngắm rặng núi xa xôi ngoài cửa sổ)</t>
+        </is>
+      </c>
+      <c r="F435" s="10" t="inlineStr">
+        <is>
+          <t>Hướng tầm mắt ra xa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="24" customHeight="1">
+      <c r="A436" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>目を閉じる</t>
+        </is>
+      </c>
+      <c r="C436" s="3" t="inlineStr">
+        <is>
+          <t>めをとじる</t>
+        </is>
+      </c>
+      <c r="D436" s="4" t="inlineStr">
+        <is>
+          <t>Nhắm mắt lại</t>
+        </is>
+      </c>
+      <c r="E436" s="4" t="inlineStr">
+        <is>
+          <t>目を閉じて音楽を聴く (nhắm nghiền mắt lắng nghe âm nhạc)</t>
+        </is>
+      </c>
+      <c r="F436" s="4" t="inlineStr">
+        <is>
+          <t>Khép mi mắt lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="24" customHeight="1">
+      <c r="A437" s="5" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" s="6" t="inlineStr">
+        <is>
+          <t>下を向く</t>
+        </is>
+      </c>
+      <c r="C437" s="6" t="inlineStr">
+        <is>
+          <t>したをむく</t>
+        </is>
+      </c>
+      <c r="D437" s="7" t="inlineStr">
+        <is>
+          <t>Cúi đầu nhìn xuống phía dưới</t>
+        </is>
+      </c>
+      <c r="E437" s="7" t="inlineStr">
+        <is>
+          <t>恥ずかしくて下を向く (xấu hổ quá nên cúi gằm đầu xuống)</t>
+        </is>
+      </c>
+      <c r="F437" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 265] = うつむく.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="24" customHeight="1">
+      <c r="A438" s="2" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>腕を組む</t>
+        </is>
+      </c>
+      <c r="C438" s="3" t="inlineStr">
+        <is>
+          <t>うでをくむ</t>
+        </is>
+      </c>
+      <c r="D438" s="4" t="inlineStr">
+        <is>
+          <t>Khoanh tay trước ngực</t>
+        </is>
+      </c>
+      <c r="E438" s="4" t="inlineStr">
+        <is>
+          <t>腕を組んで考え込む (khoanh tay trầm tư suy ngẫm)</t>
+        </is>
+      </c>
+      <c r="F438" s="4" t="inlineStr">
+        <is>
+          <t>Tư thế khoanh tay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="24" customHeight="1">
+      <c r="A439" s="5" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" s="6" t="inlineStr">
+        <is>
+          <t>利口な</t>
+        </is>
+      </c>
+      <c r="C439" s="6" t="inlineStr">
+        <is>
+          <t>りこうな (利口な)</t>
+        </is>
+      </c>
+      <c r="D439" s="7" t="inlineStr">
+        <is>
+          <t>Khôn ngoan, thông minh lanh lợi</t>
+        </is>
+      </c>
+      <c r="E439" s="7" t="inlineStr">
+        <is>
+          <t>本当に利口な犬ですね (chú chó này thật là thông minh khôn ngoan)</t>
+        </is>
+      </c>
+      <c r="F439" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 266] Đồng nghĩa với 頭がいい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="24" customHeight="1">
+      <c r="A440" s="5" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" s="6" t="inlineStr">
+        <is>
+          <t>頭がいい</t>
+        </is>
+      </c>
+      <c r="C440" s="6" t="inlineStr">
+        <is>
+          <t>あたまがいい</t>
+        </is>
+      </c>
+      <c r="D440" s="7" t="inlineStr">
+        <is>
+          <t>Thông minh, đầu óc sáng dạ</t>
+        </is>
+      </c>
+      <c r="E440" s="7" t="inlineStr">
+        <is>
+          <t>頭がいい生徒 (học sinh thông minh, nhanh hiểu)</t>
+        </is>
+      </c>
+      <c r="F440" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 266] = 利口な.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="24" customHeight="1">
+      <c r="A441" s="8" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" s="9" t="inlineStr">
+        <is>
+          <t>元気な</t>
+        </is>
+      </c>
+      <c r="C441" s="9" t="inlineStr">
+        <is>
+          <t>げんきな</t>
+        </is>
+      </c>
+      <c r="D441" s="10" t="inlineStr">
+        <is>
+          <t>Khỏe khoắn, tràn đầy năng lượng</t>
+        </is>
+      </c>
+      <c r="E441" s="10" t="inlineStr">
+        <is>
+          <t>いつも元気な子ども (đứa trẻ lúc nào cũng khỏe mạnh hoạt bát)</t>
+        </is>
+      </c>
+      <c r="F441" s="10" t="inlineStr">
+        <is>
+          <t>Thể chất tốt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="24" customHeight="1">
+      <c r="A442" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" s="3" t="inlineStr">
+        <is>
+          <t>かっこいい</t>
+        </is>
+      </c>
+      <c r="C442" s="3" t="inlineStr">
+        <is>
+          <t>かっこいい</t>
+        </is>
+      </c>
+      <c r="D442" s="4" t="inlineStr">
+        <is>
+          <t>Ngầu, bảnh bao, phong độ</t>
+        </is>
+      </c>
+      <c r="E442" s="4" t="inlineStr">
+        <is>
+          <t>かっこいい車に乗る (lái chiếc xe ô tô trông thật ngầu)</t>
+        </is>
+      </c>
+      <c r="F442" s="4" t="inlineStr">
+        <is>
+          <t>Vẻ ngoài cuốn hút.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="24" customHeight="1">
+      <c r="A443" s="5" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" s="6" t="inlineStr">
+        <is>
+          <t>用心した</t>
+        </is>
+      </c>
+      <c r="C443" s="6" t="inlineStr">
+        <is>
+          <t>ようじんした</t>
+        </is>
+      </c>
+      <c r="D443" s="7" t="inlineStr">
+        <is>
+          <t>Đề phòng, cẩn trọng chú ý</t>
+        </is>
+      </c>
+      <c r="E443" s="7" t="inlineStr">
+        <is>
+          <t>もう少し用心したほうがいい (nên cẩn trọng chú ý đề phòng hơn một chút)</t>
+        </is>
+      </c>
+      <c r="F443" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 267] Đồng nghĩa với 気をつける.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="24" customHeight="1">
+      <c r="A444" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>落ち着いた</t>
+        </is>
+      </c>
+      <c r="C444" s="3" t="inlineStr">
+        <is>
+          <t>おちついた</t>
+        </is>
+      </c>
+      <c r="D444" s="4" t="inlineStr">
+        <is>
+          <t>Bình tĩnh, điềm đạm, lắng xuống</t>
+        </is>
+      </c>
+      <c r="E444" s="4" t="inlineStr">
+        <is>
+          <t>落ち着いて行動する (hành động một cách bình tĩnh)</t>
+        </is>
+      </c>
+      <c r="F444" s="4" t="inlineStr">
+        <is>
+          <t>Giữ được sự điềm tĩnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="24" customHeight="1">
+      <c r="A445" s="8" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" s="9" t="inlineStr">
+        <is>
+          <t>がんばった</t>
+        </is>
+      </c>
+      <c r="C445" s="9" t="inlineStr">
+        <is>
+          <t>がんばった</t>
+        </is>
+      </c>
+      <c r="D445" s="10" t="inlineStr">
+        <is>
+          <t>Đã cố gắng hết sức</t>
+        </is>
+      </c>
+      <c r="E445" s="10" t="inlineStr">
+        <is>
+          <t>最後までよくがんばった (đã cố gắng rất tốt tới tận phút chót)</t>
+        </is>
+      </c>
+      <c r="F445" s="10" t="inlineStr">
+        <is>
+          <t>Nỗ lực làm việc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446" ht="24" customHeight="1">
+      <c r="A446" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>よく考えた</t>
+        </is>
+      </c>
+      <c r="C446" s="3" t="inlineStr">
+        <is>
+          <t>よくかんがえた</t>
+        </is>
+      </c>
+      <c r="D446" s="4" t="inlineStr">
+        <is>
+          <t>Suy nghĩ kỹ càng</t>
+        </is>
+      </c>
+      <c r="E446" s="4" t="inlineStr">
+        <is>
+          <t>よく考えてから決める (suy nghĩ thấu đáo rồi mới quyết định)</t>
+        </is>
+      </c>
+      <c r="F446" s="4" t="inlineStr">
+        <is>
+          <t>Tư duy cẩn trọng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="24" customHeight="1">
+      <c r="A447" s="5" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" s="6" t="inlineStr">
+        <is>
+          <t>気をつける</t>
+        </is>
+      </c>
+      <c r="C447" s="6" t="inlineStr">
+        <is>
+          <t>きをつける</t>
+        </is>
+      </c>
+      <c r="D447" s="7" t="inlineStr">
+        <is>
+          <t>Cẩn thận, chú ý đề phòng</t>
+        </is>
+      </c>
+      <c r="E447" s="7" t="inlineStr">
+        <is>
+          <t>風邪を引かないように気をつける (cẩn thận chú ý kẻo bị cảm lạnh)</t>
+        </is>
+      </c>
+      <c r="F447" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 267] = 用心する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="24" customHeight="1">
+      <c r="A448" s="5" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" s="6" t="inlineStr">
+        <is>
+          <t>くどい</t>
+        </is>
+      </c>
+      <c r="C448" s="6" t="inlineStr">
+        <is>
+          <t>くどい</t>
+        </is>
+      </c>
+      <c r="D448" s="7" t="inlineStr">
+        <is>
+          <t>Dài dòng, lặp đi lặp lại phát ngấy</t>
+        </is>
+      </c>
+      <c r="E448" s="7" t="inlineStr">
+        <is>
+          <t>説明がくどくて困る (lời giải thích lải nhải dài dòng phát mệt)</t>
+        </is>
+      </c>
+      <c r="F448" s="7" t="inlineStr">
+        <is>
+          <t>[Từ gạch chân câu 268] Đồng nghĩa với しつこい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="24" customHeight="1">
+      <c r="A449" s="8" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" s="9" t="inlineStr">
+        <is>
+          <t>つまらない</t>
+        </is>
+      </c>
+      <c r="C449" s="9" t="inlineStr">
+        <is>
+          <t>つまらない</t>
+        </is>
+      </c>
+      <c r="D449" s="10" t="inlineStr">
+        <is>
+          <t>Nhàm chán, tẻ nhạt</t>
+        </is>
+      </c>
+      <c r="E449" s="10" t="inlineStr">
+        <is>
+          <t>つまらない映画を見る (xem bộ phim nhạt nhẽo)</t>
+        </is>
+      </c>
+      <c r="F449" s="10" t="inlineStr">
+        <is>
+          <t>Không có gì cuốn hút.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="24" customHeight="1">
+      <c r="A450" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" s="3" t="inlineStr">
+        <is>
+          <t>下手</t>
+        </is>
+      </c>
+      <c r="C450" s="3" t="inlineStr">
+        <is>
+          <t>へた</t>
+        </is>
+      </c>
+      <c r="D450" s="4" t="inlineStr">
+        <is>
+          <t>Kém cỏi, vụng về</t>
+        </is>
+      </c>
+      <c r="E450" s="4" t="inlineStr">
+        <is>
+          <t>歌が下手だ (hát dở, kém hát)</t>
+        </is>
+      </c>
+      <c r="F450" s="4" t="inlineStr">
+        <is>
+          <t>Kỹ năng không tốt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="24" customHeight="1">
+      <c r="A451" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" s="6" t="inlineStr">
+        <is>
+          <t>しつこい</t>
+        </is>
+      </c>
+      <c r="C451" s="6" t="inlineStr">
+        <is>
+          <t>しつこい</t>
+        </is>
+      </c>
+      <c r="D451" s="7" t="inlineStr">
+        <is>
+          <t>Dai dẳng, lằng nhằng, lặp đi lặp lại</t>
+        </is>
+      </c>
+      <c r="E451" s="7" t="inlineStr">
+        <is>
+          <t>しつこく質問する (hỏi dồn dập dai như đỉa)</t>
+        </is>
+      </c>
+      <c r="F451" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 268] = くどい.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F213"/>
+  <autoFilter ref="A1:F451"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Tu_Vung_On_Tap_JLPT_N2.xlsx
+++ b/Tu_Vung_On_Tap_JLPT_N2.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tu_Vung_On_Tap" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tu_Vung_On_Tap'!$A$1:$F$451</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tu_Vung_On_Tap'!$A$1:$F$637</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F451"/>
+  <dimension ref="A1:F637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14043,8 +14043,5588 @@
         </is>
       </c>
     </row>
+    <row r="452" ht="24" customHeight="1">
+      <c r="A452" s="5" t="n">
+        <v>451</v>
+      </c>
+      <c r="B452" s="6" t="inlineStr">
+        <is>
+          <t>掲示</t>
+        </is>
+      </c>
+      <c r="C452" s="6" t="inlineStr">
+        <is>
+          <t>けいじ</t>
+        </is>
+      </c>
+      <c r="D452" s="7" t="inlineStr">
+        <is>
+          <t>Niêm yết, dán thông báo nơi công cộng</t>
+        </is>
+      </c>
+      <c r="E452" s="7" t="inlineStr">
+        <is>
+          <t>お知らせを掲示板に掲示する (dán thông báo lên bảng tin)</t>
+        </is>
+      </c>
+      <c r="F452" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 269] Phương án 4. Dán thông báo nơi đông người qua lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="24" customHeight="1">
+      <c r="A453" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="B453" s="9" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+      <c r="C453" s="9" t="inlineStr">
+        <is>
+          <t>けいさい</t>
+        </is>
+      </c>
+      <c r="D453" s="10" t="inlineStr">
+        <is>
+          <t>Đăng tải bài viết trên báo/sách/tạp chí</t>
+        </is>
+      </c>
+      <c r="E453" s="10" t="inlineStr">
+        <is>
+          <t>雑誌に論文を掲載する (đăng bài báo khoa học lên tạp chí)</t>
+        </is>
+      </c>
+      <c r="F453" s="10" t="inlineStr">
+        <is>
+          <t>Câu 269-1 dùng sai 掲示, đúng phải là 掲載.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="24" customHeight="1">
+      <c r="A454" s="2" t="n">
+        <v>453</v>
+      </c>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>宣伝</t>
+        </is>
+      </c>
+      <c r="C454" s="3" t="inlineStr">
+        <is>
+          <t>せんでん</t>
+        </is>
+      </c>
+      <c r="D454" s="4" t="inlineStr">
+        <is>
+          <t>Tuyên truyền, quảng cáo sản phẩm</t>
+        </is>
+      </c>
+      <c r="E454" s="4" t="inlineStr">
+        <is>
+          <t>テレビで洗剤を宣伝する (quảng cáo bột giặt trên TV)</t>
+        </is>
+      </c>
+      <c r="F454" s="4" t="inlineStr">
+        <is>
+          <t>Câu 269-2 dùng sai 掲示, đúng phải là 宣伝.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="24" customHeight="1">
+      <c r="A455" s="8" t="n">
+        <v>454</v>
+      </c>
+      <c r="B455" s="9" t="inlineStr">
+        <is>
+          <t>印刷</t>
+        </is>
+      </c>
+      <c r="C455" s="9" t="inlineStr">
+        <is>
+          <t>いんさつ</t>
+        </is>
+      </c>
+      <c r="D455" s="10" t="inlineStr">
+        <is>
+          <t>In ấn</t>
+        </is>
+      </c>
+      <c r="E455" s="10" t="inlineStr">
+        <is>
+          <t>名刺に写真を印刷する (in ảnh lên danh thiếp)</t>
+        </is>
+      </c>
+      <c r="F455" s="10" t="inlineStr">
+        <is>
+          <t>Câu 269-3 dùng sai 掲示, đúng phải là 印刷/載せる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="24" customHeight="1">
+      <c r="A456" s="5" t="n">
+        <v>455</v>
+      </c>
+      <c r="B456" s="6" t="inlineStr">
+        <is>
+          <t>快い</t>
+        </is>
+      </c>
+      <c r="C456" s="6" t="inlineStr">
+        <is>
+          <t>こころよい</t>
+        </is>
+      </c>
+      <c r="D456" s="7" t="inlineStr">
+        <is>
+          <t>Sẵn lòng, vui vẻ nhận lời; sảng khoái</t>
+        </is>
+      </c>
+      <c r="E456" s="7" t="inlineStr">
+        <is>
+          <t>急な頼みを快く引き受ける (sẵn lòng nhận lời thỉnh cầu đột xuất)</t>
+        </is>
+      </c>
+      <c r="F456" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 270] Phương án 3. Đi với `快く引き受ける/承諾する`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="24" customHeight="1">
+      <c r="A457" s="8" t="n">
+        <v>456</v>
+      </c>
+      <c r="B457" s="9" t="inlineStr">
+        <is>
+          <t>喜んで</t>
+        </is>
+      </c>
+      <c r="C457" s="9" t="inlineStr">
+        <is>
+          <t>よろこんで</t>
+        </is>
+      </c>
+      <c r="D457" s="10" t="inlineStr">
+        <is>
+          <t>Vui vẻ làm gì, sẵn lòng nhận</t>
+        </is>
+      </c>
+      <c r="E457" s="10" t="inlineStr">
+        <is>
+          <t>喜んでもらっていきます (tôi xin vui vẻ nhận lấy)</t>
+        </is>
+      </c>
+      <c r="F457" s="10" t="inlineStr">
+        <is>
+          <t>Câu 270-1 dùng sai 快く, đúng phải là 喜んで.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="24" customHeight="1">
+      <c r="A458" s="2" t="n">
+        <v>457</v>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>気軽に</t>
+        </is>
+      </c>
+      <c r="C458" s="3" t="inlineStr">
+        <is>
+          <t>きがるに</t>
+        </is>
+      </c>
+      <c r="D458" s="4" t="inlineStr">
+        <is>
+          <t>Thoải mái, đừng ngại ngần</t>
+        </is>
+      </c>
+      <c r="E458" s="4" t="inlineStr">
+        <is>
+          <t>気軽に遊びに来てください (hãy thoải mái ghé chơi nhé)</t>
+        </is>
+      </c>
+      <c r="F458" s="4" t="inlineStr">
+        <is>
+          <t>Câu 270-2 dùng sai 快く, đúng phải là 気軽に.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="24" customHeight="1">
+      <c r="A459" s="8" t="n">
+        <v>458</v>
+      </c>
+      <c r="B459" s="9" t="inlineStr">
+        <is>
+          <t>素直に</t>
+        </is>
+      </c>
+      <c r="C459" s="9" t="inlineStr">
+        <is>
+          <t>すなおに</t>
+        </is>
+      </c>
+      <c r="D459" s="10" t="inlineStr">
+        <is>
+          <t>Thành thật, cởi mở tâm sự</t>
+        </is>
+      </c>
+      <c r="E459" s="10" t="inlineStr">
+        <is>
+          <t>悩みを素直に打ち明ける (thành thật tâm sự nỗi niềm)</t>
+        </is>
+      </c>
+      <c r="F459" s="10" t="inlineStr">
+        <is>
+          <t>Câu 270-4 dùng sai 快く, đúng phải là 素直に/気兼ねなく.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="24" customHeight="1">
+      <c r="A460" s="5" t="n">
+        <v>459</v>
+      </c>
+      <c r="B460" s="6" t="inlineStr">
+        <is>
+          <t>分野</t>
+        </is>
+      </c>
+      <c r="C460" s="6" t="inlineStr">
+        <is>
+          <t>ぶんや</t>
+        </is>
+      </c>
+      <c r="D460" s="7" t="inlineStr">
+        <is>
+          <t>Lĩnh vực nghiên cứu, học thuật, nghệ thuật</t>
+        </is>
+      </c>
+      <c r="E460" s="7" t="inlineStr">
+        <is>
+          <t>心理学や言語学の分野 (lĩnh vực tâm lý học và ngôn ngữ học)</t>
+        </is>
+      </c>
+      <c r="F460" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 271] Phương án 3. Dùng cho ngành nghề học thuật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="24" customHeight="1">
+      <c r="A461" s="8" t="n">
+        <v>460</v>
+      </c>
+      <c r="B461" s="9" t="inlineStr">
+        <is>
+          <t>範囲</t>
+        </is>
+      </c>
+      <c r="C461" s="9" t="inlineStr">
+        <is>
+          <t>はんい</t>
+        </is>
+      </c>
+      <c r="D461" s="10" t="inlineStr">
+        <is>
+          <t>Phạm vi, mức độ</t>
+        </is>
+      </c>
+      <c r="E461" s="10" t="inlineStr">
+        <is>
+          <t>保証の範囲を超えた修理 (sửa chữa vượt quá phạm vi bảo hành)</t>
+        </is>
+      </c>
+      <c r="F461" s="10" t="inlineStr">
+        <is>
+          <t>Câu 271-1 dùng sai 分野, đúng phải là 範囲.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="24" customHeight="1">
+      <c r="A462" s="2" t="n">
+        <v>461</v>
+      </c>
+      <c r="B462" s="3" t="inlineStr">
+        <is>
+          <t>地域</t>
+        </is>
+      </c>
+      <c r="C462" s="3" t="inlineStr">
+        <is>
+          <t>ちいき</t>
+        </is>
+      </c>
+      <c r="D462" s="4" t="inlineStr">
+        <is>
+          <t>Khu vực địa lý, vùng đất</t>
+        </is>
+      </c>
+      <c r="E462" s="4" t="inlineStr">
+        <is>
+          <t>山に近い地域 (vùng/khu vực gần núi)</t>
+        </is>
+      </c>
+      <c r="F462" s="4" t="inlineStr">
+        <is>
+          <t>Câu 271-2 dùng sai 分野, đúng phải là 地域/地方.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="24" customHeight="1">
+      <c r="A463" s="8" t="n">
+        <v>462</v>
+      </c>
+      <c r="B463" s="9" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="C463" s="9" t="inlineStr">
+        <is>
+          <t>ぶぶん</t>
+        </is>
+      </c>
+      <c r="D463" s="10" t="inlineStr">
+        <is>
+          <t>Bộ phận, phần đoạn trong tác phẩm</t>
+        </is>
+      </c>
+      <c r="E463" s="10" t="inlineStr">
+        <is>
+          <t>小説のこの部分 (đoạn/phần này của cuốn tiểu thuyết)</t>
+        </is>
+      </c>
+      <c r="F463" s="10" t="inlineStr">
+        <is>
+          <t>Câu 271-4 dùng sai 分野, đúng phải là 部分/箇所.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="24" customHeight="1">
+      <c r="A464" s="5" t="n">
+        <v>463</v>
+      </c>
+      <c r="B464" s="6" t="inlineStr">
+        <is>
+          <t>生き生き</t>
+        </is>
+      </c>
+      <c r="C464" s="6" t="inlineStr">
+        <is>
+          <t>いきいき</t>
+        </is>
+      </c>
+      <c r="D464" s="7" t="inlineStr">
+        <is>
+          <t>Tràn đầy sức sống, sinh động, hăng say</t>
+        </is>
+      </c>
+      <c r="E464" s="7" t="inlineStr">
+        <is>
+          <t>サッカーをしているときが一番生き生きしている (lúc đá bóng là lúc tràn đầy sinh khí nhất)</t>
+        </is>
+      </c>
+      <c r="F464" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 272] Phương án 3. Tả người đang hoạt động hăng say, rạng rỡ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="24" customHeight="1">
+      <c r="A465" s="8" t="n">
+        <v>464</v>
+      </c>
+      <c r="B465" s="9" t="inlineStr">
+        <is>
+          <t>元気なうちに</t>
+        </is>
+      </c>
+      <c r="C465" s="9" t="inlineStr">
+        <is>
+          <t>げんきなうちに</t>
+        </is>
+      </c>
+      <c r="D465" s="10" t="inlineStr">
+        <is>
+          <t>Khi còn khỏe khoắn</t>
+        </is>
+      </c>
+      <c r="E465" s="10" t="inlineStr">
+        <is>
+          <t>体が元気なうちに旅行する (đi du lịch khi còn khỏe)</t>
+        </is>
+      </c>
+      <c r="F465" s="10" t="inlineStr">
+        <is>
+          <t>Câu 272-1 dùng sai 生き生き, đúng phải là 元気なうちに.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="24" customHeight="1">
+      <c r="A466" s="2" t="n">
+        <v>465</v>
+      </c>
+      <c r="B466" s="3" t="inlineStr">
+        <is>
+          <t>元気になる</t>
+        </is>
+      </c>
+      <c r="C466" s="3" t="inlineStr">
+        <is>
+          <t>げんきになる</t>
+        </is>
+      </c>
+      <c r="D466" s="4" t="inlineStr">
+        <is>
+          <t>Hồi phục sức khỏe, khỏe lại</t>
+        </is>
+      </c>
+      <c r="E466" s="4" t="inlineStr">
+        <is>
+          <t>薬を飲んだらだんだん元気になってきた (uống thuốc dần khỏe lại)</t>
+        </is>
+      </c>
+      <c r="F466" s="4" t="inlineStr">
+        <is>
+          <t>Câu 272-2 dùng sai 生き生き, đúng phải là 元気になってきた.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="24" customHeight="1">
+      <c r="A467" s="8" t="n">
+        <v>466</v>
+      </c>
+      <c r="B467" s="9" t="inlineStr">
+        <is>
+          <t>はっきりしている</t>
+        </is>
+      </c>
+      <c r="C467" s="9" t="inlineStr">
+        <is>
+          <t>はっきりしている</t>
+        </is>
+      </c>
+      <c r="D467" s="10" t="inlineStr">
+        <is>
+          <t>Rõ ràng, rành rọt</t>
+        </is>
+      </c>
+      <c r="E467" s="10" t="inlineStr">
+        <is>
+          <t>記憶がはっきりしている (ký ức còn rất rõ ràng)</t>
+        </is>
+      </c>
+      <c r="F467" s="10" t="inlineStr">
+        <is>
+          <t>Câu 272-4 dùng sai 生き生き, đúng phải là はっきりしている.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="24" customHeight="1">
+      <c r="A468" s="5" t="n">
+        <v>467</v>
+      </c>
+      <c r="B468" s="6" t="inlineStr">
+        <is>
+          <t>隔てる</t>
+        </is>
+      </c>
+      <c r="C468" s="6" t="inlineStr">
+        <is>
+          <t>へだてる</t>
+        </is>
+      </c>
+      <c r="D468" s="7" t="inlineStr">
+        <is>
+          <t>Ngăn cách, chia tách không gian/thời gian</t>
+        </is>
+      </c>
+      <c r="E468" s="7" t="inlineStr">
+        <is>
+          <t>大きな川が二つの市を隔てている (con sông lớn ngăn cách hai thành phố)</t>
+        </is>
+      </c>
+      <c r="F468" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 273] Phương án 2. Ngăn cách vật lý ở giữa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="24" customHeight="1">
+      <c r="A469" s="8" t="n">
+        <v>468</v>
+      </c>
+      <c r="B469" s="9" t="inlineStr">
+        <is>
+          <t>分けて考える</t>
+        </is>
+      </c>
+      <c r="C469" s="9" t="inlineStr">
+        <is>
+          <t>わけてかんがえる</t>
+        </is>
+      </c>
+      <c r="D469" s="10" t="inlineStr">
+        <is>
+          <t>Tách bạch, phân định rạch ròi</t>
+        </is>
+      </c>
+      <c r="E469" s="10" t="inlineStr">
+        <is>
+          <t>二つの問題は分けて考えるべきだ (cần tách riêng 2 vấn đề ra xem xét)</t>
+        </is>
+      </c>
+      <c r="F469" s="10" t="inlineStr">
+        <is>
+          <t>Câu 273-1 dùng sai 隔てる, đúng phải là 分けて.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="24" customHeight="1">
+      <c r="A470" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>間をあける</t>
+        </is>
+      </c>
+      <c r="C470" s="3" t="inlineStr">
+        <is>
+          <t>あいだをあける</t>
+        </is>
+      </c>
+      <c r="D470" s="4" t="inlineStr">
+        <is>
+          <t>Dãn cách thời gian / chỗ ngồi</t>
+        </is>
+      </c>
+      <c r="E470" s="4" t="inlineStr">
+        <is>
+          <t>間をあけて座ってください (xin hãy ngồi cách xa nhau)</t>
+        </is>
+      </c>
+      <c r="F470" s="4" t="inlineStr">
+        <is>
+          <t>Câu 273-3,4 dùng sai 隔てる, đúng phải là 間をおいて/あけて.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="24" customHeight="1">
+      <c r="A471" s="5" t="n">
+        <v>470</v>
+      </c>
+      <c r="B471" s="6" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="C471" s="6" t="inlineStr">
+        <is>
+          <t>ほそく</t>
+        </is>
+      </c>
+      <c r="D471" s="7" t="inlineStr">
+        <is>
+          <t>Bổ sung thông tin cho đầy đủ</t>
+        </is>
+      </c>
+      <c r="E471" s="7" t="inlineStr">
+        <is>
+          <t>少し説明を補足します (tôi xin bổ sung thêm một chút giải thích)</t>
+        </is>
+      </c>
+      <c r="F471" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 274] Phương án 2. Đi với `説明/資料を補足する`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="24" customHeight="1">
+      <c r="A472" s="2" t="n">
+        <v>471</v>
+      </c>
+      <c r="B472" s="3" t="inlineStr">
+        <is>
+          <t>足す</t>
+        </is>
+      </c>
+      <c r="C472" s="3" t="inlineStr">
+        <is>
+          <t>たす</t>
+        </is>
+      </c>
+      <c r="D472" s="4" t="inlineStr">
+        <is>
+          <t>Thêm vào (gia vị, số lượng)</t>
+        </is>
+      </c>
+      <c r="E472" s="4" t="inlineStr">
+        <is>
+          <t>塩を足しました (nêm thêm chút muối)</t>
+        </is>
+      </c>
+      <c r="F472" s="4" t="inlineStr">
+        <is>
+          <t>Câu 274-1 dùng sai 補足, đúng phải là 足す/加える.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473" ht="24" customHeight="1">
+      <c r="A473" s="8" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" s="9" t="inlineStr">
+        <is>
+          <t>サポートする</t>
+        </is>
+      </c>
+      <c r="C473" s="9" t="inlineStr">
+        <is>
+          <t>サポートする</t>
+        </is>
+      </c>
+      <c r="D473" s="10" t="inlineStr">
+        <is>
+          <t>Hỗ trợ, giúp đỡ công việc</t>
+        </is>
+      </c>
+      <c r="E473" s="10" t="inlineStr">
+        <is>
+          <t>新入社員の仕事をサポートする (hỗ trợ công việc cho nhân viên mới)</t>
+        </is>
+      </c>
+      <c r="F473" s="10" t="inlineStr">
+        <is>
+          <t>Câu 274-3 dùng sai 補足, đúng phải là サポートする/手伝う.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" ht="24" customHeight="1">
+      <c r="A474" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" s="3" t="inlineStr">
+        <is>
+          <t>置く</t>
+        </is>
+      </c>
+      <c r="C474" s="3" t="inlineStr">
+        <is>
+          <t>おく</t>
+        </is>
+      </c>
+      <c r="D474" s="4" t="inlineStr">
+        <is>
+          <t>Đặt để đồ đạc</t>
+        </is>
+      </c>
+      <c r="E474" s="4" t="inlineStr">
+        <is>
+          <t>家具を置く (bày trí đặt đồ đạc trong phòng)</t>
+        </is>
+      </c>
+      <c r="F474" s="4" t="inlineStr">
+        <is>
+          <t>Câu 274-4 dùng sai 補足, đúng phải là 置く/配置する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="24" customHeight="1">
+      <c r="A475" s="5" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" s="6" t="inlineStr">
+        <is>
+          <t>あわただしい</t>
+        </is>
+      </c>
+      <c r="C475" s="6" t="inlineStr">
+        <is>
+          <t>あわただしい (慌ただしい)</t>
+        </is>
+      </c>
+      <c r="D475" s="7" t="inlineStr">
+        <is>
+          <t>Tất bật, vội vã, bận rộn hối hả</t>
+        </is>
+      </c>
+      <c r="E475" s="7" t="inlineStr">
+        <is>
+          <t>昼ご飯も食べずにあわただしく出かけていった (chưa kịp ăn trưa đã tất bật vội vã đi ngay)</t>
+        </is>
+      </c>
+      <c r="F475" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 275] Phương án 4. Tả hành động/cuộc sống hối hả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="24" customHeight="1">
+      <c r="A476" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>激しい</t>
+        </is>
+      </c>
+      <c r="C476" s="3" t="inlineStr">
+        <is>
+          <t>はげしい</t>
+        </is>
+      </c>
+      <c r="D476" s="4" t="inlineStr">
+        <is>
+          <t>Gay gắt, biến động dữ dội</t>
+        </is>
+      </c>
+      <c r="E476" s="4" t="inlineStr">
+        <is>
+          <t>気温の変化が激しい (nhiệt độ thay đổi dữ dội)</t>
+        </is>
+      </c>
+      <c r="F476" s="4" t="inlineStr">
+        <is>
+          <t>Câu 275-1 dùng sai あわただしい, đúng phải là 激しい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="24" customHeight="1">
+      <c r="A477" s="8" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" s="9" t="inlineStr">
+        <is>
+          <t>おっちょこちょい</t>
+        </is>
+      </c>
+      <c r="C477" s="9" t="inlineStr">
+        <is>
+          <t>おっちょこちょい</t>
+        </is>
+      </c>
+      <c r="D477" s="10" t="inlineStr">
+        <is>
+          <t>Hậu đậu, đãng trí, lơ đễnh</t>
+        </is>
+      </c>
+      <c r="E477" s="10" t="inlineStr">
+        <is>
+          <t>うっかり屋／おっちょこちょいな人 (người đãng trí hay quên)</t>
+        </is>
+      </c>
+      <c r="F477" s="10" t="inlineStr">
+        <is>
+          <t>Câu 275-2 tả tính người hay quên, không dùng あわただしい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="24" customHeight="1">
+      <c r="A478" s="2" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>急速</t>
+        </is>
+      </c>
+      <c r="C478" s="3" t="inlineStr">
+        <is>
+          <t>きゅうそく</t>
+        </is>
+      </c>
+      <c r="D478" s="4" t="inlineStr">
+        <is>
+          <t>Nhanh chóng vượt bậc (phát triển)</t>
+        </is>
+      </c>
+      <c r="E478" s="4" t="inlineStr">
+        <is>
+          <t>町が急速に発展する (thị trấn phát triển nhanh chóng mặt)</t>
+        </is>
+      </c>
+      <c r="F478" s="4" t="inlineStr">
+        <is>
+          <t>Câu 275-3 dùng sai, phát triển thì dùng 急速に.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="24" customHeight="1">
+      <c r="A479" s="5" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" s="6" t="inlineStr">
+        <is>
+          <t>かすか</t>
+        </is>
+      </c>
+      <c r="C479" s="6" t="inlineStr">
+        <is>
+          <t>かすか (微か)</t>
+        </is>
+      </c>
+      <c r="D479" s="7" t="inlineStr">
+        <is>
+          <t>Thoang thoảng, mờ nhạt, le lói, loáng thoáng</t>
+        </is>
+      </c>
+      <c r="E479" s="7" t="inlineStr">
+        <is>
+          <t>遠くに島がかすかに見えてきた (từ xa hòn đảo đã loáng thoáng hiện ra)</t>
+        </is>
+      </c>
+      <c r="F479" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 276] Phương án 2. Cảm nhận giác quan mong manh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="24" customHeight="1">
+      <c r="A480" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>わずか</t>
+        </is>
+      </c>
+      <c r="C480" s="3" t="inlineStr">
+        <is>
+          <t>わずか (僅か)</t>
+        </is>
+      </c>
+      <c r="D480" s="4" t="inlineStr">
+        <is>
+          <t>Vỏn vẹn, ít ỏi (số lượng tiền bạc)</t>
+        </is>
+      </c>
+      <c r="E480" s="4" t="inlineStr">
+        <is>
+          <t>財布の中にわずかなお金 (trong ví chỉ còn vỏn vẹn chút tiền)</t>
+        </is>
+      </c>
+      <c r="F480" s="4" t="inlineStr">
+        <is>
+          <t>Câu 276-1 nói về lượng tiền ít ỏi thì phải dùng わずかな.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="24" customHeight="1">
+      <c r="A481" s="8" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" s="9" t="inlineStr">
+        <is>
+          <t>短い時間</t>
+        </is>
+      </c>
+      <c r="C481" s="9" t="inlineStr">
+        <is>
+          <t>みじかいじかん</t>
+        </is>
+      </c>
+      <c r="D481" s="10" t="inlineStr">
+        <is>
+          <t>Khoảng thời gian ngắn</t>
+        </is>
+      </c>
+      <c r="E481" s="10" t="inlineStr">
+        <is>
+          <t>短い時間で乾く (khô ráo trong thời gian ngắn)</t>
+        </is>
+      </c>
+      <c r="F481" s="10" t="inlineStr">
+        <is>
+          <t>Câu 276-3 dùng sai, thời gian thì dùng 短い.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="24" customHeight="1">
+      <c r="A482" s="2" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>少し</t>
+        </is>
+      </c>
+      <c r="C482" s="3" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="D482" s="4" t="inlineStr">
+        <is>
+          <t>Sớm hơn một chút (sinh nhật)</t>
+        </is>
+      </c>
+      <c r="E482" s="4" t="inlineStr">
+        <is>
+          <t>誕生日が少し早い (ngày sinh sớm hơn một chút)</t>
+        </is>
+      </c>
+      <c r="F482" s="4" t="inlineStr">
+        <is>
+          <t>Câu 276-4 dùng sai, sinh nhật thì dùng 少し/わずかに.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="24" customHeight="1">
+      <c r="A483" s="5" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" s="6" t="inlineStr">
+        <is>
+          <t>催促</t>
+        </is>
+      </c>
+      <c r="C483" s="6" t="inlineStr">
+        <is>
+          <t>さいそく</t>
+        </is>
+      </c>
+      <c r="D483" s="7" t="inlineStr">
+        <is>
+          <t>Thúc giục, hối thúc đòi tiền/đòi nợ</t>
+        </is>
+      </c>
+      <c r="E483" s="7" t="inlineStr">
+        <is>
+          <t>催促の電話がかかってきた (bị gọi điện thoại đòi/thúc giục trả tiền nhà)</t>
+        </is>
+      </c>
+      <c r="F483" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 277] Phương án 3. Đi với `家賃/返済の催促`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="24" customHeight="1">
+      <c r="A484" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>促す</t>
+        </is>
+      </c>
+      <c r="C484" s="3" t="inlineStr">
+        <is>
+          <t>うながす</t>
+        </is>
+      </c>
+      <c r="D484" s="4" t="inlineStr">
+        <is>
+          <t>Nhắc nhở, khuyến khích làm gì</t>
+        </is>
+      </c>
+      <c r="E484" s="4" t="inlineStr">
+        <is>
+          <t>注意を促す (nhắc nhở chú ý đề phòng)</t>
+        </is>
+      </c>
+      <c r="F484" s="4" t="inlineStr">
+        <is>
+          <t>Câu 277-1 dùng sai, nhắc uống nước thì dùng 促す/呼びかける.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="24" customHeight="1">
+      <c r="A485" s="8" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" s="9" t="inlineStr">
+        <is>
+          <t>促進</t>
+        </is>
+      </c>
+      <c r="C485" s="9" t="inlineStr">
+        <is>
+          <t>そくしん</t>
+        </is>
+      </c>
+      <c r="D485" s="10" t="inlineStr">
+        <is>
+          <t>Xúc tiến, thúc đẩy giao lưu</t>
+        </is>
+      </c>
+      <c r="E485" s="10" t="inlineStr">
+        <is>
+          <t>異文化交流を促進する (thúc đẩy giao lưu văn hóa)</t>
+        </is>
+      </c>
+      <c r="F485" s="10" t="inlineStr">
+        <is>
+          <t>Câu 277-2 dùng sai, đúng phải là 交流の促進.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="24" customHeight="1">
+      <c r="A486" s="2" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>そそる</t>
+        </is>
+      </c>
+      <c r="C486" s="3" t="inlineStr">
+        <is>
+          <t>そそる</t>
+        </is>
+      </c>
+      <c r="D486" s="4" t="inlineStr">
+        <is>
+          <t>Kích thích, gợi lên (cơn thèm ăn)</t>
+        </is>
+      </c>
+      <c r="E486" s="4" t="inlineStr">
+        <is>
+          <t>食欲がそそられた (kích thích cảm giác thèm ăn)</t>
+        </is>
+      </c>
+      <c r="F486" s="4" t="inlineStr">
+        <is>
+          <t>Câu 277-4 dùng sai, đúng là 食欲がそそられる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" ht="24" customHeight="1">
+      <c r="A487" s="5" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" s="6" t="inlineStr">
+        <is>
+          <t>ものたりない</t>
+        </is>
+      </c>
+      <c r="C487" s="6" t="inlineStr">
+        <is>
+          <t>ものたりない (物足りない)</t>
+        </is>
+      </c>
+      <c r="D487" s="7" t="inlineStr">
+        <is>
+          <t>Chưa thỏa mãn, còn thiếu thiếu điều gì đó</t>
+        </is>
+      </c>
+      <c r="E487" s="7" t="inlineStr">
+        <is>
+          <t>初心者向けのクラスだとものたりなくなってきた (học lớp cơ bản thấy chưa đã/chưa thỏa mãn)</t>
+        </is>
+      </c>
+      <c r="F487" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 278] Phương án 1. Cảm giác chưa đủ đô, chưa hài lòng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="24" customHeight="1">
+      <c r="A488" s="2" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>寂しい</t>
+        </is>
+      </c>
+      <c r="C488" s="3" t="inlineStr">
+        <is>
+          <t>さびしい</t>
+        </is>
+      </c>
+      <c r="D488" s="4" t="inlineStr">
+        <is>
+          <t>Buồn bã, cô đơn hụt hẫng</t>
+        </is>
+      </c>
+      <c r="E488" s="4" t="inlineStr">
+        <is>
+          <t>みんな寂しく思っています (mọi người đều thấy buồn khi bạn chuyển trường)</t>
+        </is>
+      </c>
+      <c r="F488" s="4" t="inlineStr">
+        <is>
+          <t>Câu 278-2 bạn chuyển trường thì phải dùng 寂しい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="24" customHeight="1">
+      <c r="A489" s="8" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" s="9" t="inlineStr">
+        <is>
+          <t>不自由</t>
+        </is>
+      </c>
+      <c r="C489" s="9" t="inlineStr">
+        <is>
+          <t>ふじゆう</t>
+        </is>
+      </c>
+      <c r="D489" s="10" t="inlineStr">
+        <is>
+          <t>Bất tiện, thiếu thốn cơ sở vật chất</t>
+        </is>
+      </c>
+      <c r="E489" s="10" t="inlineStr">
+        <is>
+          <t>いろいろ不自由でしょう (mới sang chắc còn nhiều thiếu thốn bất tiện)</t>
+        </is>
+      </c>
+      <c r="F489" s="10" t="inlineStr">
+        <is>
+          <t>Câu 278-3 mới đến sống thì dùng 不自由/不便.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="24" customHeight="1">
+      <c r="A490" s="2" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>残念</t>
+        </is>
+      </c>
+      <c r="C490" s="3" t="inlineStr">
+        <is>
+          <t>ざんねん</t>
+        </is>
+      </c>
+      <c r="D490" s="4" t="inlineStr">
+        <is>
+          <t>Đáng tiếc</t>
+        </is>
+      </c>
+      <c r="E490" s="4" t="inlineStr">
+        <is>
+          <t>中止だなんて本当に残念だ (bị hủy thì thật là đáng tiếc)</t>
+        </is>
+      </c>
+      <c r="F490" s="4" t="inlineStr">
+        <is>
+          <t>Câu 278-4 bữa tiệc bị hủy thì dùng 残念.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="24" customHeight="1">
+      <c r="A491" s="5" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" s="6" t="inlineStr">
+        <is>
+          <t>頑丈</t>
+        </is>
+      </c>
+      <c r="C491" s="6" t="inlineStr">
+        <is>
+          <t>がんじょう</t>
+        </is>
+      </c>
+      <c r="D491" s="7" t="inlineStr">
+        <is>
+          <t>Chắc chắn, bền chắc, chịu lực tốt (đồ vật)</t>
+        </is>
+      </c>
+      <c r="E491" s="7" t="inlineStr">
+        <is>
+          <t>このいすはとても頑丈で壊れません (chiếc ghế này rất bền chắc quăng quật không hỏng)</t>
+        </is>
+      </c>
+      <c r="F491" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 279] Phương án 3. Tả bàn ghế, thân thể lực lưỡng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="24" customHeight="1">
+      <c r="A492" s="2" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>頑固</t>
+        </is>
+      </c>
+      <c r="C492" s="3" t="inlineStr">
+        <is>
+          <t>がんこ</t>
+        </is>
+      </c>
+      <c r="D492" s="4" t="inlineStr">
+        <is>
+          <t>Bảo thủ, bướng bỉnh, cứng đầu</t>
+        </is>
+      </c>
+      <c r="E492" s="4" t="inlineStr">
+        <is>
+          <t>石川さんは頑固で意見を変えない (anh Ishikawa rất cứng đầu không chịu đổi ý)</t>
+        </is>
+      </c>
+      <c r="F492" s="4" t="inlineStr">
+        <is>
+          <t>Câu 279-1 tính người không đổi ý là 頑固.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="24" customHeight="1">
+      <c r="A493" s="8" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" s="9" t="inlineStr">
+        <is>
+          <t>厳重</t>
+        </is>
+      </c>
+      <c r="C493" s="9" t="inlineStr">
+        <is>
+          <t>げんじゅう</t>
+        </is>
+      </c>
+      <c r="D493" s="10" t="inlineStr">
+        <is>
+          <t>Nghiêm ngặt, cẩn mật</t>
+        </is>
+      </c>
+      <c r="E493" s="10" t="inlineStr">
+        <is>
+          <t>書類を厳重に管理する (quản lý tài liệu một cách cẩn mật)</t>
+        </is>
+      </c>
+      <c r="F493" s="10" t="inlineStr">
+        <is>
+          <t>Câu 279-2 bảo mật tài liệu két sắt là 厳重.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="24" customHeight="1">
+      <c r="A494" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>強固</t>
+        </is>
+      </c>
+      <c r="C494" s="3" t="inlineStr">
+        <is>
+          <t>きょうこ</t>
+        </is>
+      </c>
+      <c r="D494" s="4" t="inlineStr">
+        <is>
+          <t>Vững bền, khăng khít (quan hệ tin cậy)</t>
+        </is>
+      </c>
+      <c r="E494" s="4" t="inlineStr">
+        <is>
+          <t>強固な信頼関係 (mối quan hệ tin cậy bền chặt)</t>
+        </is>
+      </c>
+      <c r="F494" s="4" t="inlineStr">
+        <is>
+          <t>Câu 279-4 niềm tin vững chắc dùng 強固/固い.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="24" customHeight="1">
+      <c r="A495" s="5" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" s="6" t="inlineStr">
+        <is>
+          <t>畳む</t>
+        </is>
+      </c>
+      <c r="C495" s="6" t="inlineStr">
+        <is>
+          <t>たたむ</t>
+        </is>
+      </c>
+      <c r="D495" s="7" t="inlineStr">
+        <is>
+          <t>Gấp, xếp lại (quần áo, ô, chiếu); dẹp tiệm</t>
+        </is>
+      </c>
+      <c r="E495" s="7" t="inlineStr">
+        <is>
+          <t>上着を小さく畳む (gấp chiếc áo khoác gọn nhỏ lại)</t>
+        </is>
+      </c>
+      <c r="F495" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 280] Phương án 2. Gấp quần áo vải vóc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="24" customHeight="1">
+      <c r="A496" s="2" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>折る</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="inlineStr">
+        <is>
+          <t>おる</t>
+        </is>
+      </c>
+      <c r="D496" s="4" t="inlineStr">
+        <is>
+          <t>Gấp giấy origami, bẻ gập cành cây</t>
+        </is>
+      </c>
+      <c r="E496" s="4" t="inlineStr">
+        <is>
+          <t>紙を折って鶴を作った (gấp giấy thành con hạc)</t>
+        </is>
+      </c>
+      <c r="F496" s="4" t="inlineStr">
+        <is>
+          <t>Câu 280-1 gấp giấy origami chim hạc phải dùng 折る.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="24" customHeight="1">
+      <c r="A497" s="8" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" s="9" t="inlineStr">
+        <is>
+          <t>束ねる</t>
+        </is>
+      </c>
+      <c r="C497" s="9" t="inlineStr">
+        <is>
+          <t>たばねる</t>
+        </is>
+      </c>
+      <c r="D497" s="10" t="inlineStr">
+        <is>
+          <t>Búi tóc, buộc tóc thành lọn</t>
+        </is>
+      </c>
+      <c r="E497" s="10" t="inlineStr">
+        <is>
+          <t>髪を束ねる (buộc tóc gọn gàng)</t>
+        </is>
+      </c>
+      <c r="F497" s="10" t="inlineStr">
+        <is>
+          <t>Câu 280-3 buộc tóc dài lên phải dùng 束ねる/結ぶ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="24" customHeight="1">
+      <c r="A498" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>腕を組む</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>うでをくむ</t>
+        </is>
+      </c>
+      <c r="D498" s="4" t="inlineStr">
+        <is>
+          <t>Khoanh tay trước ngực</t>
+        </is>
+      </c>
+      <c r="E498" s="4" t="inlineStr">
+        <is>
+          <t>腕を組んで考え込む (khoanh tay trầm tư suy nghĩ)</t>
+        </is>
+      </c>
+      <c r="F498" s="4" t="inlineStr">
+        <is>
+          <t>Câu 280-4 khoanh tay là 腕を組む.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="24" customHeight="1">
+      <c r="A499" s="5" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" s="6" t="inlineStr">
+        <is>
+          <t>合図</t>
+        </is>
+      </c>
+      <c r="C499" s="6" t="inlineStr">
+        <is>
+          <t>あいず</t>
+        </is>
+      </c>
+      <c r="D499" s="7" t="inlineStr">
+        <is>
+          <t>Ám hiệu, hiệu lệnh ra dấu</t>
+        </is>
+      </c>
+      <c r="E499" s="7" t="inlineStr">
+        <is>
+          <t>スタートの合図で一斉に走り出した (sau hiệu lệnh xuất phát đồng loạt lao về trước)</t>
+        </is>
+      </c>
+      <c r="F499" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 281] Phương án 1. Hiệu lệnh bằng còi, cờ, tay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="24" customHeight="1">
+      <c r="A500" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" s="3" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="C500" s="3" t="inlineStr">
+        <is>
+          <t>つうち</t>
+        </is>
+      </c>
+      <c r="D500" s="4" t="inlineStr">
+        <is>
+          <t>Thông báo bằng văn bản</t>
+        </is>
+      </c>
+      <c r="E500" s="4" t="inlineStr">
+        <is>
+          <t>ガス会社から点検の通知があった (có giấy báo kiểm tra của công ty gas)</t>
+        </is>
+      </c>
+      <c r="F500" s="4" t="inlineStr">
+        <is>
+          <t>Câu 281-2 thông báo công ty là 通知/お知らせ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="24" customHeight="1">
+      <c r="A501" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" s="9" t="inlineStr">
+        <is>
+          <t>足跡</t>
+        </is>
+      </c>
+      <c r="C501" s="9" t="inlineStr">
+        <is>
+          <t>あしあと</t>
+        </is>
+      </c>
+      <c r="D501" s="10" t="inlineStr">
+        <is>
+          <t>Dấu chân động vật</t>
+        </is>
+      </c>
+      <c r="E501" s="10" t="inlineStr">
+        <is>
+          <t>動物の足跡があった (có dấu chân con thú in trên đường)</t>
+        </is>
+      </c>
+      <c r="F501" s="10" t="inlineStr">
+        <is>
+          <t>Câu 281-3 dấu chân con thú là 足跡/痕跡.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="24" customHeight="1">
+      <c r="A502" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="B502" s="3" t="inlineStr">
+        <is>
+          <t>目印</t>
+        </is>
+      </c>
+      <c r="C502" s="3" t="inlineStr">
+        <is>
+          <t>めじるし</t>
+        </is>
+      </c>
+      <c r="D502" s="4" t="inlineStr">
+        <is>
+          <t>Dấu mốc, vật đánh dấu ghi nhớ</t>
+        </is>
+      </c>
+      <c r="E502" s="4" t="inlineStr">
+        <is>
+          <t>目印をつけておく (đánh dấu mốc để khỏi quên)</t>
+        </is>
+      </c>
+      <c r="F502" s="4" t="inlineStr">
+        <is>
+          <t>Câu 281-4 đánh dấu chỗ gieo hạt là 目印.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="24" customHeight="1">
+      <c r="A503" s="5" t="n">
+        <v>502</v>
+      </c>
+      <c r="B503" s="6" t="inlineStr">
+        <is>
+          <t>こつこつ</t>
+        </is>
+      </c>
+      <c r="C503" s="6" t="inlineStr">
+        <is>
+          <t>こつこつ</t>
+        </is>
+      </c>
+      <c r="D503" s="7" t="inlineStr">
+        <is>
+          <t>Cần cù, miệt mài, kiên trì từng chút một</t>
+        </is>
+      </c>
+      <c r="E503" s="7" t="inlineStr">
+        <is>
+          <t>毎日こつこつと勉強してきた (chăm chỉ miệt mài học tập mỗi ngày)</t>
+        </is>
+      </c>
+      <c r="F503" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 282] Phương án 4. Đi với `こつこつ勉強する/働く/貯金する`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="24" customHeight="1">
+      <c r="A504" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>だんだん</t>
+        </is>
+      </c>
+      <c r="C504" s="3" t="inlineStr">
+        <is>
+          <t>だんだん</t>
+        </is>
+      </c>
+      <c r="D504" s="4" t="inlineStr">
+        <is>
+          <t>Dần dần, từng bước hiểu ra</t>
+        </is>
+      </c>
+      <c r="E504" s="4" t="inlineStr">
+        <is>
+          <t>だんだんわかってきた (dần dần đã hiểu ra được)</t>
+        </is>
+      </c>
+      <c r="F504" s="4" t="inlineStr">
+        <is>
+          <t>Câu 282-1 hiểu ra từ từ dùng だんだん/次第に.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" ht="24" customHeight="1">
+      <c r="A505" s="8" t="n">
+        <v>504</v>
+      </c>
+      <c r="B505" s="9" t="inlineStr">
+        <is>
+          <t>少しずつ</t>
+        </is>
+      </c>
+      <c r="C505" s="9" t="inlineStr">
+        <is>
+          <t>すこしずつ</t>
+        </is>
+      </c>
+      <c r="D505" s="10" t="inlineStr">
+        <is>
+          <t>Từng chút một (ăn uống)</t>
+        </is>
+      </c>
+      <c r="E505" s="10" t="inlineStr">
+        <is>
+          <t>熱いから少しずつ食べた (nóng nên ăn từng tí một)</t>
+        </is>
+      </c>
+      <c r="F505" s="10" t="inlineStr">
+        <is>
+          <t>Câu 282-2 dùng 少しずつ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" ht="24" customHeight="1">
+      <c r="A506" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="B506" s="3" t="inlineStr">
+        <is>
+          <t>ぐんぐん</t>
+        </is>
+      </c>
+      <c r="C506" s="3" t="inlineStr">
+        <is>
+          <t>ぐんぐん</t>
+        </is>
+      </c>
+      <c r="D506" s="4" t="inlineStr">
+        <is>
+          <t>Tăng vùn vụt (nhiệt độ)</t>
+        </is>
+      </c>
+      <c r="E506" s="4" t="inlineStr">
+        <is>
+          <t>気温がぐんぐん上がり始めた (nhiệt độ tăng nhanh vùn vụt)</t>
+        </is>
+      </c>
+      <c r="F506" s="4" t="inlineStr">
+        <is>
+          <t>Câu 282-3 nhiệt độ tăng nhanh dùng ぐんぐん.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" ht="24" customHeight="1">
+      <c r="A507" s="5" t="n">
+        <v>506</v>
+      </c>
+      <c r="B507" s="6" t="inlineStr">
+        <is>
+          <t>縮む</t>
+        </is>
+      </c>
+      <c r="C507" s="6" t="inlineStr">
+        <is>
+          <t>ちぢむ</t>
+        </is>
+      </c>
+      <c r="D507" s="7" t="inlineStr">
+        <is>
+          <t>Co lại, rút ngắn chiều dài/kích thước</t>
+        </is>
+      </c>
+      <c r="E507" s="7" t="inlineStr">
+        <is>
+          <t>セーターを洗ったら縮んで着られなくなった (giặt áo len xong bị co lại không mặc vừa)</t>
+        </is>
+      </c>
+      <c r="F507" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 283] Phương án 3. Đồ len, vải vóc bị co rút.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="24" customHeight="1">
+      <c r="A508" s="2" t="n">
+        <v>507</v>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>つぶれる</t>
+        </is>
+      </c>
+      <c r="C508" s="3" t="inlineStr">
+        <is>
+          <t>つぶれる</t>
+        </is>
+      </c>
+      <c r="D508" s="4" t="inlineStr">
+        <is>
+          <t>Bẹp dúm, bẹp rúm do đè nặng</t>
+        </is>
+      </c>
+      <c r="E508" s="4" t="inlineStr">
+        <is>
+          <t>重さで箱がつぶれた (hộp bị đè bẹp dúm)</t>
+        </is>
+      </c>
+      <c r="F508" s="4" t="inlineStr">
+        <is>
+          <t>Câu 283-1 hộp giấy bị đè bẹp là つぶれる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="24" customHeight="1">
+      <c r="A509" s="8" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" s="9" t="inlineStr">
+        <is>
+          <t>短くなる</t>
+        </is>
+      </c>
+      <c r="C509" s="9" t="inlineStr">
+        <is>
+          <t>みじかくなる</t>
+        </is>
+      </c>
+      <c r="D509" s="10" t="inlineStr">
+        <is>
+          <t>Ngắn đi (bút chì)</t>
+        </is>
+      </c>
+      <c r="E509" s="10" t="inlineStr">
+        <is>
+          <t>鉛筆が短くなった (bút chì đã bị ngắn cũn)</t>
+        </is>
+      </c>
+      <c r="F509" s="10" t="inlineStr">
+        <is>
+          <t>Câu 283-2 bút chì dùng mòn là 短くなる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="24" customHeight="1">
+      <c r="A510" s="2" t="n">
+        <v>509</v>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>狭くなる</t>
+        </is>
+      </c>
+      <c r="C510" s="3" t="inlineStr">
+        <is>
+          <t>せまくなる</t>
+        </is>
+      </c>
+      <c r="D510" s="4" t="inlineStr">
+        <is>
+          <t>Hẹp lại (diện tích sân vườn)</t>
+        </is>
+      </c>
+      <c r="E510" s="4" t="inlineStr">
+        <is>
+          <t>庭が狭くなった (sân vườn bị hẹp lại)</t>
+        </is>
+      </c>
+      <c r="F510" s="4" t="inlineStr">
+        <is>
+          <t>Câu 283-4 diện tích đất vườn thu hẹp là 狭くなる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="24" customHeight="1">
+      <c r="A511" s="5" t="n">
+        <v>510</v>
+      </c>
+      <c r="B511" s="6" t="inlineStr">
+        <is>
+          <t>会見</t>
+        </is>
+      </c>
+      <c r="C511" s="6" t="inlineStr">
+        <is>
+          <t>かいけん</t>
+        </is>
+      </c>
+      <c r="D511" s="7" t="inlineStr">
+        <is>
+          <t>Họp báo, tiếp kiến báo giới chính thức</t>
+        </is>
+      </c>
+      <c r="E511" s="7" t="inlineStr">
+        <is>
+          <t>社長は会見を開き、質問に答えた (giám đốc tổ chức họp báo trả lời báo giới)</t>
+        </is>
+      </c>
+      <c r="F511" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 284] Phương án 2. Đi với `記者会見を開く`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="24" customHeight="1">
+      <c r="A512" s="2" t="n">
+        <v>511</v>
+      </c>
+      <c r="B512" s="3" t="inlineStr">
+        <is>
+          <t>面接</t>
+        </is>
+      </c>
+      <c r="C512" s="3" t="inlineStr">
+        <is>
+          <t>めんせつ</t>
+        </is>
+      </c>
+      <c r="D512" s="4" t="inlineStr">
+        <is>
+          <t>Phỏng vấn xin việc làm</t>
+        </is>
+      </c>
+      <c r="E512" s="4" t="inlineStr">
+        <is>
+          <t>アルバイトの面接がある (có buổi phỏng vấn xin việc làm thêm)</t>
+        </is>
+      </c>
+      <c r="F512" s="4" t="inlineStr">
+        <is>
+          <t>Câu 284-1 phỏng vấn việc làm là 面接.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="24" customHeight="1">
+      <c r="A513" s="8" t="n">
+        <v>512</v>
+      </c>
+      <c r="B513" s="9" t="inlineStr">
+        <is>
+          <t>再会</t>
+        </is>
+      </c>
+      <c r="C513" s="9" t="inlineStr">
+        <is>
+          <t>さいかい</t>
+        </is>
+      </c>
+      <c r="D513" s="10" t="inlineStr">
+        <is>
+          <t>Tái ngộ, gặp lại bạn cũ</t>
+        </is>
+      </c>
+      <c r="E513" s="10" t="inlineStr">
+        <is>
+          <t>同級生との再会を楽しむ (tận hưởng niềm vui tái ngộ bạn bè cũ)</t>
+        </is>
+      </c>
+      <c r="F513" s="10" t="inlineStr">
+        <is>
+          <t>Câu 284-3 gặp lại bạn bè sau 10 năm là 再会.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="24" customHeight="1">
+      <c r="A514" s="2" t="n">
+        <v>513</v>
+      </c>
+      <c r="B514" s="3" t="inlineStr">
+        <is>
+          <t>取材</t>
+        </is>
+      </c>
+      <c r="C514" s="3" t="inlineStr">
+        <is>
+          <t>しゅざい</t>
+        </is>
+      </c>
+      <c r="D514" s="4" t="inlineStr">
+        <is>
+          <t>Thu thập thông tin, phỏng vấn ghi hình báo chí</t>
+        </is>
+      </c>
+      <c r="E514" s="4" t="inlineStr">
+        <is>
+          <t>テレビ番組の取材を受けた (được chương trình truyền hình phỏng vấn)</t>
+        </is>
+      </c>
+      <c r="F514" s="4" t="inlineStr">
+        <is>
+          <t>Câu 284-4 nhận phỏng vấn truyền hình là 取材.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="24" customHeight="1">
+      <c r="A515" s="5" t="n">
+        <v>514</v>
+      </c>
+      <c r="B515" s="6" t="inlineStr">
+        <is>
+          <t>支持</t>
+        </is>
+      </c>
+      <c r="C515" s="6" t="inlineStr">
+        <is>
+          <t>しじ</t>
+        </is>
+      </c>
+      <c r="D515" s="7" t="inlineStr">
+        <is>
+          <t>Ủng hộ, tán thành (chính trị gia, chính sách)</t>
+        </is>
+      </c>
+      <c r="E515" s="7" t="inlineStr">
+        <is>
+          <t>田中市長は市民から多くの支持を集めている (thị trưởng Tanaka nhận được nhiều sự ủng hộ của dân chúng)</t>
+        </is>
+      </c>
+      <c r="F515" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 285] Phương án 3. Đi với `支持を集める/支持率`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="24" customHeight="1">
+      <c r="A516" s="2" t="n">
+        <v>515</v>
+      </c>
+      <c r="B516" s="3" t="inlineStr">
+        <is>
+          <t>応援</t>
+        </is>
+      </c>
+      <c r="C516" s="3" t="inlineStr">
+        <is>
+          <t>おうえん</t>
+        </is>
+      </c>
+      <c r="D516" s="4" t="inlineStr">
+        <is>
+          <t>Cổ vũ thể thao</t>
+        </is>
+      </c>
+      <c r="E516" s="4" t="inlineStr">
+        <is>
+          <t>息子の応援に行く (đi cổ vũ cho con trai đá bóng)</t>
+        </is>
+      </c>
+      <c r="F516" s="4" t="inlineStr">
+        <is>
+          <t>Câu 285-1 cổ vũ thể thao dùng 応援.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="24" customHeight="1">
+      <c r="A517" s="8" t="n">
+        <v>516</v>
+      </c>
+      <c r="B517" s="9" t="inlineStr">
+        <is>
+          <t>許可</t>
+        </is>
+      </c>
+      <c r="C517" s="9" t="inlineStr">
+        <is>
+          <t>きょか</t>
+        </is>
+      </c>
+      <c r="D517" s="10" t="inlineStr">
+        <is>
+          <t>Cấp phép, cho phép chụp ảnh</t>
+        </is>
+      </c>
+      <c r="E517" s="10" t="inlineStr">
+        <is>
+          <t>撮影の許可を得る (xin được giấy phép chụp hình)</t>
+        </is>
+      </c>
+      <c r="F517" s="10" t="inlineStr">
+        <is>
+          <t>Câu 285-2 được phép chụp ảnh là 許可.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="24" customHeight="1">
+      <c r="A518" s="2" t="n">
+        <v>517</v>
+      </c>
+      <c r="B518" s="3" t="inlineStr">
+        <is>
+          <t>歓迎</t>
+        </is>
+      </c>
+      <c r="C518" s="3" t="inlineStr">
+        <is>
+          <t>かんげい</t>
+        </is>
+      </c>
+      <c r="D518" s="4" t="inlineStr">
+        <is>
+          <t>Hoan nghênh, chào đón nồng nhiệt</t>
+        </is>
+      </c>
+      <c r="E518" s="4" t="inlineStr">
+        <is>
+          <t>先生方に温かく歓迎された (được các thầy cô chào đón nồng nhiệt)</t>
+        </is>
+      </c>
+      <c r="F518" s="4" t="inlineStr">
+        <is>
+          <t>Câu 285-4 thầy cô chào đón dùng 歓迎.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519" ht="24" customHeight="1">
+      <c r="A519" s="5" t="n">
+        <v>518</v>
+      </c>
+      <c r="B519" s="6" t="inlineStr">
+        <is>
+          <t>妥当</t>
+        </is>
+      </c>
+      <c r="C519" s="6" t="inlineStr">
+        <is>
+          <t>だとう</t>
+        </is>
+      </c>
+      <c r="D519" s="7" t="inlineStr">
+        <is>
+          <t>Hợp lý, thỏa đáng, đúng mực</t>
+        </is>
+      </c>
+      <c r="E519" s="7" t="inlineStr">
+        <is>
+          <t>妥当な金額だと思う (tôi nghĩ đây là số tiền hợp lý thỏa đáng)</t>
+        </is>
+      </c>
+      <c r="F519" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 286] Phương án 1. Đi với `妥当な判断/妥当な金額`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520" ht="24" customHeight="1">
+      <c r="A520" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="B520" s="3" t="inlineStr">
+        <is>
+          <t>好都合</t>
+        </is>
+      </c>
+      <c r="C520" s="3" t="inlineStr">
+        <is>
+          <t>こうつごう</t>
+        </is>
+      </c>
+      <c r="D520" s="4" t="inlineStr">
+        <is>
+          <t>Thuận tiện, vừa vặn lịch trình</t>
+        </is>
+      </c>
+      <c r="E520" s="4" t="inlineStr">
+        <is>
+          <t>私には好都合だった (vừa hay lại rất thuận lợi cho tôi)</t>
+        </is>
+      </c>
+      <c r="F520" s="4" t="inlineStr">
+        <is>
+          <t>Câu 286-2 tiện cho bản thân dùng 好都合/ありがたい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521" ht="24" customHeight="1">
+      <c r="A521" s="8" t="n">
+        <v>520</v>
+      </c>
+      <c r="B521" s="9" t="inlineStr">
+        <is>
+          <t>絶好</t>
+        </is>
+      </c>
+      <c r="C521" s="9" t="inlineStr">
+        <is>
+          <t>ぜっこう</t>
+        </is>
+      </c>
+      <c r="D521" s="10" t="inlineStr">
+        <is>
+          <t>Tuyệt vời, cực kỳ lý tưởng (thời tiết)</t>
+        </is>
+      </c>
+      <c r="E521" s="10" t="inlineStr">
+        <is>
+          <t>絶好の天気になった (thời tiết trở nên tuyệt hảo)</t>
+        </is>
+      </c>
+      <c r="F521" s="10" t="inlineStr">
+        <is>
+          <t>Câu 286-3 thời tiết đẹp dùng 絶好/うってつけ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522" ht="24" customHeight="1">
+      <c r="A522" s="2" t="n">
+        <v>521</v>
+      </c>
+      <c r="B522" s="3" t="inlineStr">
+        <is>
+          <t>ぴったり</t>
+        </is>
+      </c>
+      <c r="C522" s="3" t="inlineStr">
+        <is>
+          <t>ぴったり</t>
+        </is>
+      </c>
+      <c r="D522" s="4" t="inlineStr">
+        <is>
+          <t>Hoàn toàn khớp với tâm trạng</t>
+        </is>
+      </c>
+      <c r="E522" s="4" t="inlineStr">
+        <is>
+          <t>私の気持ちにぴったりだ (rất khớp với tâm trạng của tôi)</t>
+        </is>
+      </c>
+      <c r="F522" s="4" t="inlineStr">
+        <is>
+          <t>Câu 286-4 bài hát hợp tâm trạng dùng ぴったり.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523" ht="24" customHeight="1">
+      <c r="A523" s="5" t="n">
+        <v>522</v>
+      </c>
+      <c r="B523" s="6" t="inlineStr">
+        <is>
+          <t>言い訳</t>
+        </is>
+      </c>
+      <c r="C523" s="6" t="inlineStr">
+        <is>
+          <t>いいわけ</t>
+        </is>
+      </c>
+      <c r="D523" s="7" t="inlineStr">
+        <is>
+          <t>Biện hộ, viện cớ, bào chữa lỗi lầm</t>
+        </is>
+      </c>
+      <c r="E523" s="7" t="inlineStr">
+        <is>
+          <t>仕事で失敗すると必ず言い訳をする (cứ thất bại trong công việc là lại viện cớ bao biện)</t>
+        </is>
+      </c>
+      <c r="F523" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 287] Phương án 3. Đi với `言い訳をする` (tiêu cực).</t>
+        </is>
+      </c>
+    </row>
+    <row r="524" ht="24" customHeight="1">
+      <c r="A524" s="2" t="n">
+        <v>523</v>
+      </c>
+      <c r="B524" s="3" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="C524" s="3" t="inlineStr">
+        <is>
+          <t>せつめい</t>
+        </is>
+      </c>
+      <c r="D524" s="4" t="inlineStr">
+        <is>
+          <t>Giải thích, thuyết minh</t>
+        </is>
+      </c>
+      <c r="E524" s="4" t="inlineStr">
+        <is>
+          <t>きちんと説明をした (đã giải thích rành mạch rõ ràng)</t>
+        </is>
+      </c>
+      <c r="F524" s="4" t="inlineStr">
+        <is>
+          <t>Câu 287-1,2 giải thích đề xuất/bài học dùng 説明.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525" ht="24" customHeight="1">
+      <c r="A525" s="8" t="n">
+        <v>524</v>
+      </c>
+      <c r="B525" s="9" t="inlineStr">
+        <is>
+          <t>案内</t>
+        </is>
+      </c>
+      <c r="C525" s="9" t="inlineStr">
+        <is>
+          <t>あんない</t>
+        </is>
+      </c>
+      <c r="D525" s="10" t="inlineStr">
+        <is>
+          <t>Hướng dẫn khám bệnh</t>
+        </is>
+      </c>
+      <c r="E525" s="10" t="inlineStr">
+        <is>
+          <t>検査内容について説明/案内してもらった (được bác sĩ giải thích quy trình khám)</t>
+        </is>
+      </c>
+      <c r="F525" s="10" t="inlineStr">
+        <is>
+          <t>Câu 287-4 giải thích y tế dùng 説明.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="24" customHeight="1">
+      <c r="A526" s="5" t="n">
+        <v>525</v>
+      </c>
+      <c r="B526" s="6" t="inlineStr">
+        <is>
+          <t>手軽</t>
+        </is>
+      </c>
+      <c r="C526" s="6" t="inlineStr">
+        <is>
+          <t>てがる</t>
+        </is>
+      </c>
+      <c r="D526" s="7" t="inlineStr">
+        <is>
+          <t>Đơn giản, tiện lợi, không mất công</t>
+        </is>
+      </c>
+      <c r="E526" s="7" t="inlineStr">
+        <is>
+          <t>自宅で手軽にできるので人気がある (tiện lợi tập ở nhà không cần dụng cụ nên rất được ưa chuộng)</t>
+        </is>
+      </c>
+      <c r="F526" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 288] Phương án 1. Đi với `手軽にできる/手軽な料理`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="24" customHeight="1">
+      <c r="A527" s="8" t="n">
+        <v>526</v>
+      </c>
+      <c r="B527" s="9" t="inlineStr">
+        <is>
+          <t>簡単</t>
+        </is>
+      </c>
+      <c r="C527" s="9" t="inlineStr">
+        <is>
+          <t>かんたん</t>
+        </is>
+      </c>
+      <c r="D527" s="10" t="inlineStr">
+        <is>
+          <t>Đơn giản, ngắn gọn</t>
+        </is>
+      </c>
+      <c r="E527" s="10" t="inlineStr">
+        <is>
+          <t>簡単な自己紹介 (bài tự giới thiệu ngắn gọn)</t>
+        </is>
+      </c>
+      <c r="F527" s="10" t="inlineStr">
+        <is>
+          <t>Câu 288-2 tự giới thiệu 1 phút dùng 簡単な/手短な.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="24" customHeight="1">
+      <c r="A528" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="B528" s="3" t="inlineStr">
+        <is>
+          <t>略装</t>
+        </is>
+      </c>
+      <c r="C528" s="3" t="inlineStr">
+        <is>
+          <t>りゃくそう</t>
+        </is>
+      </c>
+      <c r="D528" s="4" t="inlineStr">
+        <is>
+          <t>Trang phục thường ngày, thoải mái</t>
+        </is>
+      </c>
+      <c r="E528" s="4" t="inlineStr">
+        <is>
+          <t>カジュアルな服装 (trang phục thoải mái, giản dị)</t>
+        </is>
+      </c>
+      <c r="F528" s="4" t="inlineStr">
+        <is>
+          <t>Câu 288-3 quần áo tiệc dùng カジュアルな/略装.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="24" customHeight="1">
+      <c r="A529" s="8" t="n">
+        <v>528</v>
+      </c>
+      <c r="B529" s="9" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="C529" s="9" t="inlineStr">
+        <is>
+          <t>ようい</t>
+        </is>
+      </c>
+      <c r="D529" s="10" t="inlineStr">
+        <is>
+          <t>Dễ dàng giành chiến thắng</t>
+        </is>
+      </c>
+      <c r="E529" s="10" t="inlineStr">
+        <is>
+          <t>簡単に勝てる (tưởng là sẽ dễ dàng thắng trận)</t>
+        </is>
+      </c>
+      <c r="F529" s="10" t="inlineStr">
+        <is>
+          <t>Câu 288-4 thắng trận dùng 簡単に/たやすく.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530" ht="24" customHeight="1">
+      <c r="A530" s="5" t="n">
+        <v>529</v>
+      </c>
+      <c r="B530" s="6" t="inlineStr">
+        <is>
+          <t>温暖</t>
+        </is>
+      </c>
+      <c r="C530" s="6" t="inlineStr">
+        <is>
+          <t>おんだん</t>
+        </is>
+      </c>
+      <c r="D530" s="7" t="inlineStr">
+        <is>
+          <t>Ôn hòa, ấm áp (khí hậu thiên nhiên)</t>
+        </is>
+      </c>
+      <c r="E530" s="7" t="inlineStr">
+        <is>
+          <t>この地方は温暖で暮らしやすい (vùng này khí hậu ôn hòa dễ sống)</t>
+        </is>
+      </c>
+      <c r="F530" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 289] Phương án 3. Đi với `温暖な気候/温暖化`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="24" customHeight="1">
+      <c r="A531" s="8" t="n">
+        <v>530</v>
+      </c>
+      <c r="B531" s="9" t="inlineStr">
+        <is>
+          <t>温厚</t>
+        </is>
+      </c>
+      <c r="C531" s="9" t="inlineStr">
+        <is>
+          <t>おんこう</t>
+        </is>
+      </c>
+      <c r="D531" s="10" t="inlineStr">
+        <is>
+          <t>Hiền lành, đôn hậu, hòa nhã (tính cách)</t>
+        </is>
+      </c>
+      <c r="E531" s="10" t="inlineStr">
+        <is>
+          <t>温厚な性格の人 (người có tính tình đôn hậu hiền hòa)</t>
+        </is>
+      </c>
+      <c r="F531" s="10" t="inlineStr">
+        <is>
+          <t>Câu 289-1 tính cách con người phải dùng 温厚.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532" ht="24" customHeight="1">
+      <c r="A532" s="2" t="n">
+        <v>531</v>
+      </c>
+      <c r="B532" s="3" t="inlineStr">
+        <is>
+          <t>温かい</t>
+        </is>
+      </c>
+      <c r="C532" s="3" t="inlineStr">
+        <is>
+          <t>あたたかい</t>
+        </is>
+      </c>
+      <c r="D532" s="4" t="inlineStr">
+        <is>
+          <t>Nóng hổi, ấm nóng (thức ăn)</t>
+        </is>
+      </c>
+      <c r="E532" s="4" t="inlineStr">
+        <is>
+          <t>温かいうちに召し上がってください (hãy dùng bữa khi đồ ăn còn ấm nóng)</t>
+        </is>
+      </c>
+      <c r="F532" s="4" t="inlineStr">
+        <is>
+          <t>Câu 289-2 thức ăn ấm nóng dùng 温かい.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533" ht="24" customHeight="1">
+      <c r="A533" s="8" t="n">
+        <v>532</v>
+      </c>
+      <c r="B533" s="9" t="inlineStr">
+        <is>
+          <t>暖か</t>
+        </is>
+      </c>
+      <c r="C533" s="9" t="inlineStr">
+        <is>
+          <t>あたたか</t>
+        </is>
+      </c>
+      <c r="D533" s="10" t="inlineStr">
+        <is>
+          <t>Ấm áp (nhiệt độ trong phòng)</t>
+        </is>
+      </c>
+      <c r="E533" s="10" t="inlineStr">
+        <is>
+          <t>部屋の中が暖かくなって (bật điều hòa phòng ấm áp lên)</t>
+        </is>
+      </c>
+      <c r="F533" s="10" t="inlineStr">
+        <is>
+          <t>Câu 289-4 nhiệt độ phòng dùng 暖かく.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534" ht="24" customHeight="1">
+      <c r="A534" s="5" t="n">
+        <v>533</v>
+      </c>
+      <c r="B534" s="6" t="inlineStr">
+        <is>
+          <t>振り向く</t>
+        </is>
+      </c>
+      <c r="C534" s="6" t="inlineStr">
+        <is>
+          <t>ふりむく</t>
+        </is>
+      </c>
+      <c r="D534" s="7" t="inlineStr">
+        <is>
+          <t>Ngoái đầu lại phía sau; quan tâm đến</t>
+        </is>
+      </c>
+      <c r="E534" s="7" t="inlineStr">
+        <is>
+          <t>後ろから呼ばれたので振り向いたら、課長だった (nghe gọi đằng sau ngoái đầu lại thì hóa ra là trưởng nhóm)</t>
+        </is>
+      </c>
+      <c r="F534" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 290] Phương án 1. Quay đầu nhìn lại phía sau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535" ht="24" customHeight="1">
+      <c r="A535" s="8" t="n">
+        <v>534</v>
+      </c>
+      <c r="B535" s="9" t="inlineStr">
+        <is>
+          <t>左右を見る</t>
+        </is>
+      </c>
+      <c r="C535" s="9" t="inlineStr">
+        <is>
+          <t>さゆうをみる</t>
+        </is>
+      </c>
+      <c r="D535" s="10" t="inlineStr">
+        <is>
+          <t>Nhìn trái ngó phải</t>
+        </is>
+      </c>
+      <c r="E535" s="10" t="inlineStr">
+        <is>
+          <t>左右を確認する (ngó trước nhìn sau xem có xe không)</t>
+        </is>
+      </c>
+      <c r="F535" s="10" t="inlineStr">
+        <is>
+          <t>Câu 290-2 sang đường nhìn hai bên dùng 左右を見る.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536" ht="24" customHeight="1">
+      <c r="A536" s="2" t="n">
+        <v>535</v>
+      </c>
+      <c r="B536" s="3" t="inlineStr">
+        <is>
+          <t>見上げる</t>
+        </is>
+      </c>
+      <c r="C536" s="3" t="inlineStr">
+        <is>
+          <t>みあげる</t>
+        </is>
+      </c>
+      <c r="D536" s="4" t="inlineStr">
+        <is>
+          <t>Ngước mắt nhìn lên trên</t>
+        </is>
+      </c>
+      <c r="E536" s="4" t="inlineStr">
+        <is>
+          <t>空を見上げる (ngước nhìn lên bầu trời)</t>
+        </is>
+      </c>
+      <c r="F536" s="4" t="inlineStr">
+        <is>
+          <t>Câu 290-3 nhìn lên trời dùng 見上げる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537" ht="24" customHeight="1">
+      <c r="A537" s="8" t="n">
+        <v>536</v>
+      </c>
+      <c r="B537" s="9" t="inlineStr">
+        <is>
+          <t>うつむく</t>
+        </is>
+      </c>
+      <c r="C537" s="9" t="inlineStr">
+        <is>
+          <t>うつむく</t>
+        </is>
+      </c>
+      <c r="D537" s="10" t="inlineStr">
+        <is>
+          <t>Cúi gằm mặt xuống đất</t>
+        </is>
+      </c>
+      <c r="E537" s="10" t="inlineStr">
+        <is>
+          <t>恥ずかしそうにうつむいた (ngượng ngùng cúi gằm mặt xuống)</t>
+        </is>
+      </c>
+      <c r="F537" s="10" t="inlineStr">
+        <is>
+          <t>Câu 290-4 xấu hổ nhìn xuống dùng うつむく/下を向く.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="24" customHeight="1">
+      <c r="A538" s="5" t="n">
+        <v>537</v>
+      </c>
+      <c r="B538" s="6" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="C538" s="6" t="inlineStr">
+        <is>
+          <t>ようと</t>
+        </is>
+      </c>
+      <c r="D538" s="7" t="inlineStr">
+        <is>
+          <t>Công dụng, mục đích sử dụng (đồ vật/tiền)</t>
+        </is>
+      </c>
+      <c r="E538" s="7" t="inlineStr">
+        <is>
+          <t>本来の用途ではないが、花瓶にしてもいい (dù không phải công dụng gốc nhưng cắm hoa vẫn được)</t>
+        </is>
+      </c>
+      <c r="F538" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 291] Phương án 4. Mục đích ứng dụng của vật thể.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539" ht="24" customHeight="1">
+      <c r="A539" s="8" t="n">
+        <v>538</v>
+      </c>
+      <c r="B539" s="9" t="inlineStr">
+        <is>
+          <t>使い方</t>
+        </is>
+      </c>
+      <c r="C539" s="9" t="inlineStr">
+        <is>
+          <t>つかいかた</t>
+        </is>
+      </c>
+      <c r="D539" s="10" t="inlineStr">
+        <is>
+          <t>Cách phân bổ thời gian</t>
+        </is>
+      </c>
+      <c r="E539" s="10" t="inlineStr">
+        <is>
+          <t>時間の使い方を工夫する (sắp xếp cách dùng thời gian hợp lý)</t>
+        </is>
+      </c>
+      <c r="F539" s="10" t="inlineStr">
+        <is>
+          <t>Câu 291-1 thời gian thì dùng 使い方/配分.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="24" customHeight="1">
+      <c r="A540" s="2" t="n">
+        <v>539</v>
+      </c>
+      <c r="B540" s="3" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="C540" s="3" t="inlineStr">
+        <is>
+          <t>やくわり</t>
+        </is>
+      </c>
+      <c r="D540" s="4" t="inlineStr">
+        <is>
+          <t>Vai trò, nhiệm vụ được giao</t>
+        </is>
+      </c>
+      <c r="E540" s="4" t="inlineStr">
+        <is>
+          <t>私の役割は新入社員の指導だ (vai trò của tôi là hướng dẫn người mới)</t>
+        </is>
+      </c>
+      <c r="F540" s="4" t="inlineStr">
+        <is>
+          <t>Câu 291-2 vai trò con người dùng 役割.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="24" customHeight="1">
+      <c r="A541" s="8" t="n">
+        <v>540</v>
+      </c>
+      <c r="B541" s="9" t="inlineStr">
+        <is>
+          <t>分野</t>
+        </is>
+      </c>
+      <c r="C541" s="9" t="inlineStr">
+        <is>
+          <t>ぶんや</t>
+        </is>
+      </c>
+      <c r="D541" s="10" t="inlineStr">
+        <is>
+          <t>Lĩnh vực áp dụng tài năng</t>
+        </is>
+      </c>
+      <c r="E541" s="10" t="inlineStr">
+        <is>
+          <t>多くの分野で生かされる (tài năng được phát huy ở nhiều lĩnh vực)</t>
+        </is>
+      </c>
+      <c r="F541" s="10" t="inlineStr">
+        <is>
+          <t>Câu 291-3 tài năng phát huy ở các 分野/場面.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="24" customHeight="1">
+      <c r="A542" s="5" t="n">
+        <v>541</v>
+      </c>
+      <c r="B542" s="6" t="inlineStr">
+        <is>
+          <t>甘やかす</t>
+        </is>
+      </c>
+      <c r="C542" s="6" t="inlineStr">
+        <is>
+          <t>あまやかす</t>
+        </is>
+      </c>
+      <c r="D542" s="7" t="inlineStr">
+        <is>
+          <t>Nuông chiều, chiều chuộng quá mức (con cái)</t>
+        </is>
+      </c>
+      <c r="E542" s="7" t="inlineStr">
+        <is>
+          <t>親に甘やかされて育った (lớn lên trong sự nuông chiều của bố mẹ)</t>
+        </is>
+      </c>
+      <c r="F542" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 292] Phương án 2. Chiều chuộng trẻ sinh hư.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="24" customHeight="1">
+      <c r="A543" s="8" t="n">
+        <v>542</v>
+      </c>
+      <c r="B543" s="9" t="inlineStr">
+        <is>
+          <t>易化</t>
+        </is>
+      </c>
+      <c r="C543" s="9" t="inlineStr">
+        <is>
+          <t>いか</t>
+        </is>
+      </c>
+      <c r="D543" s="10" t="inlineStr">
+        <is>
+          <t>Làm cho đề thi dễ hơn</t>
+        </is>
+      </c>
+      <c r="E543" s="10" t="inlineStr">
+        <is>
+          <t>内容が簡単になっている (nội dung đề thi dễ hơn năm ngoái)</t>
+        </is>
+      </c>
+      <c r="F543" s="10" t="inlineStr">
+        <is>
+          <t>Câu 292-1 đề thi giảm độ khó dùng 易しくなる/簡単になる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544" ht="24" customHeight="1">
+      <c r="A544" s="2" t="n">
+        <v>543</v>
+      </c>
+      <c r="B544" s="3" t="inlineStr">
+        <is>
+          <t>甘く見る</t>
+        </is>
+      </c>
+      <c r="C544" s="3" t="inlineStr">
+        <is>
+          <t>あまくみる</t>
+        </is>
+      </c>
+      <c r="D544" s="4" t="inlineStr">
+        <is>
+          <t>Xem nhẹ, coi thường bệnh cảm</t>
+        </is>
+      </c>
+      <c r="E544" s="4" t="inlineStr">
+        <is>
+          <t>風邪を甘く見ないほうがいい (đừng có xem thường bệnh cảm cúm)</t>
+        </is>
+      </c>
+      <c r="F544" s="4" t="inlineStr">
+        <is>
+          <t>Câu 292-2 coi nhẹ dùng 甘く見る/油断する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="24" customHeight="1">
+      <c r="A545" s="8" t="n">
+        <v>544</v>
+      </c>
+      <c r="B545" s="9" t="inlineStr">
+        <is>
+          <t>甘くする</t>
+        </is>
+      </c>
+      <c r="C545" s="9" t="inlineStr">
+        <is>
+          <t>あまくする</t>
+        </is>
+      </c>
+      <c r="D545" s="10" t="inlineStr">
+        <is>
+          <t>Làm ngọt nước uống</t>
+        </is>
+      </c>
+      <c r="E545" s="10" t="inlineStr">
+        <is>
+          <t>コーヒーを甘くした (cho đường làm cà phê ngọt hơn)</t>
+        </is>
+      </c>
+      <c r="F545" s="10" t="inlineStr">
+        <is>
+          <t>Câu 292-4 nêm ngọt thức uống dùng 甘くする.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546" ht="24" customHeight="1">
+      <c r="A546" s="5" t="n">
+        <v>545</v>
+      </c>
+      <c r="B546" s="6" t="inlineStr">
+        <is>
+          <t>行方</t>
+        </is>
+      </c>
+      <c r="C546" s="6" t="inlineStr">
+        <is>
+          <t>ゆくえ</t>
+        </is>
+      </c>
+      <c r="D546" s="7" t="inlineStr">
+        <is>
+          <t>Tung tích, dấu vết nơi chốn (người mất tích)</t>
+        </is>
+      </c>
+      <c r="E546" s="7" t="inlineStr">
+        <is>
+          <t>二人は事件に関係があるが、まだ行方が分からない (hai người dính líu đến vụ án nhưng hiện chưa rõ tung tích)</t>
+        </is>
+      </c>
+      <c r="F546" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 293] Phương án 1. Đi với `行方不明/行方が分からない`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547" ht="24" customHeight="1">
+      <c r="A547" s="8" t="n">
+        <v>546</v>
+      </c>
+      <c r="B547" s="9" t="inlineStr">
+        <is>
+          <t>行き先</t>
+        </is>
+      </c>
+      <c r="C547" s="9" t="inlineStr">
+        <is>
+          <t>いきさき</t>
+        </is>
+      </c>
+      <c r="D547" s="10" t="inlineStr">
+        <is>
+          <t>Điểm đến của xe buýt/chuyến đi</t>
+        </is>
+      </c>
+      <c r="E547" s="10" t="inlineStr">
+        <is>
+          <t>行き先を確かめる (xác nhận điểm đến của xe buýt)</t>
+        </is>
+      </c>
+      <c r="F547" s="10" t="inlineStr">
+        <is>
+          <t>Câu 293-2 điểm đến xe buýt là 行き先.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548" ht="24" customHeight="1">
+      <c r="A548" s="2" t="n">
+        <v>547</v>
+      </c>
+      <c r="B548" s="3" t="inlineStr">
+        <is>
+          <t>前方</t>
+        </is>
+      </c>
+      <c r="C548" s="3" t="inlineStr">
+        <is>
+          <t>ぜんぽう</t>
+        </is>
+      </c>
+      <c r="D548" s="4" t="inlineStr">
+        <is>
+          <t>Phía trước mặt</t>
+        </is>
+      </c>
+      <c r="E548" s="4" t="inlineStr">
+        <is>
+          <t>前方に高層ビルが見えた (phía trước mặt hiện ra tòa nhà cao tầng)</t>
+        </is>
+      </c>
+      <c r="F548" s="4" t="inlineStr">
+        <is>
+          <t>Câu 293-3 hướng nhìn phía trước dùng 前方.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549" ht="24" customHeight="1">
+      <c r="A549" s="8" t="n">
+        <v>548</v>
+      </c>
+      <c r="B549" s="9" t="inlineStr">
+        <is>
+          <t>行きつけ</t>
+        </is>
+      </c>
+      <c r="C549" s="9" t="inlineStr">
+        <is>
+          <t>いきつけ</t>
+        </is>
+      </c>
+      <c r="D549" s="10" t="inlineStr">
+        <is>
+          <t>Nơi hay lui tới</t>
+        </is>
+      </c>
+      <c r="E549" s="10" t="inlineStr">
+        <is>
+          <t>行きつけの喫茶店 (quán cà phê quen hay ghé)</t>
+        </is>
+      </c>
+      <c r="F549" s="10" t="inlineStr">
+        <is>
+          <t>Câu 293-4 nơi quen hay lui tới dùng 行きつけ/行く場所.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550" ht="24" customHeight="1">
+      <c r="A550" s="5" t="n">
+        <v>549</v>
+      </c>
+      <c r="B550" s="6" t="inlineStr">
+        <is>
+          <t>作成</t>
+        </is>
+      </c>
+      <c r="C550" s="6" t="inlineStr">
+        <is>
+          <t>さくせい</t>
+        </is>
+      </c>
+      <c r="D550" s="7" t="inlineStr">
+        <is>
+          <t>Soạn thảo, lập giấy tờ tài liệu kế hoạch</t>
+        </is>
+      </c>
+      <c r="E550" s="7" t="inlineStr">
+        <is>
+          <t>会議の資料を作成しておいてください (xin hãy soạn thảo sẵn tài liệu cuộc họp)</t>
+        </is>
+      </c>
+      <c r="F550" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 294] Phương án 2. Đi với `書類/資料/計画を作成する`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551" ht="24" customHeight="1">
+      <c r="A551" s="8" t="n">
+        <v>550</v>
+      </c>
+      <c r="B551" s="9" t="inlineStr">
+        <is>
+          <t>作る</t>
+        </is>
+      </c>
+      <c r="C551" s="9" t="inlineStr">
+        <is>
+          <t>つくる</t>
+        </is>
+      </c>
+      <c r="D551" s="10" t="inlineStr">
+        <is>
+          <t>Tạo cơ hội giao tiếp</t>
+        </is>
+      </c>
+      <c r="E551" s="10" t="inlineStr">
+        <is>
+          <t>話す機会を多く作る (tạo thật nhiều cơ hội nói chuyện)</t>
+        </is>
+      </c>
+      <c r="F551" s="10" t="inlineStr">
+        <is>
+          <t>Câu 294-1 cơ hội dùng 機会を作る/設ける.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552" ht="24" customHeight="1">
+      <c r="A552" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="B552" s="3" t="inlineStr">
+        <is>
+          <t>生産</t>
+        </is>
+      </c>
+      <c r="C552" s="3" t="inlineStr">
+        <is>
+          <t>せいさん</t>
+        </is>
+      </c>
+      <c r="D552" s="4" t="inlineStr">
+        <is>
+          <t>Sản xuất, trồng trọt nông sản</t>
+        </is>
+      </c>
+      <c r="E552" s="4" t="inlineStr">
+        <is>
+          <t>生産された果物 (trái cây được nuôi trồng sản xuất ở vùng này)</t>
+        </is>
+      </c>
+      <c r="F552" s="4" t="inlineStr">
+        <is>
+          <t>Câu 294-3 hoa quả nông sản dùng 栽培/生産/収穫.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553" ht="24" customHeight="1">
+      <c r="A553" s="8" t="n">
+        <v>552</v>
+      </c>
+      <c r="B553" s="9" t="inlineStr">
+        <is>
+          <t>設立</t>
+        </is>
+      </c>
+      <c r="C553" s="9" t="inlineStr">
+        <is>
+          <t>せつりつ</t>
+        </is>
+      </c>
+      <c r="D553" s="10" t="inlineStr">
+        <is>
+          <t>Thành lập công ty</t>
+        </is>
+      </c>
+      <c r="E553" s="10" t="inlineStr">
+        <is>
+          <t>新しい会社を設立する (thành lập doanh nghiệp mới)</t>
+        </is>
+      </c>
+      <c r="F553" s="10" t="inlineStr">
+        <is>
+          <t>Câu 294-4 lập công ty dùng 設立/立ち上げる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="24" customHeight="1">
+      <c r="A554" s="5" t="n">
+        <v>553</v>
+      </c>
+      <c r="B554" s="6" t="inlineStr">
+        <is>
+          <t>いったん</t>
+        </is>
+      </c>
+      <c r="C554" s="6" t="inlineStr">
+        <is>
+          <t>いったん (一旦)</t>
+        </is>
+      </c>
+      <c r="D554" s="7" t="inlineStr">
+        <is>
+          <t>Tạm thời một lát; một khi đã...</t>
+        </is>
+      </c>
+      <c r="E554" s="7" t="inlineStr">
+        <is>
+          <t>会社にいったん戻ったが、すぐにまた出かけた (ghé tạm về công ty một lát rồi lại đi ngay)</t>
+        </is>
+      </c>
+      <c r="F554" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 295] Phương án 3. Làm việc gì tạm thời rồi tiếp tục.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555" ht="24" customHeight="1">
+      <c r="A555" s="8" t="n">
+        <v>554</v>
+      </c>
+      <c r="B555" s="9" t="inlineStr">
+        <is>
+          <t>一度も</t>
+        </is>
+      </c>
+      <c r="C555" s="9" t="inlineStr">
+        <is>
+          <t>いちども</t>
+        </is>
+      </c>
+      <c r="D555" s="10" t="inlineStr">
+        <is>
+          <t>Một lần cũng không (chưa từng đi nước ngoài)</t>
+        </is>
+      </c>
+      <c r="E555" s="10" t="inlineStr">
+        <is>
+          <t>一度も行ったことがない (chưa từng đi ra nước ngoài lần nào)</t>
+        </is>
+      </c>
+      <c r="F555" s="10" t="inlineStr">
+        <is>
+          <t>Câu 295-1 chưa đi nước ngoài dùng 一度も.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="24" customHeight="1">
+      <c r="A556" s="2" t="n">
+        <v>555</v>
+      </c>
+      <c r="B556" s="3" t="inlineStr">
+        <is>
+          <t>一度</t>
+        </is>
+      </c>
+      <c r="C556" s="3" t="inlineStr">
+        <is>
+          <t>いちど</t>
+        </is>
+      </c>
+      <c r="D556" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ một lần duy nhất</t>
+        </is>
+      </c>
+      <c r="E556" s="4" t="inlineStr">
+        <is>
+          <t>一度しか会っていない (chỉ mới gặp mặt đúng một lần duy nhất)</t>
+        </is>
+      </c>
+      <c r="F556" s="4" t="inlineStr">
+        <is>
+          <t>Câu 295-2 gặp 1 lần dùng 一度しか.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557" ht="24" customHeight="1">
+      <c r="A557" s="8" t="n">
+        <v>556</v>
+      </c>
+      <c r="B557" s="9" t="inlineStr">
+        <is>
+          <t>一回</t>
+        </is>
+      </c>
+      <c r="C557" s="9" t="inlineStr">
+        <is>
+          <t>いっかい</t>
+        </is>
+      </c>
+      <c r="D557" s="10" t="inlineStr">
+        <is>
+          <t>Mỗi tuần một lần</t>
+        </is>
+      </c>
+      <c r="E557" s="10" t="inlineStr">
+        <is>
+          <t>週に1回映画を見に行った (mỗi tuần đi xem phim 1 lần)</t>
+        </is>
+      </c>
+      <c r="F557" s="10" t="inlineStr">
+        <is>
+          <t>Câu 295-4 tần suất dùng 週に1回/1度.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558" ht="24" customHeight="1">
+      <c r="A558" s="5" t="n">
+        <v>557</v>
+      </c>
+      <c r="B558" s="6" t="inlineStr">
+        <is>
+          <t>思いつく</t>
+        </is>
+      </c>
+      <c r="C558" s="6" t="inlineStr">
+        <is>
+          <t>おもいつく</t>
+        </is>
+      </c>
+      <c r="D558" s="7" t="inlineStr">
+        <is>
+          <t>Nảy ra ý tưởng, nghĩ ra sáng kiến</t>
+        </is>
+      </c>
+      <c r="E558" s="7" t="inlineStr">
+        <is>
+          <t>散歩しているときにいいアイディアを思いついた (khi đi dạo tôi đã nảy ra ý tưởng tuyệt hay)</t>
+        </is>
+      </c>
+      <c r="F558" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 296] Phương án 2. Đi với `アイディア/計画を思いつく`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559" ht="24" customHeight="1">
+      <c r="A559" s="8" t="n">
+        <v>558</v>
+      </c>
+      <c r="B559" s="9" t="inlineStr">
+        <is>
+          <t>想像する</t>
+        </is>
+      </c>
+      <c r="C559" s="9" t="inlineStr">
+        <is>
+          <t>そうぞうする</t>
+        </is>
+      </c>
+      <c r="D559" s="10" t="inlineStr">
+        <is>
+          <t>Mường tượng, hình dung viễn cảnh</t>
+        </is>
+      </c>
+      <c r="E559" s="10" t="inlineStr">
+        <is>
+          <t>成功している自分の姿を想像する (hình dung bản thân thành đạt sau này)</t>
+        </is>
+      </c>
+      <c r="F559" s="10" t="inlineStr">
+        <is>
+          <t>Câu 296-1 viễn cảnh tương lai dùng 想像する/思い描く.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560" ht="24" customHeight="1">
+      <c r="A560" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="B560" s="3" t="inlineStr">
+        <is>
+          <t>予感する</t>
+        </is>
+      </c>
+      <c r="C560" s="3" t="inlineStr">
+        <is>
+          <t>よかんする</t>
+        </is>
+      </c>
+      <c r="D560" s="4" t="inlineStr">
+        <is>
+          <t>Linh cảm, cảm thấy</t>
+        </is>
+      </c>
+      <c r="E560" s="4" t="inlineStr">
+        <is>
+          <t>親友になれそうな気がした (có linh cảm là sẽ trở thành bạn thân)</t>
+        </is>
+      </c>
+      <c r="F560" s="4" t="inlineStr">
+        <is>
+          <t>Câu 296-2 cảm thấy hợp tính dùng 気がする/直感した.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561" ht="24" customHeight="1">
+      <c r="A561" s="8" t="n">
+        <v>560</v>
+      </c>
+      <c r="B561" s="9" t="inlineStr">
+        <is>
+          <t>思い出す</t>
+        </is>
+      </c>
+      <c r="C561" s="9" t="inlineStr">
+        <is>
+          <t>おもいだす</t>
+        </is>
+      </c>
+      <c r="D561" s="10" t="inlineStr">
+        <is>
+          <t>Nhớ lại kỷ niệm quá khứ</t>
+        </is>
+      </c>
+      <c r="E561" s="10" t="inlineStr">
+        <is>
+          <t>学生時代のことを思い出す (nhớ lại thời học sinh)</t>
+        </is>
+      </c>
+      <c r="F561" s="10" t="inlineStr">
+        <is>
+          <t>Câu 296-4 hồi tưởng chuyện xưa dùng 思い出す.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="24" customHeight="1">
+      <c r="A562" s="5" t="n">
+        <v>561</v>
+      </c>
+      <c r="B562" s="6" t="inlineStr">
+        <is>
+          <t>中断</t>
+        </is>
+      </c>
+      <c r="C562" s="6" t="inlineStr">
+        <is>
+          <t>ちゅうだん</t>
+        </is>
+      </c>
+      <c r="D562" s="7" t="inlineStr">
+        <is>
+          <t>Tạm dừng, gián đoạn giữa chừng do sự cố</t>
+        </is>
+      </c>
+      <c r="E562" s="7" t="inlineStr">
+        <is>
+          <t>雨が強くなって試合が中断されている (mưa lớn nên trận đấu tạm thời bị gián đoạn)</t>
+        </is>
+      </c>
+      <c r="F562" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 297] Phương án 4. Đi với `試合/会議が中断する`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563" ht="24" customHeight="1">
+      <c r="A563" s="8" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" s="9" t="inlineStr">
+        <is>
+          <t>中止</t>
+        </is>
+      </c>
+      <c r="C563" s="9" t="inlineStr">
+        <is>
+          <t>ちゅうし</t>
+        </is>
+      </c>
+      <c r="D563" s="10" t="inlineStr">
+        <is>
+          <t>Hủy bỏ hoàn toàn sự kiện</t>
+        </is>
+      </c>
+      <c r="E563" s="10" t="inlineStr">
+        <is>
+          <t>イベントは中止されることになった (sự kiện đã bị hủy bỏ hoàn toàn)</t>
+        </is>
+      </c>
+      <c r="F563" s="10" t="inlineStr">
+        <is>
+          <t>Câu 297-1 thiếu người hủy sự kiện dùng 中止.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" ht="24" customHeight="1">
+      <c r="A564" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="B564" s="3" t="inlineStr">
+        <is>
+          <t>折れる</t>
+        </is>
+      </c>
+      <c r="C564" s="3" t="inlineStr">
+        <is>
+          <t>おれる</t>
+        </is>
+      </c>
+      <c r="D564" s="4" t="inlineStr">
+        <is>
+          <t>Gãy cành cây</t>
+        </is>
+      </c>
+      <c r="E564" s="4" t="inlineStr">
+        <is>
+          <t>折れた木 (cây khô bị gãy gập)</t>
+        </is>
+      </c>
+      <c r="F564" s="4" t="inlineStr">
+        <is>
+          <t>Câu 297-2 cây cối dùng 折れた/倒れた.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="24" customHeight="1">
+      <c r="A565" s="8" t="n">
+        <v>564</v>
+      </c>
+      <c r="B565" s="9" t="inlineStr">
+        <is>
+          <t>退職</t>
+        </is>
+      </c>
+      <c r="C565" s="9" t="inlineStr">
+        <is>
+          <t>たいしょく</t>
+        </is>
+      </c>
+      <c r="D565" s="10" t="inlineStr">
+        <is>
+          <t>Nghỉ việc chuyển công ty</t>
+        </is>
+      </c>
+      <c r="E565" s="10" t="inlineStr">
+        <is>
+          <t>会社を辞めて／退職して (nghỉ việc ở công ty hiện tại)</t>
+        </is>
+      </c>
+      <c r="F565" s="10" t="inlineStr">
+        <is>
+          <t>Câu 297-3 nghỉ việc đổi chỗ làm dùng 辞める/退職する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="24" customHeight="1">
+      <c r="A566" s="5" t="n">
+        <v>565</v>
+      </c>
+      <c r="B566" s="6" t="inlineStr">
+        <is>
+          <t>たくましい</t>
+        </is>
+      </c>
+      <c r="C566" s="6" t="inlineStr">
+        <is>
+          <t>たくましい</t>
+        </is>
+      </c>
+      <c r="D566" s="7" t="inlineStr">
+        <is>
+          <t>Kiên cường, bất khuất; vạm vỡ</t>
+        </is>
+      </c>
+      <c r="E566" s="7" t="inlineStr">
+        <is>
+          <t>どんな苦労にも負けずにたくましく生きてきた (bất chấp gian khổ vẫn kiên cường vươn lên sống tốt)</t>
+        </is>
+      </c>
+      <c r="F566" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 298] Phương án 1. Sức sống mãnh liệt, kiên cường.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="24" customHeight="1">
+      <c r="A567" s="8" t="n">
+        <v>566</v>
+      </c>
+      <c r="B567" s="9" t="inlineStr">
+        <is>
+          <t>丈夫</t>
+        </is>
+      </c>
+      <c r="C567" s="9" t="inlineStr">
+        <is>
+          <t>じょうぶ</t>
+        </is>
+      </c>
+      <c r="D567" s="10" t="inlineStr">
+        <is>
+          <t>Bền dai, chắc chắn (sợi dây)</t>
+        </is>
+      </c>
+      <c r="E567" s="10" t="inlineStr">
+        <is>
+          <t>もっと丈夫なひも (sợi dây thừng bền chắc hơn)</t>
+        </is>
+      </c>
+      <c r="F567" s="10" t="inlineStr">
+        <is>
+          <t>Câu 298-2 dây thừng dùng 丈夫な/太い.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="24" customHeight="1">
+      <c r="A568" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="B568" s="3" t="inlineStr">
+        <is>
+          <t>豊富</t>
+        </is>
+      </c>
+      <c r="C568" s="3" t="inlineStr">
+        <is>
+          <t>ほうふ</t>
+        </is>
+      </c>
+      <c r="D568" s="4" t="inlineStr">
+        <is>
+          <t>Phong phú, dày dạn kinh nghiệm</t>
+        </is>
+      </c>
+      <c r="E568" s="4" t="inlineStr">
+        <is>
+          <t>仕事の経験が豊富だ (kinh nghiệm công việc phong phú)</t>
+        </is>
+      </c>
+      <c r="F568" s="4" t="inlineStr">
+        <is>
+          <t>Câu 298-3 kinh nghiệm dùng 豊富/豊か.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="24" customHeight="1">
+      <c r="A569" s="8" t="n">
+        <v>568</v>
+      </c>
+      <c r="B569" s="9" t="inlineStr">
+        <is>
+          <t>強烈</t>
+        </is>
+      </c>
+      <c r="C569" s="9" t="inlineStr">
+        <is>
+          <t>きょうれつ</t>
+        </is>
+      </c>
+      <c r="D569" s="10" t="inlineStr">
+        <is>
+          <t>Gay gắt, chói chang (nắng hè)</t>
+        </is>
+      </c>
+      <c r="E569" s="10" t="inlineStr">
+        <is>
+          <t>日ざしが強くなった (ánh nắng trở nên chói chang gay gắt)</t>
+        </is>
+      </c>
+      <c r="F569" s="10" t="inlineStr">
+        <is>
+          <t>Câu 298-4 ánh nắng dùng 強い/強烈な.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="24" customHeight="1">
+      <c r="A570" s="5" t="n">
+        <v>569</v>
+      </c>
+      <c r="B570" s="6" t="inlineStr">
+        <is>
+          <t>発達</t>
+        </is>
+      </c>
+      <c r="C570" s="6" t="inlineStr">
+        <is>
+          <t>はったつ</t>
+        </is>
+      </c>
+      <c r="D570" s="7" t="inlineStr">
+        <is>
+          <t>Phát triển vượt bậc (giao thông, bão, cơ thể)</t>
+        </is>
+      </c>
+      <c r="E570" s="7" t="inlineStr">
+        <is>
+          <t>交通が発達したことにより便利になった (giao thông phát triển hiện đại giúp đời sống tiện lợi hơn)</t>
+        </is>
+      </c>
+      <c r="F570" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 299] Phương án 2. Đi với `交通/文明/台風が発達する`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="24" customHeight="1">
+      <c r="A571" s="8" t="n">
+        <v>570</v>
+      </c>
+      <c r="B571" s="9" t="inlineStr">
+        <is>
+          <t>伸びる</t>
+        </is>
+      </c>
+      <c r="C571" s="9" t="inlineStr">
+        <is>
+          <t>のびる</t>
+        </is>
+      </c>
+      <c r="D571" s="10" t="inlineStr">
+        <is>
+          <t>Tăng trưởng chiều cao</t>
+        </is>
+      </c>
+      <c r="E571" s="10" t="inlineStr">
+        <is>
+          <t>身長が伸びて (chiều cao tăng vọt lên)</t>
+        </is>
+      </c>
+      <c r="F571" s="10" t="inlineStr">
+        <is>
+          <t>Câu 299-1 chiều cao người dùng 伸びる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" ht="24" customHeight="1">
+      <c r="A572" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="B572" s="3" t="inlineStr">
+        <is>
+          <t>向上</t>
+        </is>
+      </c>
+      <c r="C572" s="3" t="inlineStr">
+        <is>
+          <t>こうじょう</t>
+        </is>
+      </c>
+      <c r="D572" s="4" t="inlineStr">
+        <is>
+          <t>Nâng cao chất lượng dịch vụ</t>
+        </is>
+      </c>
+      <c r="E572" s="4" t="inlineStr">
+        <is>
+          <t>サービスの向上に努める (nỗ lực nâng cấp dịch vụ)</t>
+        </is>
+      </c>
+      <c r="F572" s="4" t="inlineStr">
+        <is>
+          <t>Câu 299-3 dịch vụ dùng 向上/改善.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="24" customHeight="1">
+      <c r="A573" s="8" t="n">
+        <v>572</v>
+      </c>
+      <c r="B573" s="9" t="inlineStr">
+        <is>
+          <t>育ち</t>
+        </is>
+      </c>
+      <c r="C573" s="9" t="inlineStr">
+        <is>
+          <t>そだち</t>
+        </is>
+      </c>
+      <c r="D573" s="10" t="inlineStr">
+        <is>
+          <t>Cây cối sinh trưởng tốt tươi</t>
+        </is>
+      </c>
+      <c r="E573" s="10" t="inlineStr">
+        <is>
+          <t>トマトの育ちが良い (cây cà chua sinh trưởng tươi tốt)</t>
+        </is>
+      </c>
+      <c r="F573" s="10" t="inlineStr">
+        <is>
+          <t>Câu 299-4 rau củ quả dùng 生育/育ち.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574" ht="24" customHeight="1">
+      <c r="A574" s="5" t="n">
+        <v>573</v>
+      </c>
+      <c r="B574" s="6" t="inlineStr">
+        <is>
+          <t>きっかけ</t>
+        </is>
+      </c>
+      <c r="C574" s="6" t="inlineStr">
+        <is>
+          <t>きっかけ</t>
+        </is>
+      </c>
+      <c r="D574" s="7" t="inlineStr">
+        <is>
+          <t>Cơ duyên, động cơ khởi phát, bước ngoặt</t>
+        </is>
+      </c>
+      <c r="E574" s="7" t="inlineStr">
+        <is>
+          <t>今回の事件をきっかけに防犯意識が高まった (lấy vụ án lần này làm bước ngoặt nâng cao ý thức phòng chống tội phạm)</t>
+        </is>
+      </c>
+      <c r="F574" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 300] Phương án 3. Mẫu ngữ pháp N2: `～をきっかけに`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575" ht="24" customHeight="1">
+      <c r="A575" s="8" t="n">
+        <v>574</v>
+      </c>
+      <c r="B575" s="9" t="inlineStr">
+        <is>
+          <t>機会</t>
+        </is>
+      </c>
+      <c r="C575" s="9" t="inlineStr">
+        <is>
+          <t>きかい</t>
+        </is>
+      </c>
+      <c r="D575" s="10" t="inlineStr">
+        <is>
+          <t>Dịp, cơ hội tham dự</t>
+        </is>
+      </c>
+      <c r="E575" s="10" t="inlineStr">
+        <is>
+          <t>次の機会にはぜひ出席したい (dịp tới nhất định tôi sẽ tham gia)</t>
+        </is>
+      </c>
+      <c r="F575" s="10" t="inlineStr">
+        <is>
+          <t>Câu 300-1 dịp/cơ hội tham dự dùng 機会/次回.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" ht="24" customHeight="1">
+      <c r="A576" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="B576" s="3" t="inlineStr">
+        <is>
+          <t>起源</t>
+        </is>
+      </c>
+      <c r="C576" s="3" t="inlineStr">
+        <is>
+          <t>きげん</t>
+        </is>
+      </c>
+      <c r="D576" s="4" t="inlineStr">
+        <is>
+          <t>Nguồn gốc, lai lịch chữ Hán</t>
+        </is>
+      </c>
+      <c r="E576" s="4" t="inlineStr">
+        <is>
+          <t>漢字の起源／成り立ち (nguồn gốc cấu tạo của chữ Hán)</t>
+        </is>
+      </c>
+      <c r="F576" s="4" t="inlineStr">
+        <is>
+          <t>Câu 300-2 lịch sử chữ Hán dùng 起源/歴史.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" ht="24" customHeight="1">
+      <c r="A577" s="8" t="n">
+        <v>576</v>
+      </c>
+      <c r="B577" s="9" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="C577" s="9" t="inlineStr">
+        <is>
+          <t>りゆう</t>
+        </is>
+      </c>
+      <c r="D577" s="10" t="inlineStr">
+        <is>
+          <t>Lý do phản đối dự án</t>
+        </is>
+      </c>
+      <c r="E577" s="10" t="inlineStr">
+        <is>
+          <t>反対する理由は (lý do phản đối dự án công trình)</t>
+        </is>
+      </c>
+      <c r="F577" s="10" t="inlineStr">
+        <is>
+          <t>Câu 300-4 lý do phản đối dùng 理由/原因.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="24" customHeight="1">
+      <c r="A578" s="5" t="n">
+        <v>577</v>
+      </c>
+      <c r="B578" s="6" t="inlineStr">
+        <is>
+          <t>引退</t>
+        </is>
+      </c>
+      <c r="C578" s="6" t="inlineStr">
+        <is>
+          <t>いんたい</t>
+        </is>
+      </c>
+      <c r="D578" s="7" t="inlineStr">
+        <is>
+          <t>Giải nghệ, giã từ sự nghiệp thể thao/chính trường</t>
+        </is>
+      </c>
+      <c r="E578" s="7" t="inlineStr">
+        <is>
+          <t>鈴木選手は去年引退し、海外に移住した (vận động viên Suzuki năm ngoái đã giải nghệ và định cư nước ngoài)</t>
+        </is>
+      </c>
+      <c r="F578" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 301] Phương án 3. Vận động viên, nghệ sĩ, chính khách giải nghệ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="24" customHeight="1">
+      <c r="A579" s="8" t="n">
+        <v>578</v>
+      </c>
+      <c r="B579" s="9" t="inlineStr">
+        <is>
+          <t>辞退</t>
+        </is>
+      </c>
+      <c r="C579" s="9" t="inlineStr">
+        <is>
+          <t>じたい</t>
+        </is>
+      </c>
+      <c r="D579" s="10" t="inlineStr">
+        <is>
+          <t>Xin rút lui, từ chối tham gia thi đấu</t>
+        </is>
+      </c>
+      <c r="E579" s="10" t="inlineStr">
+        <is>
+          <t>スピーチ大会を辞退する (xin rút lui không tham gia cuộc thi diễn thuyết)</t>
+        </is>
+      </c>
+      <c r="F579" s="10" t="inlineStr">
+        <is>
+          <t>Câu 301-1 rút khỏi cuộc thi dùng 辞退する/欠場する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="24" customHeight="1">
+      <c r="A580" s="2" t="n">
+        <v>579</v>
+      </c>
+      <c r="B580" s="3" t="inlineStr">
+        <is>
+          <t>辞める</t>
+        </is>
+      </c>
+      <c r="C580" s="3" t="inlineStr">
+        <is>
+          <t>やめる</t>
+        </is>
+      </c>
+      <c r="D580" s="4" t="inlineStr">
+        <is>
+          <t>Nghỉ làm thêm</t>
+        </is>
+      </c>
+      <c r="E580" s="4" t="inlineStr">
+        <is>
+          <t>アルバイトを辞めて (bỏ công việc làm thêm để tập trung học)</t>
+        </is>
+      </c>
+      <c r="F580" s="4" t="inlineStr">
+        <is>
+          <t>Câu 301-2 nghỉ làm thêm dùng 辞める.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581" ht="24" customHeight="1">
+      <c r="A581" s="8" t="n">
+        <v>580</v>
+      </c>
+      <c r="B581" s="9" t="inlineStr">
+        <is>
+          <t>辞退する</t>
+        </is>
+      </c>
+      <c r="C581" s="9" t="inlineStr">
+        <is>
+          <t>じたいする</t>
+        </is>
+      </c>
+      <c r="D581" s="10" t="inlineStr">
+        <is>
+          <t>Từ chối lời mời vào công ty</t>
+        </is>
+      </c>
+      <c r="E581" s="10" t="inlineStr">
+        <is>
+          <t>内定を辞退する (từ chối lời mời làm việc của công ty)</t>
+        </is>
+      </c>
+      <c r="F581" s="10" t="inlineStr">
+        <is>
+          <t>Câu 301-4 đỗ phỏng vấn nhưng không vào dùng 辞退する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582" ht="24" customHeight="1">
+      <c r="A582" s="5" t="n">
+        <v>581</v>
+      </c>
+      <c r="B582" s="6" t="inlineStr">
+        <is>
+          <t>順調</t>
+        </is>
+      </c>
+      <c r="C582" s="6" t="inlineStr">
+        <is>
+          <t>じゅんちょう</t>
+        </is>
+      </c>
+      <c r="D582" s="7" t="inlineStr">
+        <is>
+          <t>Thuận buồm xuôi gió, trôi chảy suôn sẻ</t>
+        </is>
+      </c>
+      <c r="E582" s="7" t="inlineStr">
+        <is>
+          <t>発売以来、順調に売り上げを伸ばしている (kể từ khi mở bán doanh số đã tăng trưởng rất đều đặn thuận lợi)</t>
+        </is>
+      </c>
+      <c r="F582" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 302] Phương án 4. Đi với `順調に進む/順調に伸びる`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583" ht="24" customHeight="1">
+      <c r="A583" s="8" t="n">
+        <v>582</v>
+      </c>
+      <c r="B583" s="9" t="inlineStr">
+        <is>
+          <t>親切</t>
+        </is>
+      </c>
+      <c r="C583" s="9" t="inlineStr">
+        <is>
+          <t>しんせつ</t>
+        </is>
+      </c>
+      <c r="D583" s="10" t="inlineStr">
+        <is>
+          <t>Tận tình, kiên nhẫn trả lời</t>
+        </is>
+      </c>
+      <c r="E583" s="10" t="inlineStr">
+        <is>
+          <t>ていねいに答えてくれる (thầy giáo kiên nhẫn giải đáp tỉ mỉ)</t>
+        </is>
+      </c>
+      <c r="F583" s="10" t="inlineStr">
+        <is>
+          <t>Câu 302-1 giải đáp thắc mắc dùng ていねいに/的確に.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="24" customHeight="1">
+      <c r="A584" s="2" t="n">
+        <v>583</v>
+      </c>
+      <c r="B584" s="3" t="inlineStr">
+        <is>
+          <t>うまく</t>
+        </is>
+      </c>
+      <c r="C584" s="3" t="inlineStr">
+        <is>
+          <t>うまく</t>
+        </is>
+      </c>
+      <c r="D584" s="4" t="inlineStr">
+        <is>
+          <t>Dễ dàng, trơn tru (nuốt thức ăn)</t>
+        </is>
+      </c>
+      <c r="E584" s="4" t="inlineStr">
+        <is>
+          <t>食べ物をうまく飲み込めない (cổ họng đau không nuốt trôi thức ăn)</t>
+        </is>
+      </c>
+      <c r="F584" s="4" t="inlineStr">
+        <is>
+          <t>Câu 302-2 nuốt thức ăn dùng うまく/スムーズに.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585" ht="24" customHeight="1">
+      <c r="A585" s="8" t="n">
+        <v>584</v>
+      </c>
+      <c r="B585" s="9" t="inlineStr">
+        <is>
+          <t>派手に</t>
+        </is>
+      </c>
+      <c r="C585" s="9" t="inlineStr">
+        <is>
+          <t>はでに</t>
+        </is>
+      </c>
+      <c r="D585" s="10" t="inlineStr">
+        <is>
+          <t>Ngã nhào ra đất một cú đau điếng</t>
+        </is>
+      </c>
+      <c r="E585" s="10" t="inlineStr">
+        <is>
+          <t>派手に転んでしまった (đường trơn ngã nhào ra đất)</t>
+        </is>
+      </c>
+      <c r="F585" s="10" t="inlineStr">
+        <is>
+          <t>Câu 302-3 trượt chân ngã dùng 派手に/激しく.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586" ht="24" customHeight="1">
+      <c r="A586" s="5" t="n">
+        <v>585</v>
+      </c>
+      <c r="B586" s="6" t="inlineStr">
+        <is>
+          <t>生じる</t>
+        </is>
+      </c>
+      <c r="C586" s="6" t="inlineStr">
+        <is>
+          <t>しょうじる</t>
+        </is>
+      </c>
+      <c r="D586" s="7" t="inlineStr">
+        <is>
+          <t>Phát sinh, nảy sinh (vấn đề, hiểu lầm, lỗi)</t>
+        </is>
+      </c>
+      <c r="E586" s="7" t="inlineStr">
+        <is>
+          <t>習慣の違いから誤解が生じることがある (do khác biệt tập quán nên đôi khi nảy sinh hiểu lầm)</t>
+        </is>
+      </c>
+      <c r="F586" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 303] Phương án 1. Đi với `誤解/問題/被害が生じる`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587" ht="24" customHeight="1">
+      <c r="A587" s="8" t="n">
+        <v>586</v>
+      </c>
+      <c r="B587" s="9" t="inlineStr">
+        <is>
+          <t>実る</t>
+        </is>
+      </c>
+      <c r="C587" s="9" t="inlineStr">
+        <is>
+          <t>みのる</t>
+        </is>
+      </c>
+      <c r="D587" s="10" t="inlineStr">
+        <is>
+          <t>Đơm hoa kết trái</t>
+        </is>
+      </c>
+      <c r="E587" s="10" t="inlineStr">
+        <is>
+          <t>果物が実っている (trái cây đơm hoa kết trái trĩu cành)</t>
+        </is>
+      </c>
+      <c r="F587" s="10" t="inlineStr">
+        <is>
+          <t>Câu 303-2 hoa quả kết trái dùng 実る/栽培される.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588" ht="24" customHeight="1">
+      <c r="A588" s="2" t="n">
+        <v>587</v>
+      </c>
+      <c r="B588" s="3" t="inlineStr">
+        <is>
+          <t>生まれる</t>
+        </is>
+      </c>
+      <c r="C588" s="3" t="inlineStr">
+        <is>
+          <t>うまれる</t>
+        </is>
+      </c>
+      <c r="D588" s="4" t="inlineStr">
+        <is>
+          <t>Ra đời, phát minh công nghệ mới</t>
+        </is>
+      </c>
+      <c r="E588" s="4" t="inlineStr">
+        <is>
+          <t>新しい技術が開発された (công nghệ mới được phát minh/ra đời)</t>
+        </is>
+      </c>
+      <c r="F588" s="4" t="inlineStr">
+        <is>
+          <t>Câu 303-3 công nghệ dùng 誕生した/開発された.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589" ht="24" customHeight="1">
+      <c r="A589" s="8" t="n">
+        <v>588</v>
+      </c>
+      <c r="B589" s="9" t="inlineStr">
+        <is>
+          <t>輩出</t>
+        </is>
+      </c>
+      <c r="C589" s="9" t="inlineStr">
+        <is>
+          <t>はいしゅつ</t>
+        </is>
+      </c>
+      <c r="D589" s="10" t="inlineStr">
+        <is>
+          <t>Đào tạo, sản sinh ra nhiều nhân tài</t>
+        </is>
+      </c>
+      <c r="E589" s="10" t="inlineStr">
+        <is>
+          <t>研究者を多く輩出している (trường đại học này sản sinh đào tạo nhiều nhà nghiên cứu)</t>
+        </is>
+      </c>
+      <c r="F589" s="10" t="inlineStr">
+        <is>
+          <t>Câu 303-4 đào tạo nhân tài dùng 輩出している.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590" ht="24" customHeight="1">
+      <c r="A590" s="5" t="n">
+        <v>589</v>
+      </c>
+      <c r="B590" s="6" t="inlineStr">
+        <is>
+          <t>延長</t>
+        </is>
+      </c>
+      <c r="C590" s="6" t="inlineStr">
+        <is>
+          <t>えんちょう</t>
+        </is>
+      </c>
+      <c r="D590" s="7" t="inlineStr">
+        <is>
+          <t>Gia hạn thời gian, kéo dài cuộc họp</t>
+        </is>
+      </c>
+      <c r="E590" s="7" t="inlineStr">
+        <is>
+          <t>会議が1時間延長されることになった (cuộc họp đã được quyết định kéo dài thêm 1 tiếng)</t>
+        </is>
+      </c>
+      <c r="F590" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 304] Phương án 3. Đi với `時間を延長する`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591" ht="24" customHeight="1">
+      <c r="A591" s="8" t="n">
+        <v>590</v>
+      </c>
+      <c r="B591" s="9" t="inlineStr">
+        <is>
+          <t>延期</t>
+        </is>
+      </c>
+      <c r="C591" s="9" t="inlineStr">
+        <is>
+          <t>えんき</t>
+        </is>
+      </c>
+      <c r="D591" s="10" t="inlineStr">
+        <is>
+          <t>Hoãn dời ngày tổ chức</t>
+        </is>
+      </c>
+      <c r="E591" s="10" t="inlineStr">
+        <is>
+          <t>出発が三日後に延期された (chuyến đi bị hoãn lùi lại 3 ngày)</t>
+        </is>
+      </c>
+      <c r="F591" s="10" t="inlineStr">
+        <is>
+          <t>Câu 304-1 hoãn lùi ngày lại dùng 延期された.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592" ht="24" customHeight="1">
+      <c r="A592" s="2" t="n">
+        <v>591</v>
+      </c>
+      <c r="B592" s="3" t="inlineStr">
+        <is>
+          <t>増築</t>
+        </is>
+      </c>
+      <c r="C592" s="3" t="inlineStr">
+        <is>
+          <t>ぞうちく</t>
+        </is>
+      </c>
+      <c r="D592" s="4" t="inlineStr">
+        <is>
+          <t>Xây thêm tầng, cơi nới nhà cửa</t>
+        </is>
+      </c>
+      <c r="E592" s="4" t="inlineStr">
+        <is>
+          <t>3階建てに増築する (cơi nới xây thêm tầng 3)</t>
+        </is>
+      </c>
+      <c r="F592" s="4" t="inlineStr">
+        <is>
+          <t>Câu 304-2 xây thêm tầng nhà dùng 増築する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593" ht="24" customHeight="1">
+      <c r="A593" s="8" t="n">
+        <v>592</v>
+      </c>
+      <c r="B593" s="9" t="inlineStr">
+        <is>
+          <t>乗り越す</t>
+        </is>
+      </c>
+      <c r="C593" s="9" t="inlineStr">
+        <is>
+          <t>のりこす</t>
+        </is>
+      </c>
+      <c r="D593" s="10" t="inlineStr">
+        <is>
+          <t>Đi quá ga dự định</t>
+        </is>
+      </c>
+      <c r="E593" s="10" t="inlineStr">
+        <is>
+          <t>一駅乗り越してしまった (ngủ gật nên đi quá mất một ga)</t>
+        </is>
+      </c>
+      <c r="F593" s="10" t="inlineStr">
+        <is>
+          <t>Câu 304-4 ngủ quên đi quá ga dùng 乗り越す.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594" ht="24" customHeight="1">
+      <c r="A594" s="5" t="n">
+        <v>593</v>
+      </c>
+      <c r="B594" s="6" t="inlineStr">
+        <is>
+          <t>さびる</t>
+        </is>
+      </c>
+      <c r="C594" s="6" t="inlineStr">
+        <is>
+          <t>さびる (錆びる)</t>
+        </is>
+      </c>
+      <c r="D594" s="7" t="inlineStr">
+        <is>
+          <t>Bị rỉ sét (kim loại sắt thép)</t>
+        </is>
+      </c>
+      <c r="E594" s="7" t="inlineStr">
+        <is>
+          <t>鉄の棒がさびて茶色くなっている (thanh sắt để ngoài trời bị rỉ sét ngả màu nâu)</t>
+        </is>
+      </c>
+      <c r="F594" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 305] Phương án 4. Kim loại sắt thép bị oxy hóa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595" ht="24" customHeight="1">
+      <c r="A595" s="8" t="n">
+        <v>594</v>
+      </c>
+      <c r="B595" s="9" t="inlineStr">
+        <is>
+          <t>腐る</t>
+        </is>
+      </c>
+      <c r="C595" s="9" t="inlineStr">
+        <is>
+          <t>くさる</t>
+        </is>
+      </c>
+      <c r="D595" s="10" t="inlineStr">
+        <is>
+          <t>Ô thiu, hôi thối (thực phẩm)</t>
+        </is>
+      </c>
+      <c r="E595" s="10" t="inlineStr">
+        <is>
+          <t>生ものが腐って臭くなった (đồ tươi sống bị ôi thiu bốc mùi)</t>
+        </is>
+      </c>
+      <c r="F595" s="10" t="inlineStr">
+        <is>
+          <t>Câu 305-1 thức ăn ôi thiu dùng 腐る.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" ht="24" customHeight="1">
+      <c r="A596" s="2" t="n">
+        <v>595</v>
+      </c>
+      <c r="B596" s="3" t="inlineStr">
+        <is>
+          <t>濁る</t>
+        </is>
+      </c>
+      <c r="C596" s="3" t="inlineStr">
+        <is>
+          <t>にごる</t>
+        </is>
+      </c>
+      <c r="D596" s="4" t="inlineStr">
+        <is>
+          <t>Vẩn đục (nước sông sau mưa)</t>
+        </is>
+      </c>
+      <c r="E596" s="4" t="inlineStr">
+        <is>
+          <t>川の水が濁っている (nước sông đục ngầu phù sa)</t>
+        </is>
+      </c>
+      <c r="F596" s="4" t="inlineStr">
+        <is>
+          <t>Câu 305-2 nước sông đục dùng 濁る.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597" ht="24" customHeight="1">
+      <c r="A597" s="8" t="n">
+        <v>596</v>
+      </c>
+      <c r="B597" s="9" t="inlineStr">
+        <is>
+          <t>枯れる</t>
+        </is>
+      </c>
+      <c r="C597" s="9" t="inlineStr">
+        <is>
+          <t>かれる</t>
+        </is>
+      </c>
+      <c r="D597" s="10" t="inlineStr">
+        <is>
+          <t>Héo úa, tàn lụi (cây cỏ)</t>
+        </is>
+      </c>
+      <c r="E597" s="10" t="inlineStr">
+        <is>
+          <t>花が枯れてしまった (quên tưới cây nên hoa bị héo rũ)</t>
+        </is>
+      </c>
+      <c r="F597" s="10" t="inlineStr">
+        <is>
+          <t>Câu 305-3 hoa héo tàn dùng 枯れる.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598" ht="24" customHeight="1">
+      <c r="A598" s="5" t="n">
+        <v>597</v>
+      </c>
+      <c r="B598" s="6" t="inlineStr">
+        <is>
+          <t>目上</t>
+        </is>
+      </c>
+      <c r="C598" s="6" t="inlineStr">
+        <is>
+          <t>めうえ</t>
+        </is>
+      </c>
+      <c r="D598" s="7" t="inlineStr">
+        <is>
+          <t>Cấp trên, người bề trên, bậc tiền bối</t>
+        </is>
+      </c>
+      <c r="E598" s="7" t="inlineStr">
+        <is>
+          <t>参加した社員がすべて目上だった (các nhân viên tham gia đều là bậc tiền bối bề trên)</t>
+        </is>
+      </c>
+      <c r="F598" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 306] Phương án 1. Người lớn tuổi hoặc có chức vụ cao hơn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599" ht="24" customHeight="1">
+      <c r="A599" s="8" t="n">
+        <v>598</v>
+      </c>
+      <c r="B599" s="9" t="inlineStr">
+        <is>
+          <t>高級</t>
+        </is>
+      </c>
+      <c r="C599" s="9" t="inlineStr">
+        <is>
+          <t>こうきゅう</t>
+        </is>
+      </c>
+      <c r="D599" s="10" t="inlineStr">
+        <is>
+          <t>Hàng hóa thượng hạng, cao cấp</t>
+        </is>
+      </c>
+      <c r="E599" s="10" t="inlineStr">
+        <is>
+          <t>最も高級な商品 (món hàng cao cấp đắt đỏ nhất tiệm)</t>
+        </is>
+      </c>
+      <c r="F599" s="10" t="inlineStr">
+        <is>
+          <t>Câu 306-2 hàng hóa giá cao dùng 高級な/上位の.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600" ht="24" customHeight="1">
+      <c r="A600" s="2" t="n">
+        <v>599</v>
+      </c>
+      <c r="B600" s="3" t="inlineStr">
+        <is>
+          <t>トップ</t>
+        </is>
+      </c>
+      <c r="C600" s="3" t="inlineStr">
+        <is>
+          <t>トップ</t>
+        </is>
+      </c>
+      <c r="D600" s="4" t="inlineStr">
+        <is>
+          <t>Dẫn đầu, đứng nhất bảng</t>
+        </is>
+      </c>
+      <c r="E600" s="4" t="inlineStr">
+        <is>
+          <t>成績はいつもトップだった (thành tích học tập luôn đứng đầu bảng)</t>
+        </is>
+      </c>
+      <c r="F600" s="4" t="inlineStr">
+        <is>
+          <t>Câu 306-3 thành tích đứng đầu dùng トップ/1位.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601" ht="24" customHeight="1">
+      <c r="A601" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="B601" s="9" t="inlineStr">
+        <is>
+          <t>素晴らしい</t>
+        </is>
+      </c>
+      <c r="C601" s="9" t="inlineStr">
+        <is>
+          <t>すばらしい</t>
+        </is>
+      </c>
+      <c r="D601" s="10" t="inlineStr">
+        <is>
+          <t>Người xuất sắc, tuyệt vời</t>
+        </is>
+      </c>
+      <c r="E601" s="10" t="inlineStr">
+        <is>
+          <t>本当に優秀な人だ (thực sự là người rất xuất sắc)</t>
+        </is>
+      </c>
+      <c r="F601" s="10" t="inlineStr">
+        <is>
+          <t>Câu 306-4 khen người tài giỏi dùng 優秀な/偉大な.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602" ht="24" customHeight="1">
+      <c r="A602" s="5" t="n">
+        <v>601</v>
+      </c>
+      <c r="B602" s="6" t="inlineStr">
+        <is>
+          <t>大げさ</t>
+        </is>
+      </c>
+      <c r="C602" s="6" t="inlineStr">
+        <is>
+          <t>おおげさ (大袈裟)</t>
+        </is>
+      </c>
+      <c r="D602" s="7" t="inlineStr">
+        <is>
+          <t>Nói quá, cường điệu, thổi phồng sự việc</t>
+        </is>
+      </c>
+      <c r="E602" s="7" t="inlineStr">
+        <is>
+          <t>小さなことを大げさに言う (chuyện bé xé ra to, thổi phồng sự việc nhỏ)</t>
+        </is>
+      </c>
+      <c r="F602" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 307] Phương án 4. Đi với `大げさに言う/大げさな表現`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603" ht="24" customHeight="1">
+      <c r="A603" s="8" t="n">
+        <v>602</v>
+      </c>
+      <c r="B603" s="9" t="inlineStr">
+        <is>
+          <t>大量に</t>
+        </is>
+      </c>
+      <c r="C603" s="9" t="inlineStr">
+        <is>
+          <t>たいりょうに</t>
+        </is>
+      </c>
+      <c r="D603" s="10" t="inlineStr">
+        <is>
+          <t>Thừa mứa rất nhiều (nấu ăn)</t>
+        </is>
+      </c>
+      <c r="E603" s="10" t="inlineStr">
+        <is>
+          <t>料理がたくさん余ってしまった (nấu quá tay thừa ê hề đồ ăn)</t>
+        </is>
+      </c>
+      <c r="F603" s="10" t="inlineStr">
+        <is>
+          <t>Câu 307-1 đồ ăn thừa dùng たくさん/大量に.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604" ht="24" customHeight="1">
+      <c r="A604" s="2" t="n">
+        <v>603</v>
+      </c>
+      <c r="B604" s="3" t="inlineStr">
+        <is>
+          <t>大幅に</t>
+        </is>
+      </c>
+      <c r="C604" s="3" t="inlineStr">
+        <is>
+          <t>おおはばに</t>
+        </is>
+      </c>
+      <c r="D604" s="4" t="inlineStr">
+        <is>
+          <t>Hạ nhiệt độ đáng kể, biên độ lớn</t>
+        </is>
+      </c>
+      <c r="E604" s="4" t="inlineStr">
+        <is>
+          <t>気温が大幅に下がる (nhiệt độ giảm mạnh đáng kể)</t>
+        </is>
+      </c>
+      <c r="F604" s="4" t="inlineStr">
+        <is>
+          <t>Câu 307-2 nhiệt độ giảm mạnh dùng 大幅に/急激に.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605" ht="24" customHeight="1">
+      <c r="A605" s="8" t="n">
+        <v>604</v>
+      </c>
+      <c r="B605" s="9" t="inlineStr">
+        <is>
+          <t>飛躍的に</t>
+        </is>
+      </c>
+      <c r="C605" s="9" t="inlineStr">
+        <is>
+          <t>ひやくてきに</t>
+        </is>
+      </c>
+      <c r="D605" s="10" t="inlineStr">
+        <is>
+          <t>Tiến bộ vượt bậc, ngoạn mục</t>
+        </is>
+      </c>
+      <c r="E605" s="10" t="inlineStr">
+        <is>
+          <t>成績がぐんと伸びた (thành tích thi cử tiến bộ vượt bậc)</t>
+        </is>
+      </c>
+      <c r="F605" s="10" t="inlineStr">
+        <is>
+          <t>Câu 307-3 điểm số tăng vọt dùng 飛躍的に/大幅に.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606" ht="24" customHeight="1">
+      <c r="A606" s="5" t="n">
+        <v>605</v>
+      </c>
+      <c r="B606" s="6" t="inlineStr">
+        <is>
+          <t>反省</t>
+        </is>
+      </c>
+      <c r="C606" s="6" t="inlineStr">
+        <is>
+          <t>はんせい</t>
+        </is>
+      </c>
+      <c r="D606" s="7" t="inlineStr">
+        <is>
+          <t>Kiểm điểm, tự nhìn nhận và ăn năn lỗi lầm</t>
+        </is>
+      </c>
+      <c r="E606" s="7" t="inlineStr">
+        <is>
+          <t>準備不足で迷惑をかけたことを反省しています (tôi đang tự kiểm điểm sâu sắc vì chuẩn bị chưa chu đáo gây phiền hà)</t>
+        </is>
+      </c>
+      <c r="F606" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 308] Phương án 2. Tự suy ngẫm hối lỗi về sai lầm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607" ht="24" customHeight="1">
+      <c r="A607" s="8" t="n">
+        <v>606</v>
+      </c>
+      <c r="B607" s="9" t="inlineStr">
+        <is>
+          <t>思い出す</t>
+        </is>
+      </c>
+      <c r="C607" s="9" t="inlineStr">
+        <is>
+          <t>おもいだす</t>
+        </is>
+      </c>
+      <c r="D607" s="10" t="inlineStr">
+        <is>
+          <t>Cố nhớ lại bài thuyết trình</t>
+        </is>
+      </c>
+      <c r="E607" s="10" t="inlineStr">
+        <is>
+          <t>どんなに思い出そうとしても (dù cố nhớ lại thế nào cũng chịu)</t>
+        </is>
+      </c>
+      <c r="F607" s="10" t="inlineStr">
+        <is>
+          <t>Câu 308-1 cố nhớ lại trong đầu dùng 思い出す.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608" ht="24" customHeight="1">
+      <c r="A608" s="2" t="n">
+        <v>607</v>
+      </c>
+      <c r="B608" s="3" t="inlineStr">
+        <is>
+          <t>懐かしむ</t>
+        </is>
+      </c>
+      <c r="C608" s="3" t="inlineStr">
+        <is>
+          <t>なつかしむ</t>
+        </is>
+      </c>
+      <c r="D608" s="4" t="inlineStr">
+        <is>
+          <t>Bồi hồi nhớ lại kỷ niệm xưa</t>
+        </is>
+      </c>
+      <c r="E608" s="4" t="inlineStr">
+        <is>
+          <t>思い出を懐かしそうに話す (kể lại kỷ niệm với vẻ mặt bồi hồi hoài niệm)</t>
+        </is>
+      </c>
+      <c r="F608" s="4" t="inlineStr">
+        <is>
+          <t>Câu 308-2 nhớ chuyện xưa dùng 懐かしむ/振り返る.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609" ht="24" customHeight="1">
+      <c r="A609" s="8" t="n">
+        <v>608</v>
+      </c>
+      <c r="B609" s="9" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="C609" s="9" t="inlineStr">
+        <is>
+          <t>かくにん</t>
+        </is>
+      </c>
+      <c r="D609" s="10" t="inlineStr">
+        <is>
+          <t>Xem lại, kiểm tra lại cách dùng máy</t>
+        </is>
+      </c>
+      <c r="E609" s="10" t="inlineStr">
+        <is>
+          <t>もう一度最初から確認しておきましょう (hãy kiểm tra lại từ đầu cách thao tác)</t>
+        </is>
+      </c>
+      <c r="F609" s="10" t="inlineStr">
+        <is>
+          <t>Câu 308-4 kiểm tra máy móc dùng 確認する/おさらいする.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610" ht="24" customHeight="1">
+      <c r="A610" s="5" t="n">
+        <v>609</v>
+      </c>
+      <c r="B610" s="6" t="inlineStr">
+        <is>
+          <t>役目</t>
+        </is>
+      </c>
+      <c r="C610" s="6" t="inlineStr">
+        <is>
+          <t>やくめ</t>
+        </is>
+      </c>
+      <c r="D610" s="7" t="inlineStr">
+        <is>
+          <t>Bổn phận, trách nhiệm, nhiệm vụ được giao</t>
+        </is>
+      </c>
+      <c r="E610" s="7" t="inlineStr">
+        <is>
+          <t>部下に仕事を教えるのは課長の役目の一つだ (hướng dẫn công việc cho cấp dưới là một trong những bổn phận của trưởng nhóm)</t>
+        </is>
+      </c>
+      <c r="F610" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 309] Phương án 4. Đi với `役目を果たす`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611" ht="24" customHeight="1">
+      <c r="A611" s="8" t="n">
+        <v>610</v>
+      </c>
+      <c r="B611" s="9" t="inlineStr">
+        <is>
+          <t>役</t>
+        </is>
+      </c>
+      <c r="C611" s="9" t="inlineStr">
+        <is>
+          <t>やく</t>
+        </is>
+      </c>
+      <c r="D611" s="10" t="inlineStr">
+        <is>
+          <t>Đóng vai bác sĩ trong vở kịch</t>
+        </is>
+      </c>
+      <c r="E611" s="10" t="inlineStr">
+        <is>
+          <t>医者の役を演じる (hóa thân thủ vai bác sĩ)</t>
+        </is>
+      </c>
+      <c r="F611" s="10" t="inlineStr">
+        <is>
+          <t>Câu 309-1 vai diễn sân khấu dùng 役.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612" ht="24" customHeight="1">
+      <c r="A612" s="2" t="n">
+        <v>611</v>
+      </c>
+      <c r="B612" s="3" t="inlineStr">
+        <is>
+          <t>日課</t>
+        </is>
+      </c>
+      <c r="C612" s="3" t="inlineStr">
+        <is>
+          <t>にっか</t>
+        </is>
+      </c>
+      <c r="D612" s="4" t="inlineStr">
+        <is>
+          <t>Thói quen hàng ngày, bài tập mỗi ngày</t>
+        </is>
+      </c>
+      <c r="E612" s="4" t="inlineStr">
+        <is>
+          <t>毎朝散歩することが日課になっている (đi bộ mỗi sáng đã thành thói quen thường nhật)</t>
+        </is>
+      </c>
+      <c r="F612" s="4" t="inlineStr">
+        <is>
+          <t>Câu 309-2 thói quen đi bộ hàng ngày dùng 日課.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613" ht="24" customHeight="1">
+      <c r="A613" s="8" t="n">
+        <v>612</v>
+      </c>
+      <c r="B613" s="9" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="C613" s="9" t="inlineStr">
+        <is>
+          <t>たんとう</t>
+        </is>
+      </c>
+      <c r="D613" s="10" t="inlineStr">
+        <is>
+          <t>Người phụ trách ca trực vệ sinh</t>
+        </is>
+      </c>
+      <c r="E613" s="10" t="inlineStr">
+        <is>
+          <t>今日の掃除の担当だ (người phụ trách dọn dẹp vệ sinh hôm nay)</t>
+        </is>
+      </c>
+      <c r="F613" s="10" t="inlineStr">
+        <is>
+          <t>Câu 309-3 phân công trực nhật dùng 担当/係.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614" ht="24" customHeight="1">
+      <c r="A614" s="5" t="n">
+        <v>613</v>
+      </c>
+      <c r="B614" s="6" t="inlineStr">
+        <is>
+          <t>最寄り</t>
+        </is>
+      </c>
+      <c r="C614" s="6" t="inlineStr">
+        <is>
+          <t>もより</t>
+        </is>
+      </c>
+      <c r="D614" s="7" t="inlineStr">
+        <is>
+          <t>Gần nhất (chỉ dùng cho địa điểm giao thông/cơ sở công cộng)</t>
+        </is>
+      </c>
+      <c r="E614" s="7" t="inlineStr">
+        <is>
+          <t>最寄りの店までは歩いて30分だ (đi bộ tới cửa hàng gần nhất cũng mất 30 phút)</t>
+        </is>
+      </c>
+      <c r="F614" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 310] Phương án 1. Đi với `最寄りの駅/バス停/店`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615" ht="24" customHeight="1">
+      <c r="A615" s="8" t="n">
+        <v>614</v>
+      </c>
+      <c r="B615" s="9" t="inlineStr">
+        <is>
+          <t>親しい</t>
+        </is>
+      </c>
+      <c r="C615" s="9" t="inlineStr">
+        <is>
+          <t>したしい</t>
+        </is>
+      </c>
+      <c r="D615" s="10" t="inlineStr">
+        <is>
+          <t>Bạn bè thân thiết nhất</t>
+        </is>
+      </c>
+      <c r="E615" s="10" t="inlineStr">
+        <is>
+          <t>一番親しい友達 (người bạn thân thiết nhất của tôi)</t>
+        </is>
+      </c>
+      <c r="F615" s="10" t="inlineStr">
+        <is>
+          <t>Câu 310-2 bạn thân dùng 親しい/親友.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616" ht="24" customHeight="1">
+      <c r="A616" s="2" t="n">
+        <v>615</v>
+      </c>
+      <c r="B616" s="3" t="inlineStr">
+        <is>
+          <t>直前</t>
+        </is>
+      </c>
+      <c r="C616" s="3" t="inlineStr">
+        <is>
+          <t>ちょくぜん</t>
+        </is>
+      </c>
+      <c r="D616" s="4" t="inlineStr">
+        <is>
+          <t>Kỳ thi sắp tới gần</t>
+        </is>
+      </c>
+      <c r="E616" s="4" t="inlineStr">
+        <is>
+          <t>次の試験／直近の試験 (kỳ thi gần nhất sắp diễn ra)</t>
+        </is>
+      </c>
+      <c r="F616" s="4" t="inlineStr">
+        <is>
+          <t>Câu 310-3 kỳ thi gần nhất dùng 次の/直近の.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617" ht="24" customHeight="1">
+      <c r="A617" s="8" t="n">
+        <v>616</v>
+      </c>
+      <c r="B617" s="9" t="inlineStr">
+        <is>
+          <t>隣の</t>
+        </is>
+      </c>
+      <c r="C617" s="9" t="inlineStr">
+        <is>
+          <t>となりの</t>
+        </is>
+      </c>
+      <c r="D617" s="10" t="inlineStr">
+        <is>
+          <t>Người ngồi bên cạnh trên tàu</t>
+        </is>
+      </c>
+      <c r="E617" s="10" t="inlineStr">
+        <is>
+          <t>隣の人に足を踏まれた (bị người ngồi bên cạnh giẫm vào chân)</t>
+        </is>
+      </c>
+      <c r="F617" s="10" t="inlineStr">
+        <is>
+          <t>Câu 310-4 người bên cạnh dùng 隣の人.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618" ht="24" customHeight="1">
+      <c r="A618" s="5" t="n">
+        <v>617</v>
+      </c>
+      <c r="B618" s="6" t="inlineStr">
+        <is>
+          <t>解約</t>
+        </is>
+      </c>
+      <c r="C618" s="6" t="inlineStr">
+        <is>
+          <t>かいやく</t>
+        </is>
+      </c>
+      <c r="D618" s="7" t="inlineStr">
+        <is>
+          <t>Hủy hợp đồng, hủy tài khoản dịch vụ tài chính</t>
+        </is>
+      </c>
+      <c r="E618" s="7" t="inlineStr">
+        <is>
+          <t>銀行の口座を解約した (đóng/tất toán tài khoản ngân hàng)</t>
+        </is>
+      </c>
+      <c r="F618" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 311] Phương án 2. Đi với `携帯／保険／口座を解約する`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619" ht="24" customHeight="1">
+      <c r="A619" s="8" t="n">
+        <v>618</v>
+      </c>
+      <c r="B619" s="9" t="inlineStr">
+        <is>
+          <t>撤回</t>
+        </is>
+      </c>
+      <c r="C619" s="9" t="inlineStr">
+        <is>
+          <t>てっかい</t>
+        </is>
+      </c>
+      <c r="D619" s="10" t="inlineStr">
+        <is>
+          <t>Rút lại lời phát ngôn</t>
+        </is>
+      </c>
+      <c r="E619" s="10" t="inlineStr">
+        <is>
+          <t>昨日の発言を撤回した (bộ trưởng tuyên bố rút lại phát ngôn ngày hôm qua)</t>
+        </is>
+      </c>
+      <c r="F619" s="10" t="inlineStr">
+        <is>
+          <t>Câu 311-1 rút lại phát biểu dùng 撤回する/取り消す.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620" ht="24" customHeight="1">
+      <c r="A620" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="B620" s="3" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="C620" s="3" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="D620" s="4" t="inlineStr">
+        <is>
+          <t>Hủy cuộc hẹn gặp</t>
+        </is>
+      </c>
+      <c r="E620" s="4" t="inlineStr">
+        <is>
+          <t>面会の約束をキャンセルした (hủy cuộc gặp gỡ đối tác)</t>
+        </is>
+      </c>
+      <c r="F620" s="4" t="inlineStr">
+        <is>
+          <t>Câu 311-3 hủy hẹn gặp dùng キャンセル/取りやめ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621" ht="24" customHeight="1">
+      <c r="A621" s="8" t="n">
+        <v>620</v>
+      </c>
+      <c r="B621" s="9" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+      <c r="C621" s="9" t="inlineStr">
+        <is>
+          <t>かいしょう</t>
+        </is>
+      </c>
+      <c r="D621" s="10" t="inlineStr">
+        <is>
+          <t>Xóa bỏ tình trạng thâm hụt tài chính</t>
+        </is>
+      </c>
+      <c r="E621" s="10" t="inlineStr">
+        <is>
+          <t>赤字を解消することができた (đã xóa bỏ được thâm hụt kinh doanh)</t>
+        </is>
+      </c>
+      <c r="F621" s="10" t="inlineStr">
+        <is>
+          <t>Câu 311-4 thâm hụt tài chính dùng 赤字を解消する.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622" ht="24" customHeight="1">
+      <c r="A622" s="5" t="n">
+        <v>621</v>
+      </c>
+      <c r="B622" s="6" t="inlineStr">
+        <is>
+          <t>演説</t>
+        </is>
+      </c>
+      <c r="C622" s="6" t="inlineStr">
+        <is>
+          <t>えんぜつ</t>
+        </is>
+      </c>
+      <c r="D622" s="7" t="inlineStr">
+        <is>
+          <t>Diễn thuyết, hùng biện chính trị trước công chúng</t>
+        </is>
+      </c>
+      <c r="E622" s="7" t="inlineStr">
+        <is>
+          <t>首相は国会での演説で決意を述べた (thủ tướng bày tỏ quyết tâm trong bài diễn thuyết tại Quốc hội)</t>
+        </is>
+      </c>
+      <c r="F622" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 312] Phương án 2. Đi với `街頭演説/国会での演説`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623" ht="24" customHeight="1">
+      <c r="A623" s="8" t="n">
+        <v>622</v>
+      </c>
+      <c r="B623" s="9" t="inlineStr">
+        <is>
+          <t>答辞</t>
+        </is>
+      </c>
+      <c r="C623" s="9" t="inlineStr">
+        <is>
+          <t>とうじ</t>
+        </is>
+      </c>
+      <c r="D623" s="10" t="inlineStr">
+        <is>
+          <t>Bài phát biểu tri ân bế giảng</t>
+        </is>
+      </c>
+      <c r="E623" s="10" t="inlineStr">
+        <is>
+          <t>卒業式での答辞／スピーチ (bài phát biểu chia tay bế giảng của học sinh)</t>
+        </is>
+      </c>
+      <c r="F623" s="10" t="inlineStr">
+        <is>
+          <t>Câu 312-1 phát biểu tốt nghiệp dùng 挨拶/答辞/スピーチ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624" ht="24" customHeight="1">
+      <c r="A624" s="2" t="n">
+        <v>623</v>
+      </c>
+      <c r="B624" s="3" t="inlineStr">
+        <is>
+          <t>インタビュー</t>
+        </is>
+      </c>
+      <c r="C624" s="3" t="inlineStr">
+        <is>
+          <t>インタビュー</t>
+        </is>
+      </c>
+      <c r="D624" s="4" t="inlineStr">
+        <is>
+          <t>Phỏng vấn sau trận đấu thể thao</t>
+        </is>
+      </c>
+      <c r="E624" s="4" t="inlineStr">
+        <is>
+          <t>試合後のインタビューで (trong cuộc phỏng vấn sau trận đấu)</t>
+        </is>
+      </c>
+      <c r="F624" s="4" t="inlineStr">
+        <is>
+          <t>Câu 312-2 cầu thủ chia sẻ sau trận đấu dùng インタビュー/コメント.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625" ht="24" customHeight="1">
+      <c r="A625" s="8" t="n">
+        <v>624</v>
+      </c>
+      <c r="B625" s="9" t="inlineStr">
+        <is>
+          <t>記者会見</t>
+        </is>
+      </c>
+      <c r="C625" s="9" t="inlineStr">
+        <is>
+          <t>きしゃかいけん</t>
+        </is>
+      </c>
+      <c r="D625" s="10" t="inlineStr">
+        <is>
+          <t>Họp báo định hướng kinh doanh</t>
+        </is>
+      </c>
+      <c r="E625" s="10" t="inlineStr">
+        <is>
+          <t>記者会見で方針を述べた (nêu phương châm trong buổi họp báo)</t>
+        </is>
+      </c>
+      <c r="F625" s="10" t="inlineStr">
+        <is>
+          <t>Câu 312-4 họp báo công ty dùng 記者会見.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626" ht="24" customHeight="1">
+      <c r="A626" s="5" t="n">
+        <v>625</v>
+      </c>
+      <c r="B626" s="6" t="inlineStr">
+        <is>
+          <t>きっぱり</t>
+        </is>
+      </c>
+      <c r="C626" s="6" t="inlineStr">
+        <is>
+          <t>きっぱり</t>
+        </is>
+      </c>
+      <c r="D626" s="7" t="inlineStr">
+        <is>
+          <t>Dứt khoát, thẳng thừng, kiên quyết (từ chối)</t>
+        </is>
+      </c>
+      <c r="E626" s="7" t="inlineStr">
+        <is>
+          <t>デートの誘いをきっぱり断った (thẳng thừng từ chối dứt khoát lời mời hẹn hò)</t>
+        </is>
+      </c>
+      <c r="F626" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 313] Phương án 3. Đi liền với `きっぱり断る`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="627" ht="24" customHeight="1">
+      <c r="A627" s="8" t="n">
+        <v>626</v>
+      </c>
+      <c r="B627" s="9" t="inlineStr">
+        <is>
+          <t>くっきり</t>
+        </is>
+      </c>
+      <c r="C627" s="9" t="inlineStr">
+        <is>
+          <t>くっきり</t>
+        </is>
+      </c>
+      <c r="D627" s="10" t="inlineStr">
+        <is>
+          <t>Rõ mồn một, nét căng (tầm nhìn)</t>
+        </is>
+      </c>
+      <c r="E627" s="10" t="inlineStr">
+        <is>
+          <t>遠くの物もくっきり見える (nhìn thấy rõ mồn một cảnh vật từ xa)</t>
+        </is>
+      </c>
+      <c r="F627" s="10" t="inlineStr">
+        <is>
+          <t>Câu 313-1 nhìn rõ mồn một dùng くっきり/はっきり.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628" ht="24" customHeight="1">
+      <c r="A628" s="2" t="n">
+        <v>627</v>
+      </c>
+      <c r="B628" s="3" t="inlineStr">
+        <is>
+          <t>すっかり</t>
+        </is>
+      </c>
+      <c r="C628" s="3" t="inlineStr">
+        <is>
+          <t>すっかり</t>
+        </is>
+      </c>
+      <c r="D628" s="4" t="inlineStr">
+        <is>
+          <t>Hoàn toàn ngấy phát ngán</t>
+        </is>
+      </c>
+      <c r="E628" s="4" t="inlineStr">
+        <is>
+          <t>すっかり飽きてしまった (hoàn toàn ngấy phát ngán món này)</t>
+        </is>
+      </c>
+      <c r="F628" s="4" t="inlineStr">
+        <is>
+          <t>Câu 313-2 ngán hoàn toàn dùng すっかり.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629" ht="24" customHeight="1">
+      <c r="A629" s="8" t="n">
+        <v>628</v>
+      </c>
+      <c r="B629" s="9" t="inlineStr">
+        <is>
+          <t>さっぱり</t>
+        </is>
+      </c>
+      <c r="C629" s="9" t="inlineStr">
+        <is>
+          <t>さっぱり</t>
+        </is>
+      </c>
+      <c r="D629" s="10" t="inlineStr">
+        <is>
+          <t>Hoàn toàn không nhớ ra nổi</t>
+        </is>
+      </c>
+      <c r="E629" s="10" t="inlineStr">
+        <is>
+          <t>さっぱり思い出せない (hoàn toàn không thể nhớ ra được chút nào)</t>
+        </is>
+      </c>
+      <c r="F629" s="10" t="inlineStr">
+        <is>
+          <t>Câu 313-4 phủ định hoàn toàn dùng さっぱり/全く.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630" ht="24" customHeight="1">
+      <c r="A630" s="5" t="n">
+        <v>629</v>
+      </c>
+      <c r="B630" s="6" t="inlineStr">
+        <is>
+          <t>保存</t>
+        </is>
+      </c>
+      <c r="C630" s="6" t="inlineStr">
+        <is>
+          <t>ほぞん</t>
+        </is>
+      </c>
+      <c r="D630" s="7" t="inlineStr">
+        <is>
+          <t>Bảo quản thực phẩm trong tủ lạnh, lưu file máy tính</t>
+        </is>
+      </c>
+      <c r="E630" s="7" t="inlineStr">
+        <is>
+          <t>この食蘭は必ず冷蔵庫で保存してください (thực phẩm này nhất định phải bảo quản trong tủ lạnh)</t>
+        </is>
+      </c>
+      <c r="F630" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 314] Phương án 3. Đi với `食品を保存する/データを保存する`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631" ht="24" customHeight="1">
+      <c r="A631" s="8" t="n">
+        <v>630</v>
+      </c>
+      <c r="B631" s="9" t="inlineStr">
+        <is>
+          <t>貯金</t>
+        </is>
+      </c>
+      <c r="C631" s="9" t="inlineStr">
+        <is>
+          <t>ちょきん</t>
+        </is>
+      </c>
+      <c r="D631" s="10" t="inlineStr">
+        <is>
+          <t>Tiết kiệm tiền bạc</t>
+        </is>
+      </c>
+      <c r="E631" s="10" t="inlineStr">
+        <is>
+          <t>お金を貯金したほうがいい (nên tiết kiệm tiền cho tương lai)</t>
+        </is>
+      </c>
+      <c r="F631" s="10" t="inlineStr">
+        <is>
+          <t>Câu 314-1 tiền bạc thì dùng 貯金/貯蓄.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632" ht="24" customHeight="1">
+      <c r="A632" s="2" t="n">
+        <v>631</v>
+      </c>
+      <c r="B632" s="3" t="inlineStr">
+        <is>
+          <t>確保</t>
+        </is>
+      </c>
+      <c r="C632" s="3" t="inlineStr">
+        <is>
+          <t>かくほ</t>
+        </is>
+      </c>
+      <c r="D632" s="4" t="inlineStr">
+        <is>
+          <t>Giữ chỗ ngồi, xí chỗ</t>
+        </is>
+      </c>
+      <c r="E632" s="4" t="inlineStr">
+        <is>
+          <t>友達の席を確保しておいた (xí sẵn chỗ ngồi cho bạn)</t>
+        </is>
+      </c>
+      <c r="F632" s="4" t="inlineStr">
+        <is>
+          <t>Câu 314-2 giữ chỗ dùng 確保する/取っておく.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633" ht="24" customHeight="1">
+      <c r="A633" s="8" t="n">
+        <v>632</v>
+      </c>
+      <c r="B633" s="9" t="inlineStr">
+        <is>
+          <t>温存</t>
+        </is>
+      </c>
+      <c r="C633" s="9" t="inlineStr">
+        <is>
+          <t>おんぞん</t>
+        </is>
+      </c>
+      <c r="D633" s="10" t="inlineStr">
+        <is>
+          <t>Dưỡng sức, giữ gìn thể lực</t>
+        </is>
+      </c>
+      <c r="E633" s="10" t="inlineStr">
+        <is>
+          <t>体力を温存しないと (nếu không biết giữ sức thì nửa chặng sau sẽ đuối)</t>
+        </is>
+      </c>
+      <c r="F633" s="10" t="inlineStr">
+        <is>
+          <t>Câu 314-4 thể lực dùng 温存/節約.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634" ht="24" customHeight="1">
+      <c r="A634" s="5" t="n">
+        <v>633</v>
+      </c>
+      <c r="B634" s="6" t="inlineStr">
+        <is>
+          <t>鈍い</t>
+        </is>
+      </c>
+      <c r="C634" s="6" t="inlineStr">
+        <is>
+          <t>にぶい</t>
+        </is>
+      </c>
+      <c r="D634" s="7" t="inlineStr">
+        <is>
+          <t>Chậm chạp, lờ đờ (cử động cơ thể, phản xạ)</t>
+        </is>
+      </c>
+      <c r="E634" s="7" t="inlineStr">
+        <is>
+          <t>疲れているのか、いつもより動きが鈍い (do mệt mỏi hay sao mà cử động chậm chạp hơn mọi khi)</t>
+        </is>
+      </c>
+      <c r="F634" s="7" t="inlineStr">
+        <is>
+          <t>[Đáp án đúng câu 315] Phương án 4. Đi với `動き/反応/感覚が鈍い`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635" ht="24" customHeight="1">
+      <c r="A635" s="8" t="n">
+        <v>634</v>
+      </c>
+      <c r="B635" s="9" t="inlineStr">
+        <is>
+          <t>遅い</t>
+        </is>
+      </c>
+      <c r="C635" s="9" t="inlineStr">
+        <is>
+          <t>おそい</t>
+        </is>
+      </c>
+      <c r="D635" s="10" t="inlineStr">
+        <is>
+          <t>Chậm chạm (tính toán con số)</t>
+        </is>
+      </c>
+      <c r="E635" s="10" t="inlineStr">
+        <is>
+          <t>計算がとても遅い (tính toán rất chậm)</t>
+        </is>
+      </c>
+      <c r="F635" s="10" t="inlineStr">
+        <is>
+          <t>Câu 315-1 tính toán kém/chậm dùng 苦手/遅い.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636" ht="24" customHeight="1">
+      <c r="A636" s="2" t="n">
+        <v>635</v>
+      </c>
+      <c r="B636" s="3" t="inlineStr">
+        <is>
+          <t>長く感じられた</t>
+        </is>
+      </c>
+      <c r="C636" s="3" t="inlineStr">
+        <is>
+          <t>ながくかんじられた</t>
+        </is>
+      </c>
+      <c r="D636" s="4" t="inlineStr">
+        <is>
+          <t>Thời gian trôi qua cảm giác dài lê thê</t>
+        </is>
+      </c>
+      <c r="E636" s="4" t="inlineStr">
+        <is>
+          <t>時間がたつのが遅く／長く感じられた (thấy thời gian trôi qua lâu ghê)</t>
+        </is>
+      </c>
+      <c r="F636" s="4" t="inlineStr">
+        <is>
+          <t>Câu 315-2 thời gian trôi chậm dùng 遅く/長く.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637" ht="24" customHeight="1">
+      <c r="A637" s="8" t="n">
+        <v>636</v>
+      </c>
+      <c r="B637" s="9" t="inlineStr">
+        <is>
+          <t>仕事が遅い</t>
+        </is>
+      </c>
+      <c r="C637" s="9" t="inlineStr">
+        <is>
+          <t>しごとがおそい</t>
+        </is>
+      </c>
+      <c r="D637" s="10" t="inlineStr">
+        <is>
+          <t>Làm việc chậm rãi nhưng cẩn thận</t>
+        </is>
+      </c>
+      <c r="E637" s="10" t="inlineStr">
+        <is>
+          <t>彼は仕事が遅いが、その分丁寧だ (anh ấy thao tác chậm nhưng rất cẩn thận)</t>
+        </is>
+      </c>
+      <c r="F637" s="10" t="inlineStr">
+        <is>
+          <t>Câu 315-3 làm việc chậm dùng 遅い/のろい.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F451"/>
+  <autoFilter ref="A1:F637"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>